--- a/AAII_Financials/Quarterly/IQ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IQ_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="92">
   <si>
     <t>IQ</t>
   </si>
@@ -656,403 +656,428 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1077300</v>
+        <v>1071400</v>
       </c>
       <c r="E8" s="3">
-        <v>1152800</v>
+        <v>1114300</v>
       </c>
       <c r="F8" s="3">
-        <v>1048400</v>
+        <v>1084700</v>
       </c>
       <c r="G8" s="3">
-        <v>1031600</v>
+        <v>1160700</v>
       </c>
       <c r="H8" s="3">
-        <v>919100</v>
+        <v>1055600</v>
       </c>
       <c r="I8" s="3">
+        <v>1038600</v>
+      </c>
+      <c r="J8" s="3">
+        <v>925400</v>
+      </c>
+      <c r="K8" s="3">
         <v>1004800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1020200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>1078800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>1092700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>1109200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>1038200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>1049600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>1092200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>1197700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>1154300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>1154000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>1086300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1063300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>1020600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>967700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>863600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>699800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>691200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>734700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>642100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>477600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>458800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>473800</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>797300</v>
+        <v>769200</v>
       </c>
       <c r="E9" s="3">
-        <v>822400</v>
+        <v>811800</v>
       </c>
       <c r="F9" s="3">
-        <v>745900</v>
+        <v>802700</v>
       </c>
       <c r="G9" s="3">
-        <v>787800</v>
+        <v>828000</v>
       </c>
       <c r="H9" s="3">
-        <v>724600</v>
+        <v>751000</v>
       </c>
       <c r="I9" s="3">
+        <v>793100</v>
+      </c>
+      <c r="J9" s="3">
+        <v>729600</v>
+      </c>
+      <c r="K9" s="3">
         <v>823500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>898600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>999000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>986500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>989600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>944400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>929300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>1007000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>1237300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>1218700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>1275500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>1066600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>1107000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>1237800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>1071400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>854700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>695600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>650700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>726900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>1304500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>1035100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>453900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>456800</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>280100</v>
+        <v>302100</v>
       </c>
       <c r="E10" s="3">
-        <v>330400</v>
+        <v>302400</v>
       </c>
       <c r="F10" s="3">
-        <v>302500</v>
+        <v>282000</v>
       </c>
       <c r="G10" s="3">
-        <v>243800</v>
+        <v>332600</v>
       </c>
       <c r="H10" s="3">
-        <v>194500</v>
+        <v>304500</v>
       </c>
       <c r="I10" s="3">
+        <v>245500</v>
+      </c>
+      <c r="J10" s="3">
+        <v>195800</v>
+      </c>
+      <c r="K10" s="3">
         <v>181300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>121700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>79800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>106200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>119600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>93800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>120400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>85200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>-39600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>-64300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>-121500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>19700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>-43700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>-217200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>-103700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>8900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>4200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>40500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>7800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>-662500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>-557500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>4900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1084,97 +1109,105 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>60600</v>
+        <v>62800</v>
       </c>
       <c r="E12" s="3">
-        <v>59100</v>
+        <v>62200</v>
       </c>
       <c r="F12" s="3">
-        <v>64400</v>
+        <v>61000</v>
       </c>
       <c r="G12" s="3">
-        <v>65700</v>
+        <v>59500</v>
       </c>
       <c r="H12" s="3">
-        <v>66600</v>
+        <v>64800</v>
       </c>
       <c r="I12" s="3">
+        <v>66200</v>
+      </c>
+      <c r="J12" s="3">
+        <v>67000</v>
+      </c>
+      <c r="K12" s="3">
         <v>65600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>105400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>97100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>97200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>93600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>92300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>97800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>97900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>106200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>109500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>109700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>100000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>91000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>88200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>78100</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>61800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>55600</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>52300</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>50800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>87400</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>78200</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>35500</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>33400</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1262,8 +1295,14 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1351,8 +1390,14 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1440,8 +1485,14 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,186 +1521,200 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>993100</v>
+        <v>963800</v>
       </c>
       <c r="E17" s="3">
-        <v>1034200</v>
+        <v>1010400</v>
       </c>
       <c r="F17" s="3">
-        <v>940200</v>
+        <v>999800</v>
       </c>
       <c r="G17" s="3">
-        <v>988800</v>
+        <v>1041300</v>
       </c>
       <c r="H17" s="3">
-        <v>901800</v>
+        <v>946600</v>
       </c>
       <c r="I17" s="3">
+        <v>995600</v>
+      </c>
+      <c r="J17" s="3">
+        <v>907900</v>
+      </c>
+      <c r="K17" s="3">
         <v>991900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1154900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1273200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1253800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1250400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>1220200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>1226300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>1281000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>1548600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1543700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>1595700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>1372300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>1371500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>1503400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>1330400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>1049400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>852200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>814000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>893000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>789100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>628800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>569700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>557900</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>84300</v>
+        <v>107600</v>
       </c>
       <c r="E18" s="3">
-        <v>118600</v>
+        <v>103800</v>
       </c>
       <c r="F18" s="3">
-        <v>108200</v>
+        <v>84900</v>
       </c>
       <c r="G18" s="3">
-        <v>42800</v>
+        <v>119400</v>
       </c>
       <c r="H18" s="3">
-        <v>17400</v>
+        <v>108900</v>
       </c>
       <c r="I18" s="3">
+        <v>43100</v>
+      </c>
+      <c r="J18" s="3">
+        <v>17500</v>
+      </c>
+      <c r="K18" s="3">
         <v>12900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-134700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-194500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-161100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-141200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-182000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-176600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-188900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-351000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-389400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-441800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-286000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-308200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-482800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-362700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-185900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-152400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-122800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-158300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-147000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-151200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-110900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-84100</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1681,97 +1746,105 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E20" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F20" s="3">
         <v>6100</v>
       </c>
-      <c r="E20" s="3">
-        <v>10700</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-43400</v>
-      </c>
       <c r="G20" s="3">
-        <v>-66300</v>
+        <v>10800</v>
       </c>
       <c r="H20" s="3">
-        <v>-15100</v>
+        <v>-43700</v>
       </c>
       <c r="I20" s="3">
+        <v>-66800</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="K20" s="3">
         <v>37700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-59200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>3000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>16800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>15100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>3900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>49100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>18400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-57400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>54200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-89300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-27300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>52700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>3800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-73300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-106200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>96800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>39800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>2300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>17900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>-20200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
@@ -1841,293 +1914,317 @@
       <c r="Y21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB21" s="3">
         <v>1174600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>835600</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AD21" s="3">
+      <c r="AD21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AE21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF21" s="3">
         <v>598900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>443800</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>38500</v>
+        <v>39500</v>
       </c>
       <c r="E22" s="3">
-        <v>39500</v>
+        <v>39100</v>
       </c>
       <c r="F22" s="3">
-        <v>24300</v>
+        <v>38700</v>
       </c>
       <c r="G22" s="3">
-        <v>25100</v>
+        <v>39800</v>
       </c>
       <c r="H22" s="3">
-        <v>25100</v>
+        <v>24500</v>
       </c>
       <c r="I22" s="3">
+        <v>25300</v>
+      </c>
+      <c r="J22" s="3">
+        <v>25300</v>
+      </c>
+      <c r="K22" s="3">
         <v>24200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>44800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>49900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>49300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>46000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>37500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>39300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>39100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>41000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>42600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>39700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>37900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>20600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>8900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>2200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>1300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>1200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>6300</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD22" s="3">
         <v>12200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>9900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>6100</v>
       </c>
-      <c r="AE22" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>51900</v>
+        <v>71400</v>
       </c>
       <c r="E23" s="3">
-        <v>89800</v>
+        <v>68500</v>
       </c>
       <c r="F23" s="3">
-        <v>40500</v>
+        <v>52200</v>
       </c>
       <c r="G23" s="3">
-        <v>-48700</v>
+        <v>90400</v>
       </c>
       <c r="H23" s="3">
-        <v>-22800</v>
+        <v>40700</v>
       </c>
       <c r="I23" s="3">
+        <v>-49000</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-23000</v>
+      </c>
+      <c r="K23" s="3">
         <v>26300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-238700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-241400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-193600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-172100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-215500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-166900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-209600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-449400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-377800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-570700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-351100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-276100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-487900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-438200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-293400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-56900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-89300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-156000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-141400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-162700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-137200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-91300</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E24" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F24" s="3">
         <v>1100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>3400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>-1600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>5900</v>
-      </c>
-      <c r="H24" s="3">
-        <v>5000</v>
-      </c>
-      <c r="I24" s="3">
-        <v>2300</v>
       </c>
       <c r="J24" s="3">
         <v>5000</v>
       </c>
       <c r="K24" s="3">
+        <v>2300</v>
+      </c>
+      <c r="L24" s="3">
+        <v>5000</v>
+      </c>
+      <c r="M24" s="3">
         <v>1300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>4400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>2900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>-2300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>2800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>2300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>3500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>2500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>1100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>11500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>-800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>700</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>100</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>-1400</v>
       </c>
       <c r="AA24" s="3">
         <v>100</v>
       </c>
       <c r="AB24" s="3">
-        <v>100</v>
+        <v>-1400</v>
       </c>
       <c r="AC24" s="3">
         <v>100</v>
       </c>
       <c r="AD24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF24" s="3">
         <v>600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,186 +2312,204 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>50800</v>
+        <v>66100</v>
       </c>
       <c r="E26" s="3">
-        <v>86400</v>
+        <v>67200</v>
       </c>
       <c r="F26" s="3">
-        <v>42100</v>
+        <v>51100</v>
       </c>
       <c r="G26" s="3">
-        <v>-54500</v>
+        <v>87000</v>
       </c>
       <c r="H26" s="3">
-        <v>-27800</v>
+        <v>42400</v>
       </c>
       <c r="I26" s="3">
+        <v>-54900</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="K26" s="3">
         <v>24000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-243700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-242700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-198000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-175000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-213300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-169600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-212000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-450100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-381200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-573200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-352000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-277200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-499400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-437300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-294100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-56900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-87900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-156100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-141500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-162800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-137800</v>
       </c>
-      <c r="AE26" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG26" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>50400</v>
+        <v>64800</v>
       </c>
       <c r="E27" s="3">
-        <v>85300</v>
+        <v>66200</v>
       </c>
       <c r="F27" s="3">
-        <v>42000</v>
+        <v>50800</v>
       </c>
       <c r="G27" s="3">
-        <v>-54600</v>
+        <v>85900</v>
       </c>
       <c r="H27" s="3">
-        <v>-29500</v>
+        <v>42300</v>
       </c>
       <c r="I27" s="3">
+        <v>-55000</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-29700</v>
+      </c>
+      <c r="K27" s="3">
         <v>23300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-246300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-246500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-201300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-176800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-215700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-171700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-212700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-450300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-384200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-575400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-355600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-275900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-504900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-439500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-294800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-98300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>2198300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-1737000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-248500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-267600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-410200</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG27" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2597,14 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2571,8 +2692,14 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2787,14 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,186 +2882,204 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="F32" s="3">
         <v>-6100</v>
       </c>
-      <c r="E32" s="3">
-        <v>-10700</v>
-      </c>
-      <c r="F32" s="3">
-        <v>43400</v>
-      </c>
       <c r="G32" s="3">
-        <v>66300</v>
+        <v>-10800</v>
       </c>
       <c r="H32" s="3">
-        <v>15100</v>
+        <v>43700</v>
       </c>
       <c r="I32" s="3">
+        <v>66800</v>
+      </c>
+      <c r="J32" s="3">
+        <v>15200</v>
+      </c>
+      <c r="K32" s="3">
         <v>-37700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>59200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-3000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-16800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-15100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-3900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-49100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-18400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>57400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-54200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>89300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>27300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-52700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-3800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>73300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>106200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-96800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-39800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-17900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>1600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>20200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>50400</v>
+        <v>64800</v>
       </c>
       <c r="E33" s="3">
-        <v>85300</v>
+        <v>66200</v>
       </c>
       <c r="F33" s="3">
-        <v>42000</v>
+        <v>50800</v>
       </c>
       <c r="G33" s="3">
-        <v>-54600</v>
+        <v>85900</v>
       </c>
       <c r="H33" s="3">
-        <v>-29500</v>
+        <v>42300</v>
       </c>
       <c r="I33" s="3">
+        <v>-55000</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-29700</v>
+      </c>
+      <c r="K33" s="3">
         <v>23300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-246300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-246500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-201300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-176800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-215700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-171700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-212700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-450300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-384200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-575400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-355600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-275900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-504900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-439500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-294800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-98300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>2198300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-1737000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-248500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-267600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-410200</v>
       </c>
-      <c r="AE33" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AG33" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,191 +3167,209 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>50400</v>
+        <v>64800</v>
       </c>
       <c r="E35" s="3">
-        <v>85300</v>
+        <v>66200</v>
       </c>
       <c r="F35" s="3">
-        <v>42000</v>
+        <v>50800</v>
       </c>
       <c r="G35" s="3">
-        <v>-54600</v>
+        <v>85900</v>
       </c>
       <c r="H35" s="3">
-        <v>-29500</v>
+        <v>42300</v>
       </c>
       <c r="I35" s="3">
+        <v>-55000</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-29700</v>
+      </c>
+      <c r="K35" s="3">
         <v>23300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-246300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-246500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-201300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-176800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-215700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-171700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-212700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-450300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-384200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-575400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-355600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-275900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-504900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-439500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-294800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-98300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>2198300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-1737000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-248500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-267600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-410200</v>
       </c>
-      <c r="AE35" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AG35" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3401,10 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,809 +3436,865 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>492300</v>
+        <v>616500</v>
       </c>
       <c r="E41" s="3">
-        <v>625400</v>
+        <v>588100</v>
       </c>
       <c r="F41" s="3">
-        <v>980100</v>
+        <v>495600</v>
       </c>
       <c r="G41" s="3">
-        <v>491600</v>
+        <v>629700</v>
       </c>
       <c r="H41" s="3">
-        <v>403600</v>
+        <v>986800</v>
       </c>
       <c r="I41" s="3">
+        <v>494900</v>
+      </c>
+      <c r="J41" s="3">
+        <v>406400</v>
+      </c>
+      <c r="K41" s="3">
         <v>526300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>413900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1037100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>960100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1023500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1519400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>461900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>630800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>578200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>913800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>702900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>829200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>1806300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>666100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>816200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>1159100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>57900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>105200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>176500</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD41" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AE41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>140100</v>
+        <v>130900</v>
       </c>
       <c r="E42" s="3">
-        <v>92400</v>
+        <v>142500</v>
       </c>
       <c r="F42" s="3">
-        <v>113000</v>
+        <v>141100</v>
       </c>
       <c r="G42" s="3">
-        <v>203000</v>
+        <v>93000</v>
       </c>
       <c r="H42" s="3">
-        <v>261000</v>
+        <v>113800</v>
       </c>
       <c r="I42" s="3">
+        <v>204400</v>
+      </c>
+      <c r="J42" s="3">
+        <v>262800</v>
+      </c>
+      <c r="K42" s="3">
         <v>177100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>186200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>520500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>793700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>823300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>467500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>526300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>618400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>823300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>705100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>1067400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>1347200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>591100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>880400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>538000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>665100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>70700</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>111900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>497500</v>
       </c>
-      <c r="AB42" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD42" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AE42" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG42" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>393800</v>
+        <v>538900</v>
       </c>
       <c r="E43" s="3">
-        <v>399600</v>
+        <v>372000</v>
       </c>
       <c r="F43" s="3">
-        <v>346100</v>
+        <v>396500</v>
       </c>
       <c r="G43" s="3">
-        <v>380200</v>
+        <v>402400</v>
       </c>
       <c r="H43" s="3">
-        <v>356600</v>
+        <v>348500</v>
       </c>
       <c r="I43" s="3">
+        <v>382800</v>
+      </c>
+      <c r="J43" s="3">
+        <v>359000</v>
+      </c>
+      <c r="K43" s="3">
         <v>388200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>400900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>448800</v>
-      </c>
-      <c r="L43" s="3">
-        <v>478900</v>
-      </c>
-      <c r="M43" s="3">
-        <v>494800</v>
       </c>
       <c r="N43" s="3">
         <v>478900</v>
       </c>
       <c r="O43" s="3">
+        <v>494800</v>
+      </c>
+      <c r="P43" s="3">
+        <v>478900</v>
+      </c>
+      <c r="Q43" s="3">
         <v>500900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>503700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>717100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>591200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>514100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>513100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>535000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>460500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>452200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>350200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>420800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>322200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>693700</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD43" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AE43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>114900</v>
+        <v>81000</v>
       </c>
       <c r="E44" s="3">
-        <v>129900</v>
+        <v>96900</v>
       </c>
       <c r="F44" s="3">
-        <v>103000</v>
+        <v>115700</v>
       </c>
       <c r="G44" s="3">
-        <v>113000</v>
+        <v>130700</v>
       </c>
       <c r="H44" s="3">
-        <v>109900</v>
+        <v>103700</v>
       </c>
       <c r="I44" s="3">
+        <v>113700</v>
+      </c>
+      <c r="J44" s="3">
+        <v>110700</v>
+      </c>
+      <c r="K44" s="3">
         <v>125700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>128600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>155900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>127900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>143600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>144100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>182200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>174500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>224300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>188600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>206500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>179700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>191900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>169000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>147200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>162900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>172400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>117500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>110300</v>
       </c>
-      <c r="AB44" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD44" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AE44" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG44" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>368800</v>
+        <v>389300</v>
       </c>
       <c r="E45" s="3">
-        <v>1550300</v>
+        <v>411400</v>
       </c>
       <c r="F45" s="3">
-        <v>361300</v>
+        <v>371300</v>
       </c>
       <c r="G45" s="3">
-        <v>309900</v>
+        <v>1560800</v>
       </c>
       <c r="H45" s="3">
-        <v>306600</v>
+        <v>363800</v>
       </c>
       <c r="I45" s="3">
+        <v>312000</v>
+      </c>
+      <c r="J45" s="3">
+        <v>308700</v>
+      </c>
+      <c r="K45" s="3">
         <v>381200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>461800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>540900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>588900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>597800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>492900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>601500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>679700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>690600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>722800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>1031300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>926000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>772700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>707300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>430500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>377800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>145500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>161200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>137200</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD45" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AE45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1509900</v>
+        <v>1756500</v>
       </c>
       <c r="E46" s="3">
-        <v>2797500</v>
+        <v>1611000</v>
       </c>
       <c r="F46" s="3">
-        <v>1903500</v>
+        <v>1520200</v>
       </c>
       <c r="G46" s="3">
-        <v>1497700</v>
+        <v>2816600</v>
       </c>
       <c r="H46" s="3">
-        <v>1437800</v>
+        <v>1916500</v>
       </c>
       <c r="I46" s="3">
+        <v>1507900</v>
+      </c>
+      <c r="J46" s="3">
+        <v>1447600</v>
+      </c>
+      <c r="K46" s="3">
         <v>1598500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1591300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>2703300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>2949500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>3083100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>3102800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>2272700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>2607100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>3033400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>3121600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>3522200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>3795200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>3897100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>2883300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>2384200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>2715100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>867300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>817900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>1615200</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD46" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AE46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>350000</v>
+        <v>336300</v>
       </c>
       <c r="E47" s="3">
-        <v>320400</v>
+        <v>349400</v>
       </c>
       <c r="F47" s="3">
-        <v>347100</v>
+        <v>352400</v>
       </c>
       <c r="G47" s="3">
-        <v>402900</v>
+        <v>322600</v>
       </c>
       <c r="H47" s="3">
-        <v>445400</v>
+        <v>349400</v>
       </c>
       <c r="I47" s="3">
+        <v>405600</v>
+      </c>
+      <c r="J47" s="3">
+        <v>448400</v>
+      </c>
+      <c r="K47" s="3">
         <v>452500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>430300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>499900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>503200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>485900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>451300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>577200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>579900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>580200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>485700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>480400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>413700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>400600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>381200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>322800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>173900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>170000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>81500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>59000</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD47" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AE47" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG47" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>223200</v>
+        <v>215200</v>
       </c>
       <c r="E48" s="3">
-        <v>233400</v>
+        <v>214700</v>
       </c>
       <c r="F48" s="3">
-        <v>245600</v>
+        <v>224700</v>
       </c>
       <c r="G48" s="3">
-        <v>260300</v>
+        <v>235000</v>
       </c>
       <c r="H48" s="3">
-        <v>290100</v>
+        <v>247300</v>
       </c>
       <c r="I48" s="3">
+        <v>262000</v>
+      </c>
+      <c r="J48" s="3">
+        <v>292000</v>
+      </c>
+      <c r="K48" s="3">
         <v>302900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>311000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>320700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>345200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>323500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>333400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>360000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>408400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>402000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>381400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>369600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>358100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>265700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>235000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>206500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>196600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>189200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>179200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>179600</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD48" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AE48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>3230800</v>
+        <v>3402400</v>
       </c>
       <c r="E49" s="3">
-        <v>3251100</v>
+        <v>3312600</v>
       </c>
       <c r="F49" s="3">
-        <v>3328500</v>
+        <v>3252800</v>
       </c>
       <c r="G49" s="3">
-        <v>3342400</v>
+        <v>3273200</v>
       </c>
       <c r="H49" s="3">
-        <v>3269200</v>
+        <v>3351100</v>
       </c>
       <c r="I49" s="3">
+        <v>3365100</v>
+      </c>
+      <c r="J49" s="3">
+        <v>3291500</v>
+      </c>
+      <c r="K49" s="3">
         <v>3244400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>3126500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>3033800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>2854200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>2546200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>2436900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>2355300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>2174600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>2369400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>2362800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>2601800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>2423100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>2432100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>2315500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>2285000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>1858100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>1623800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>1409900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>1221500</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD49" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AE49" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG49" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4382,14 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,97 +4477,109 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>635800</v>
+        <v>489100</v>
       </c>
       <c r="E52" s="3">
-        <v>582300</v>
+        <v>643900</v>
       </c>
       <c r="F52" s="3">
-        <v>533700</v>
+        <v>640200</v>
       </c>
       <c r="G52" s="3">
-        <v>419400</v>
+        <v>586300</v>
       </c>
       <c r="H52" s="3">
-        <v>438300</v>
+        <v>537300</v>
       </c>
       <c r="I52" s="3">
+        <v>422200</v>
+      </c>
+      <c r="J52" s="3">
+        <v>441300</v>
+      </c>
+      <c r="K52" s="3">
         <v>420100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>405500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>449900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>373200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>380400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>382900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>405700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>460100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>431800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>545600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>562800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>686200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>787200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>685500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>570200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>530500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>439700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>409900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>378500</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD52" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AE52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,97 +4667,109 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>5949700</v>
+        <v>6199500</v>
       </c>
       <c r="E54" s="3">
-        <v>7184700</v>
+        <v>6131600</v>
       </c>
       <c r="F54" s="3">
-        <v>6358400</v>
+        <v>5990200</v>
       </c>
       <c r="G54" s="3">
-        <v>5922600</v>
+        <v>7233600</v>
       </c>
       <c r="H54" s="3">
-        <v>5880800</v>
+        <v>6401600</v>
       </c>
       <c r="I54" s="3">
+        <v>5962900</v>
+      </c>
+      <c r="J54" s="3">
+        <v>5920800</v>
+      </c>
+      <c r="K54" s="3">
         <v>6018500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>5864600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>7007500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>7025300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>6819100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>6707400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>5970900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>6230000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>6816800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>6897200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>7536800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>7676300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>7782700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>6500500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>5768700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>5474100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>3289900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>2898400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>3453700</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD54" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AE54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4801,10 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,542 +4836,580 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>792600</v>
+        <v>788400</v>
       </c>
       <c r="E57" s="3">
-        <v>790000</v>
+        <v>825200</v>
       </c>
       <c r="F57" s="3">
-        <v>827600</v>
+        <v>798000</v>
       </c>
       <c r="G57" s="3">
-        <v>950300</v>
+        <v>795400</v>
       </c>
       <c r="H57" s="3">
-        <v>871400</v>
+        <v>833200</v>
       </c>
       <c r="I57" s="3">
+        <v>956800</v>
+      </c>
+      <c r="J57" s="3">
+        <v>877400</v>
+      </c>
+      <c r="K57" s="3">
         <v>969600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1228400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1297500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>1181700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>1045200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>1052600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>1088800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>1133500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>1304000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>1264600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>1574100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>1464200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>1574600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>1475900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>1458800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>1269100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>1252000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>1010300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>1035600</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD57" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AE57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>416400</v>
+        <v>886100</v>
       </c>
       <c r="E58" s="3">
-        <v>1591700</v>
+        <v>900200</v>
       </c>
       <c r="F58" s="3">
-        <v>1609100</v>
+        <v>419200</v>
       </c>
       <c r="G58" s="3">
-        <v>1720400</v>
+        <v>1602500</v>
       </c>
       <c r="H58" s="3">
-        <v>1667600</v>
+        <v>1620000</v>
       </c>
       <c r="I58" s="3">
+        <v>1732100</v>
+      </c>
+      <c r="J58" s="3">
+        <v>1678900</v>
+      </c>
+      <c r="K58" s="3">
         <v>606400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>568600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1344000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1249600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1102100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>1200900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>662600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>601300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>519500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>516600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>604300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>667800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>557600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>454600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>165500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>89900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>58400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>44400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>1232000</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC58" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD58" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AE58" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG58" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1378400</v>
+        <v>1431400</v>
       </c>
       <c r="E59" s="3">
-        <v>1439900</v>
+        <v>1415900</v>
       </c>
       <c r="F59" s="3">
-        <v>1447600</v>
+        <v>1387800</v>
       </c>
       <c r="G59" s="3">
-        <v>1354300</v>
+        <v>1449700</v>
       </c>
       <c r="H59" s="3">
-        <v>1348900</v>
+        <v>1457400</v>
       </c>
       <c r="I59" s="3">
+        <v>1363500</v>
+      </c>
+      <c r="J59" s="3">
+        <v>1358100</v>
+      </c>
+      <c r="K59" s="3">
         <v>1389900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1306500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1331100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1335500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1355800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1206300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>1242700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1281200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1445100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>1325100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>1178200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>1144200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>1013800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>946900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>887200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>710200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>619500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>613400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>1325600</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD59" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AE59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>2587300</v>
+        <v>3105900</v>
       </c>
       <c r="E60" s="3">
-        <v>3821600</v>
+        <v>3141300</v>
       </c>
       <c r="F60" s="3">
-        <v>3884200</v>
+        <v>2604900</v>
       </c>
       <c r="G60" s="3">
-        <v>4025000</v>
+        <v>3847600</v>
       </c>
       <c r="H60" s="3">
-        <v>3887900</v>
+        <v>3910600</v>
       </c>
       <c r="I60" s="3">
+        <v>4052400</v>
+      </c>
+      <c r="J60" s="3">
+        <v>3914400</v>
+      </c>
+      <c r="K60" s="3">
         <v>2965900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>3103600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>3972600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>3766800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>3503200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>3459800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>2994100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>3016000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>3268600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>3106300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>3356700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>3276200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>3146000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>2877300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>2511500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>2069200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>1929900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>1668000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>3593200</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD60" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AE60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1580600</v>
+        <v>1145800</v>
       </c>
       <c r="E61" s="3">
-        <v>1611200</v>
+        <v>1160700</v>
       </c>
       <c r="F61" s="3">
-        <v>1321200</v>
+        <v>1591300</v>
       </c>
       <c r="G61" s="3">
-        <v>879600</v>
+        <v>1622100</v>
       </c>
       <c r="H61" s="3">
-        <v>827100</v>
+        <v>1330200</v>
       </c>
       <c r="I61" s="3">
+        <v>885600</v>
+      </c>
+      <c r="J61" s="3">
+        <v>832800</v>
+      </c>
+      <c r="K61" s="3">
         <v>1828100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>1747000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>1801200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>1808500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>1763700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>1660200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>1889000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>2001200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>2112200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>2029000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>2057800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>1879700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>1856600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>777900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>38300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>39000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>40000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>40700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>42100</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
       <c r="AD61" s="3">
         <v>0</v>
       </c>
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>298700</v>
+        <v>253800</v>
       </c>
       <c r="E62" s="3">
-        <v>281200</v>
+        <v>252200</v>
       </c>
       <c r="F62" s="3">
-        <v>277100</v>
+        <v>300700</v>
       </c>
       <c r="G62" s="3">
-        <v>265400</v>
+        <v>283100</v>
       </c>
       <c r="H62" s="3">
-        <v>286800</v>
+        <v>279000</v>
       </c>
       <c r="I62" s="3">
+        <v>267200</v>
+      </c>
+      <c r="J62" s="3">
+        <v>288800</v>
+      </c>
+      <c r="K62" s="3">
         <v>271600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>230700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>232500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>253100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>258600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>272800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>288000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>290300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>281500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>266000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>220700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>225900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>248700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>208500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>210000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>97000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>96100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>1200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>1100</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD62" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AE62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5497,14 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5592,14 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,97 +5687,109 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>4477900</v>
+        <v>4519200</v>
       </c>
       <c r="E66" s="3">
-        <v>5725300</v>
+        <v>4566700</v>
       </c>
       <c r="F66" s="3">
-        <v>5495300</v>
+        <v>4508400</v>
       </c>
       <c r="G66" s="3">
-        <v>5183000</v>
+        <v>5764300</v>
       </c>
       <c r="H66" s="3">
-        <v>5014700</v>
+        <v>5532700</v>
       </c>
       <c r="I66" s="3">
+        <v>5218300</v>
+      </c>
+      <c r="J66" s="3">
+        <v>5048800</v>
+      </c>
+      <c r="K66" s="3">
         <v>5075000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>5148300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>6071100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>5873200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>5566700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>5418900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>5194800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>5329500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>5684500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>5423400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>5659900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>5402400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>5268100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>3880900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>2771200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>2205600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>2066400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>1710600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>3636400</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD66" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AE66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5821,10 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5912,14 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +6007,14 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5747,28 +6082,34 @@
         <v>0</v>
       </c>
       <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="3">
         <v>3284400</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AB70" s="3">
         <v>3242900</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AC70" s="3">
         <v>4323600</v>
       </c>
-      <c r="AB70" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC70" s="3">
-        <v>0</v>
-      </c>
       <c r="AD70" s="3">
         <v>0</v>
       </c>
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,97 +6197,109 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-6284800</v>
+        <v>-6196600</v>
       </c>
       <c r="E72" s="3">
-        <v>-6335200</v>
+        <v>-6261400</v>
       </c>
       <c r="F72" s="3">
-        <v>-6420600</v>
+        <v>-6327600</v>
       </c>
       <c r="G72" s="3">
-        <v>-6462600</v>
+        <v>-6378300</v>
       </c>
       <c r="H72" s="3">
-        <v>-6408000</v>
+        <v>-6464300</v>
       </c>
       <c r="I72" s="3">
+        <v>-6506600</v>
+      </c>
+      <c r="J72" s="3">
+        <v>-6451600</v>
+      </c>
+      <c r="K72" s="3">
         <v>-6378400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-6512400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-6450800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-6268400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-5880400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-5703600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-5757100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-5636300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-5750400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-5209800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-4889200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-4224500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-3852200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-3414300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-2796700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-2357100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-2130900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-2154600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-4631600</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD72" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AE72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6387,14 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6482,14 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,97 +6577,109 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1471800</v>
+        <v>1680300</v>
       </c>
       <c r="E76" s="3">
-        <v>1459400</v>
+        <v>1564800</v>
       </c>
       <c r="F76" s="3">
-        <v>863100</v>
+        <v>1481800</v>
       </c>
       <c r="G76" s="3">
-        <v>739600</v>
+        <v>1469300</v>
       </c>
       <c r="H76" s="3">
-        <v>866100</v>
+        <v>869000</v>
       </c>
       <c r="I76" s="3">
+        <v>744600</v>
+      </c>
+      <c r="J76" s="3">
+        <v>872000</v>
+      </c>
+      <c r="K76" s="3">
         <v>943500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>716300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>936400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>1152200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1252400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>1288500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>776100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>900500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>1132300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>1473700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>1876900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>2273900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>2514600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>2619500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>2997500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>3268500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>-2060900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>-2055000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>-4506300</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD76" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AE76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,191 +6767,209 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>50400</v>
+        <v>64800</v>
       </c>
       <c r="E81" s="3">
-        <v>85300</v>
+        <v>66200</v>
       </c>
       <c r="F81" s="3">
-        <v>42000</v>
+        <v>50800</v>
       </c>
       <c r="G81" s="3">
-        <v>-54600</v>
+        <v>85900</v>
       </c>
       <c r="H81" s="3">
-        <v>-29500</v>
+        <v>42300</v>
       </c>
       <c r="I81" s="3">
+        <v>-55000</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-29700</v>
+      </c>
+      <c r="K81" s="3">
         <v>23300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-246300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-246500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-201300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-176800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-215700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-171700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-212700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-450300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-384200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-575400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-355600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-275900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-504900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-439500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-294800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-98300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>2198300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-1737000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-248500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-267600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-410200</v>
       </c>
-      <c r="AE81" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG81" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,8 +7001,10 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6686,17 +7083,23 @@
       <c r="AB83" s="3">
         <v>0</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AD83" s="3" t="s">
-        <v>16</v>
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD83" s="3">
+        <v>0</v>
       </c>
       <c r="AE83" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG83" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +7187,14 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7282,14 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7377,14 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7472,14 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,59 +7567,65 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-16000</v>
+        <v>88100</v>
       </c>
       <c r="E89" s="3">
-        <v>138300</v>
+        <v>115500</v>
       </c>
       <c r="F89" s="3">
-        <v>117800</v>
+        <v>123100</v>
       </c>
       <c r="G89" s="3">
-        <v>27000</v>
+        <v>139300</v>
       </c>
       <c r="H89" s="3">
-        <v>6500</v>
+        <v>118600</v>
       </c>
       <c r="I89" s="3">
+        <v>27200</v>
+      </c>
+      <c r="J89" s="3">
+        <v>6600</v>
+      </c>
+      <c r="K89" s="3">
         <v>-161100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-151200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-295700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-204800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-187900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-211500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-281700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-200200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-94600</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="S89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>16</v>
       </c>
@@ -7202,11 +7635,11 @@
       <c r="V89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W89" s="3">
-        <v>0</v>
-      </c>
-      <c r="X89" s="3">
-        <v>0</v>
+      <c r="W89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Y89" s="3">
         <v>0</v>
@@ -7220,17 +7653,23 @@
       <c r="AB89" s="3">
         <v>0</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AD89" s="3" t="s">
-        <v>16</v>
+      <c r="AC89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD89" s="3">
+        <v>0</v>
       </c>
       <c r="AE89" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG89" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,40 +7701,42 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-13100</v>
+        <v>-4200</v>
       </c>
       <c r="E91" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="F91" s="3">
         <v>-200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-8800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-48100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-66000</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
         <v>0</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M91" s="3" t="s">
-        <v>16</v>
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
+        <v>0</v>
       </c>
       <c r="N91" s="3" t="s">
         <v>16</v>
@@ -7303,11 +7744,11 @@
       <c r="O91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="P91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -7342,17 +7783,23 @@
       <c r="AB91" s="3">
         <v>0</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AD91" s="3" t="s">
-        <v>16</v>
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
+        <v>0</v>
       </c>
       <c r="AE91" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG91" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7887,14 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,59 +7982,65 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-81100</v>
+        <v>-198900</v>
       </c>
       <c r="E94" s="3">
-        <v>23000</v>
+        <v>-7700</v>
       </c>
       <c r="F94" s="3">
-        <v>79900</v>
+        <v>-58500</v>
       </c>
       <c r="G94" s="3">
-        <v>56200</v>
+        <v>23200</v>
       </c>
       <c r="H94" s="3">
-        <v>-90100</v>
+        <v>80500</v>
       </c>
       <c r="I94" s="3">
+        <v>56600</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-90700</v>
+      </c>
+      <c r="K94" s="3">
         <v>-9300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>289600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>268000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>8400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-386700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>39200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>50100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>168600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-252000</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>16</v>
       </c>
@@ -7591,11 +8050,11 @@
       <c r="V94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
-      <c r="X94" s="3">
-        <v>0</v>
+      <c r="W94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Y94" s="3">
         <v>0</v>
@@ -7609,17 +8068,23 @@
       <c r="AB94" s="3">
         <v>0</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AD94" s="3" t="s">
-        <v>16</v>
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3">
+        <v>0</v>
       </c>
       <c r="AE94" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG94" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +8116,10 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7740,8 +8207,14 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8302,14 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8397,14 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,59 +8492,65 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>301200</v>
+        <v>-3100</v>
       </c>
       <c r="E100" s="3">
-        <v>-463500</v>
+        <v>37400</v>
       </c>
       <c r="F100" s="3">
-        <v>395100</v>
+        <v>-163400</v>
       </c>
       <c r="G100" s="3">
-        <v>-14600</v>
+        <v>-466600</v>
       </c>
       <c r="H100" s="3">
-        <v>-46000</v>
+        <v>397800</v>
       </c>
       <c r="I100" s="3">
+        <v>-14700</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-46300</v>
+      </c>
+      <c r="K100" s="3">
         <v>282600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-723400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>123300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>115100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>85000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>1168200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>34800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>121200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-12400</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>16</v>
       </c>
@@ -8069,11 +8560,11 @@
       <c r="V100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3">
-        <v>0</v>
+      <c r="W100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Y100" s="3">
         <v>0</v>
@@ -8087,68 +8578,74 @@
       <c r="AB100" s="3">
         <v>0</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AD100" s="3" t="s">
-        <v>16</v>
+      <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
+        <v>0</v>
       </c>
       <c r="AE100" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG100" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>18900</v>
+        <v>-4400</v>
       </c>
       <c r="E101" s="3">
+        <v>600</v>
+      </c>
+      <c r="F101" s="3">
+        <v>17800</v>
+      </c>
+      <c r="G101" s="3">
         <v>-1200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-1200</v>
       </c>
-      <c r="G101" s="3">
-        <v>8300</v>
-      </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
+        <v>8400</v>
+      </c>
+      <c r="J101" s="3">
         <v>10400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-10200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-3200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-13300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-3900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-4600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-16500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>10100</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="S101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T101" s="3" t="s">
         <v>16</v>
       </c>
@@ -8158,11 +8655,11 @@
       <c r="V101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
-      <c r="X101" s="3">
-        <v>0</v>
+      <c r="W101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Y101" s="3">
         <v>0</v>
@@ -8176,68 +8673,74 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-      <c r="AC101" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AD101" s="3" t="s">
-        <v>16</v>
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
+        <v>0</v>
       </c>
       <c r="AE101" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG101" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>222900</v>
+        <v>-118300</v>
       </c>
       <c r="E102" s="3">
-        <v>-303300</v>
+        <v>145900</v>
       </c>
       <c r="F102" s="3">
-        <v>591700</v>
+        <v>-81000</v>
       </c>
       <c r="G102" s="3">
-        <v>76900</v>
+        <v>-305400</v>
       </c>
       <c r="H102" s="3">
-        <v>-119200</v>
+        <v>595700</v>
       </c>
       <c r="I102" s="3">
+        <v>77400</v>
+      </c>
+      <c r="J102" s="3">
+        <v>-120000</v>
+      </c>
+      <c r="K102" s="3">
         <v>111600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-595300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>92400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-94700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-493500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>991300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-213400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>88300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-348900</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="S102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>16</v>
       </c>
@@ -8247,11 +8750,11 @@
       <c r="V102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W102" s="3">
-        <v>0</v>
-      </c>
-      <c r="X102" s="3">
-        <v>0</v>
+      <c r="W102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Y102" s="3">
         <v>0</v>
@@ -8265,13 +8768,19 @@
       <c r="AB102" s="3">
         <v>0</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AD102" s="3" t="s">
-        <v>16</v>
+      <c r="AC102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="3">
+        <v>0</v>
       </c>
       <c r="AE102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG102" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IQ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IQ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="92">
   <si>
     <t>IQ</t>
   </si>
@@ -656,428 +656,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1071400</v>
+        <v>1095200</v>
       </c>
       <c r="E8" s="3">
-        <v>1114300</v>
+        <v>1064700</v>
       </c>
       <c r="F8" s="3">
-        <v>1084700</v>
+        <v>1107400</v>
       </c>
       <c r="G8" s="3">
-        <v>1160700</v>
+        <v>1078000</v>
       </c>
       <c r="H8" s="3">
-        <v>1055600</v>
+        <v>1153500</v>
       </c>
       <c r="I8" s="3">
-        <v>1038600</v>
+        <v>1049000</v>
       </c>
       <c r="J8" s="3">
+        <v>1032200</v>
+      </c>
+      <c r="K8" s="3">
         <v>925400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1004800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1020200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1078800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1092700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1109200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1038200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1049600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1092200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1197700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1154300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1154000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1086300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1063300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1020600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>967700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>863600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>699800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>691200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>734700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>642100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>477600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>458800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>473800</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>769200</v>
+        <v>778000</v>
       </c>
       <c r="E9" s="3">
-        <v>811800</v>
+        <v>764500</v>
       </c>
       <c r="F9" s="3">
-        <v>802700</v>
+        <v>806800</v>
       </c>
       <c r="G9" s="3">
-        <v>828000</v>
+        <v>797700</v>
       </c>
       <c r="H9" s="3">
-        <v>751000</v>
+        <v>822900</v>
       </c>
       <c r="I9" s="3">
-        <v>793100</v>
+        <v>746400</v>
       </c>
       <c r="J9" s="3">
+        <v>788200</v>
+      </c>
+      <c r="K9" s="3">
         <v>729600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>823500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>898600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>999000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>986500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>989600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>944400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>929300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1007000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1237300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1218700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1275500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1066600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1107000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1237800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1071400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>854700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>695600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>650700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>726900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1304500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1035100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>453900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>456800</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>302100</v>
+        <v>317200</v>
       </c>
       <c r="E10" s="3">
-        <v>302400</v>
+        <v>300300</v>
       </c>
       <c r="F10" s="3">
-        <v>282000</v>
+        <v>300600</v>
       </c>
       <c r="G10" s="3">
-        <v>332600</v>
+        <v>280200</v>
       </c>
       <c r="H10" s="3">
-        <v>304500</v>
+        <v>330600</v>
       </c>
       <c r="I10" s="3">
-        <v>245500</v>
+        <v>302700</v>
       </c>
       <c r="J10" s="3">
+        <v>244000</v>
+      </c>
+      <c r="K10" s="3">
         <v>195800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>181300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>121700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>79800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>106200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>119600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>93800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>120400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>85200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-39600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-64300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>-121500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>19700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>-43700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>-217200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>-103700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>8900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>4200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>40500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>7800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>-662500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>-557500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>4900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1111,103 +1124,107 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>62800</v>
+        <v>59300</v>
       </c>
       <c r="E12" s="3">
-        <v>62200</v>
+        <v>62400</v>
       </c>
       <c r="F12" s="3">
-        <v>61000</v>
+        <v>61800</v>
       </c>
       <c r="G12" s="3">
-        <v>59500</v>
+        <v>60700</v>
       </c>
       <c r="H12" s="3">
-        <v>64800</v>
+        <v>59200</v>
       </c>
       <c r="I12" s="3">
-        <v>66200</v>
+        <v>64400</v>
       </c>
       <c r="J12" s="3">
+        <v>65700</v>
+      </c>
+      <c r="K12" s="3">
         <v>67000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>65600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>105400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>97100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>97200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>93600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>92300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>97800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>97900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>106200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>109500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>109700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>100000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>91000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>88200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>78100</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>61800</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>55600</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>52300</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>50800</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>87400</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>78200</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>35500</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>33400</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1301,8 +1318,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1396,8 +1416,11 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1491,8 +1514,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,198 +1549,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>963800</v>
+        <v>964700</v>
       </c>
       <c r="E17" s="3">
-        <v>1010400</v>
+        <v>957800</v>
       </c>
       <c r="F17" s="3">
-        <v>999800</v>
+        <v>1004200</v>
       </c>
       <c r="G17" s="3">
-        <v>1041300</v>
+        <v>993600</v>
       </c>
       <c r="H17" s="3">
-        <v>946600</v>
+        <v>1034800</v>
       </c>
       <c r="I17" s="3">
-        <v>995600</v>
+        <v>940800</v>
       </c>
       <c r="J17" s="3">
+        <v>989400</v>
+      </c>
+      <c r="K17" s="3">
         <v>907900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>991900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1154900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1273200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1253800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1250400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1220200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1226300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1281000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1548600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1543700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1595700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1372300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1371500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1503400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1330400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1049400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>852200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>814000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>893000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>789100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>628800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>569700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>557900</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>107600</v>
+        <v>130500</v>
       </c>
       <c r="E18" s="3">
-        <v>103800</v>
+        <v>106900</v>
       </c>
       <c r="F18" s="3">
-        <v>84900</v>
+        <v>103200</v>
       </c>
       <c r="G18" s="3">
-        <v>119400</v>
+        <v>84300</v>
       </c>
       <c r="H18" s="3">
-        <v>108900</v>
+        <v>118600</v>
       </c>
       <c r="I18" s="3">
-        <v>43100</v>
+        <v>108300</v>
       </c>
       <c r="J18" s="3">
+        <v>42800</v>
+      </c>
+      <c r="K18" s="3">
         <v>17500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>12900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-134700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-194500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-161100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-141200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-182000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-176600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-188900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-351000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-389400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-441800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-286000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-308200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-482800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-362700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-185900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-152400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-122800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-158300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-147000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-151200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-110900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-84100</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1748,103 +1781,107 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E20" s="3">
         <v>3400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>6100</v>
       </c>
-      <c r="G20" s="3">
-        <v>10800</v>
-      </c>
       <c r="H20" s="3">
-        <v>-43700</v>
+        <v>10700</v>
       </c>
       <c r="I20" s="3">
-        <v>-66800</v>
+        <v>-43500</v>
       </c>
       <c r="J20" s="3">
+        <v>-66400</v>
+      </c>
+      <c r="K20" s="3">
         <v>-15200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>37700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-59200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>16800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>15100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>3900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>49100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>18400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-57400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>54200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-89300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-27300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>52700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>3800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-73300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-106200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>96800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>39800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>2300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>17900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-20200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
@@ -1920,296 +1957,305 @@
       <c r="AA21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AB21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC21" s="3">
         <v>1174600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>835600</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AF21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG21" s="3">
         <v>598900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>443800</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>39300</v>
+      </c>
+      <c r="F22" s="3">
+        <v>38900</v>
+      </c>
+      <c r="G22" s="3">
+        <v>38500</v>
+      </c>
+      <c r="H22" s="3">
         <v>39500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="I22" s="3">
+        <v>24300</v>
+      </c>
+      <c r="J22" s="3">
+        <v>25100</v>
+      </c>
+      <c r="K22" s="3">
+        <v>25300</v>
+      </c>
+      <c r="L22" s="3">
+        <v>24200</v>
+      </c>
+      <c r="M22" s="3">
+        <v>44800</v>
+      </c>
+      <c r="N22" s="3">
+        <v>49900</v>
+      </c>
+      <c r="O22" s="3">
+        <v>49300</v>
+      </c>
+      <c r="P22" s="3">
+        <v>46000</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>37500</v>
+      </c>
+      <c r="R22" s="3">
+        <v>39300</v>
+      </c>
+      <c r="S22" s="3">
         <v>39100</v>
       </c>
-      <c r="F22" s="3">
-        <v>38700</v>
-      </c>
-      <c r="G22" s="3">
-        <v>39800</v>
-      </c>
-      <c r="H22" s="3">
-        <v>24500</v>
-      </c>
-      <c r="I22" s="3">
-        <v>25300</v>
-      </c>
-      <c r="J22" s="3">
-        <v>25300</v>
-      </c>
-      <c r="K22" s="3">
-        <v>24200</v>
-      </c>
-      <c r="L22" s="3">
-        <v>44800</v>
-      </c>
-      <c r="M22" s="3">
-        <v>49900</v>
-      </c>
-      <c r="N22" s="3">
-        <v>49300</v>
-      </c>
-      <c r="O22" s="3">
-        <v>46000</v>
-      </c>
-      <c r="P22" s="3">
-        <v>37500</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>39300</v>
-      </c>
-      <c r="R22" s="3">
-        <v>39100</v>
-      </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>41000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>42600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>39700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>37900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>20600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>8900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>2200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>1300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>1200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>6300</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AD22" s="3">
+      <c r="AD22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AE22" s="3">
         <v>12200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>9900</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>6100</v>
       </c>
-      <c r="AG22" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>71400</v>
+        <v>94400</v>
       </c>
       <c r="E23" s="3">
-        <v>68500</v>
+        <v>71000</v>
       </c>
       <c r="F23" s="3">
-        <v>52200</v>
+        <v>68000</v>
       </c>
       <c r="G23" s="3">
-        <v>90400</v>
+        <v>51900</v>
       </c>
       <c r="H23" s="3">
-        <v>40700</v>
+        <v>89900</v>
       </c>
       <c r="I23" s="3">
-        <v>-49000</v>
+        <v>40500</v>
       </c>
       <c r="J23" s="3">
+        <v>-48700</v>
+      </c>
+      <c r="K23" s="3">
         <v>-23000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>26300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-238700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-241400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-193600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-172100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-215500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-166900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-209600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-449400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-377800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-570700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-351100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-276100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-487900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-438200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-293400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-56900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-89300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-156000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-141400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-162700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-137200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-91300</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E24" s="3">
         <v>5300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G24" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H24" s="3">
+        <v>3400</v>
+      </c>
+      <c r="I24" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="J24" s="3">
+        <v>5900</v>
+      </c>
+      <c r="K24" s="3">
+        <v>5000</v>
+      </c>
+      <c r="L24" s="3">
+        <v>2300</v>
+      </c>
+      <c r="M24" s="3">
+        <v>5000</v>
+      </c>
+      <c r="N24" s="3">
         <v>1300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="O24" s="3">
+        <v>4400</v>
+      </c>
+      <c r="P24" s="3">
+        <v>2900</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="R24" s="3">
+        <v>2800</v>
+      </c>
+      <c r="S24" s="3">
+        <v>2300</v>
+      </c>
+      <c r="T24" s="3">
+        <v>800</v>
+      </c>
+      <c r="U24" s="3">
+        <v>3500</v>
+      </c>
+      <c r="V24" s="3">
+        <v>2500</v>
+      </c>
+      <c r="W24" s="3">
+        <v>900</v>
+      </c>
+      <c r="X24" s="3">
         <v>1100</v>
       </c>
-      <c r="G24" s="3">
-        <v>3400</v>
-      </c>
-      <c r="H24" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="I24" s="3">
-        <v>5900</v>
-      </c>
-      <c r="J24" s="3">
-        <v>5000</v>
-      </c>
-      <c r="K24" s="3">
-        <v>2300</v>
-      </c>
-      <c r="L24" s="3">
-        <v>5000</v>
-      </c>
-      <c r="M24" s="3">
-        <v>1300</v>
-      </c>
-      <c r="N24" s="3">
-        <v>4400</v>
-      </c>
-      <c r="O24" s="3">
-        <v>2900</v>
-      </c>
-      <c r="P24" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>2800</v>
-      </c>
-      <c r="R24" s="3">
-        <v>2300</v>
-      </c>
-      <c r="S24" s="3">
-        <v>800</v>
-      </c>
-      <c r="T24" s="3">
-        <v>3500</v>
-      </c>
-      <c r="U24" s="3">
-        <v>2500</v>
-      </c>
-      <c r="V24" s="3">
-        <v>900</v>
-      </c>
-      <c r="W24" s="3">
-        <v>1100</v>
-      </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>11500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-1400</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>100</v>
       </c>
       <c r="AD24" s="3">
         <v>100</v>
@@ -2218,13 +2264,16 @@
         <v>100</v>
       </c>
       <c r="AF24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG24" s="3">
         <v>600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>66100</v>
+        <v>92000</v>
       </c>
       <c r="E26" s="3">
-        <v>67200</v>
+        <v>65700</v>
       </c>
       <c r="F26" s="3">
-        <v>51100</v>
+        <v>66800</v>
       </c>
       <c r="G26" s="3">
-        <v>87000</v>
+        <v>50800</v>
       </c>
       <c r="H26" s="3">
-        <v>42400</v>
+        <v>86500</v>
       </c>
       <c r="I26" s="3">
-        <v>-54900</v>
+        <v>42100</v>
       </c>
       <c r="J26" s="3">
+        <v>-54600</v>
+      </c>
+      <c r="K26" s="3">
         <v>-28000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>24000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-243700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-242700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-198000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-175000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-213300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-169600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-212000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-450100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-381200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-573200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-352000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-277200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-499400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-437300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-294100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-56900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-87900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-156100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-141500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-162800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-137800</v>
       </c>
-      <c r="AG26" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH26" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>64800</v>
+        <v>90500</v>
       </c>
       <c r="E27" s="3">
-        <v>66200</v>
+        <v>64400</v>
       </c>
       <c r="F27" s="3">
-        <v>50800</v>
+        <v>65800</v>
       </c>
       <c r="G27" s="3">
-        <v>85900</v>
+        <v>50500</v>
       </c>
       <c r="H27" s="3">
-        <v>42300</v>
+        <v>85400</v>
       </c>
       <c r="I27" s="3">
-        <v>-55000</v>
+        <v>42000</v>
       </c>
       <c r="J27" s="3">
+        <v>-54700</v>
+      </c>
+      <c r="K27" s="3">
         <v>-29700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>23300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-246300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-246500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-201300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-176800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-215700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-171700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-212700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-450300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-384200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-575400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-355600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-275900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-504900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-439500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-294800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-98300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2198300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1737000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-248500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-267600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-410200</v>
       </c>
-      <c r="AG27" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH27" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2698,8 +2759,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,198 +2955,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-6100</v>
       </c>
-      <c r="G32" s="3">
-        <v>-10800</v>
-      </c>
       <c r="H32" s="3">
-        <v>43700</v>
+        <v>-10700</v>
       </c>
       <c r="I32" s="3">
-        <v>66800</v>
+        <v>43500</v>
       </c>
       <c r="J32" s="3">
+        <v>66400</v>
+      </c>
+      <c r="K32" s="3">
         <v>15200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-37700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>59200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-16800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-15100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-49100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-18400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>57400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-54200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>89300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>27300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-52700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-3800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>73300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>106200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-96800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-39800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-2300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-17900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>1600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>20200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>64800</v>
+        <v>90500</v>
       </c>
       <c r="E33" s="3">
-        <v>66200</v>
+        <v>64400</v>
       </c>
       <c r="F33" s="3">
-        <v>50800</v>
+        <v>65800</v>
       </c>
       <c r="G33" s="3">
-        <v>85900</v>
+        <v>50500</v>
       </c>
       <c r="H33" s="3">
-        <v>42300</v>
+        <v>85400</v>
       </c>
       <c r="I33" s="3">
-        <v>-55000</v>
+        <v>42000</v>
       </c>
       <c r="J33" s="3">
+        <v>-54700</v>
+      </c>
+      <c r="K33" s="3">
         <v>-29700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>23300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-246300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-246500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-201300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-176800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-215700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-171700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-212700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-450300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-384200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-575400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-355600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-275900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-504900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-439500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-294800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-98300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2198300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1737000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-248500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-267600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-410200</v>
       </c>
-      <c r="AG33" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH33" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>64800</v>
+        <v>90500</v>
       </c>
       <c r="E35" s="3">
-        <v>66200</v>
+        <v>64400</v>
       </c>
       <c r="F35" s="3">
-        <v>50800</v>
+        <v>65800</v>
       </c>
       <c r="G35" s="3">
-        <v>85900</v>
+        <v>50500</v>
       </c>
       <c r="H35" s="3">
-        <v>42300</v>
+        <v>85400</v>
       </c>
       <c r="I35" s="3">
-        <v>-55000</v>
+        <v>42000</v>
       </c>
       <c r="J35" s="3">
+        <v>-54700</v>
+      </c>
+      <c r="K35" s="3">
         <v>-29700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>23300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-246300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-246500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-201300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-176800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-215700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-171700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-212700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-450300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-384200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-575400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-355600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-275900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-504900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-439500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-294800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-98300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2198300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1737000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-248500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-267600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-410200</v>
       </c>
-      <c r="AG35" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH35" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,92 +3524,93 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>616500</v>
+        <v>697100</v>
       </c>
       <c r="E41" s="3">
-        <v>588100</v>
+        <v>612700</v>
       </c>
       <c r="F41" s="3">
-        <v>495600</v>
+        <v>584500</v>
       </c>
       <c r="G41" s="3">
-        <v>629700</v>
+        <v>492600</v>
       </c>
       <c r="H41" s="3">
-        <v>986800</v>
+        <v>625800</v>
       </c>
       <c r="I41" s="3">
-        <v>494900</v>
+        <v>980700</v>
       </c>
       <c r="J41" s="3">
+        <v>491800</v>
+      </c>
+      <c r="K41" s="3">
         <v>406400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>526300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>413900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1037100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>960100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1023500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1519400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>461900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>630800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>578200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>913800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>702900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>829200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1806300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>666100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>816200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1159100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>57900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>105200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>176500</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE41" s="3" t="s">
         <v>16</v>
       </c>
@@ -3533,92 +3620,95 @@
       <c r="AG41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>130900</v>
+        <v>136200</v>
       </c>
       <c r="E42" s="3">
-        <v>142500</v>
+        <v>130100</v>
       </c>
       <c r="F42" s="3">
-        <v>141100</v>
+        <v>141600</v>
       </c>
       <c r="G42" s="3">
-        <v>93000</v>
+        <v>140200</v>
       </c>
       <c r="H42" s="3">
-        <v>113800</v>
+        <v>92400</v>
       </c>
       <c r="I42" s="3">
-        <v>204400</v>
+        <v>113100</v>
       </c>
       <c r="J42" s="3">
+        <v>203200</v>
+      </c>
+      <c r="K42" s="3">
         <v>262800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>177100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>186200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>520500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>793700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>823300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>467500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>526300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>618400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>823300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>705100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1067400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1347200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>591100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>880400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>538000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>665100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>70700</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>111900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>497500</v>
       </c>
-      <c r="AD42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE42" s="3" t="s">
         <v>16</v>
       </c>
@@ -3628,92 +3718,95 @@
       <c r="AG42" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>538900</v>
+        <v>614000</v>
       </c>
       <c r="E43" s="3">
-        <v>372000</v>
+        <v>535500</v>
       </c>
       <c r="F43" s="3">
-        <v>396500</v>
+        <v>369700</v>
       </c>
       <c r="G43" s="3">
-        <v>402400</v>
+        <v>394000</v>
       </c>
       <c r="H43" s="3">
-        <v>348500</v>
+        <v>399900</v>
       </c>
       <c r="I43" s="3">
-        <v>382800</v>
+        <v>346300</v>
       </c>
       <c r="J43" s="3">
+        <v>380500</v>
+      </c>
+      <c r="K43" s="3">
         <v>359000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>388200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>400900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>448800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>478900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>494800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>478900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>500900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>503700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>717100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>591200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>514100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>513100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>535000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>460500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>452200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>350200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>420800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>322200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>693700</v>
       </c>
-      <c r="AD43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE43" s="3" t="s">
         <v>16</v>
       </c>
@@ -3723,92 +3816,95 @@
       <c r="AG43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>81000</v>
+        <v>100100</v>
       </c>
       <c r="E44" s="3">
-        <v>96900</v>
+        <v>80500</v>
       </c>
       <c r="F44" s="3">
-        <v>115700</v>
+        <v>96300</v>
       </c>
       <c r="G44" s="3">
-        <v>130700</v>
+        <v>115000</v>
       </c>
       <c r="H44" s="3">
-        <v>103700</v>
+        <v>129900</v>
       </c>
       <c r="I44" s="3">
-        <v>113700</v>
+        <v>103100</v>
       </c>
       <c r="J44" s="3">
+        <v>113000</v>
+      </c>
+      <c r="K44" s="3">
         <v>110700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>125700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>128600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>155900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>127900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>143600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>144100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>182200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>174500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>224300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>188600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>206500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>179700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>191900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>169000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>147200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>162900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>172400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>117500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>110300</v>
       </c>
-      <c r="AD44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE44" s="3" t="s">
         <v>16</v>
       </c>
@@ -3818,92 +3914,95 @@
       <c r="AG44" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>389300</v>
+        <v>359500</v>
       </c>
       <c r="E45" s="3">
-        <v>411400</v>
+        <v>386900</v>
       </c>
       <c r="F45" s="3">
-        <v>371300</v>
+        <v>408900</v>
       </c>
       <c r="G45" s="3">
-        <v>1560800</v>
+        <v>369000</v>
       </c>
       <c r="H45" s="3">
-        <v>363800</v>
+        <v>1551100</v>
       </c>
       <c r="I45" s="3">
-        <v>312000</v>
+        <v>361500</v>
       </c>
       <c r="J45" s="3">
+        <v>310100</v>
+      </c>
+      <c r="K45" s="3">
         <v>308700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>381200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>461800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>540900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>588900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>597800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>492900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>601500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>679700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>690600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>722800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1031300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>926000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>772700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>707300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>430500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>377800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>145500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>161200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>137200</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE45" s="3" t="s">
         <v>16</v>
       </c>
@@ -3913,92 +4012,95 @@
       <c r="AG45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1756500</v>
+        <v>1906900</v>
       </c>
       <c r="E46" s="3">
-        <v>1611000</v>
+        <v>1745700</v>
       </c>
       <c r="F46" s="3">
-        <v>1520200</v>
+        <v>1601000</v>
       </c>
       <c r="G46" s="3">
-        <v>2816600</v>
+        <v>1510800</v>
       </c>
       <c r="H46" s="3">
-        <v>1916500</v>
+        <v>2799100</v>
       </c>
       <c r="I46" s="3">
-        <v>1507900</v>
+        <v>1904600</v>
       </c>
       <c r="J46" s="3">
+        <v>1498600</v>
+      </c>
+      <c r="K46" s="3">
         <v>1447600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1598500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1591300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2703300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2949500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3083100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3102800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2272700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2607100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3033400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3121600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3522200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3795200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3897100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2883300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2384200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2715100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>867300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>817900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1615200</v>
       </c>
-      <c r="AD46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE46" s="3" t="s">
         <v>16</v>
       </c>
@@ -4008,92 +4110,95 @@
       <c r="AG46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>336300</v>
+        <v>339500</v>
       </c>
       <c r="E47" s="3">
-        <v>349400</v>
+        <v>334300</v>
       </c>
       <c r="F47" s="3">
-        <v>352400</v>
+        <v>347200</v>
       </c>
       <c r="G47" s="3">
-        <v>322600</v>
+        <v>350200</v>
       </c>
       <c r="H47" s="3">
-        <v>349400</v>
+        <v>320600</v>
       </c>
       <c r="I47" s="3">
-        <v>405600</v>
+        <v>347300</v>
       </c>
       <c r="J47" s="3">
+        <v>403100</v>
+      </c>
+      <c r="K47" s="3">
         <v>448400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>452500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>430300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>499900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>503200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>485900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>451300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>577200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>579900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>580200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>485700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>480400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>413700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>400600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>381200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>322800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>173900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>170000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>81500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>59000</v>
       </c>
-      <c r="AD47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE47" s="3" t="s">
         <v>16</v>
       </c>
@@ -4103,92 +4208,95 @@
       <c r="AG47" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>215200</v>
+        <v>208100</v>
       </c>
       <c r="E48" s="3">
-        <v>214700</v>
+        <v>213800</v>
       </c>
       <c r="F48" s="3">
-        <v>224700</v>
+        <v>213400</v>
       </c>
       <c r="G48" s="3">
+        <v>223300</v>
+      </c>
+      <c r="H48" s="3">
+        <v>233500</v>
+      </c>
+      <c r="I48" s="3">
+        <v>245700</v>
+      </c>
+      <c r="J48" s="3">
+        <v>260400</v>
+      </c>
+      <c r="K48" s="3">
+        <v>292000</v>
+      </c>
+      <c r="L48" s="3">
+        <v>302900</v>
+      </c>
+      <c r="M48" s="3">
+        <v>311000</v>
+      </c>
+      <c r="N48" s="3">
+        <v>320700</v>
+      </c>
+      <c r="O48" s="3">
+        <v>345200</v>
+      </c>
+      <c r="P48" s="3">
+        <v>323500</v>
+      </c>
+      <c r="Q48" s="3">
+        <v>333400</v>
+      </c>
+      <c r="R48" s="3">
+        <v>360000</v>
+      </c>
+      <c r="S48" s="3">
+        <v>408400</v>
+      </c>
+      <c r="T48" s="3">
+        <v>402000</v>
+      </c>
+      <c r="U48" s="3">
+        <v>381400</v>
+      </c>
+      <c r="V48" s="3">
+        <v>369600</v>
+      </c>
+      <c r="W48" s="3">
+        <v>358100</v>
+      </c>
+      <c r="X48" s="3">
+        <v>265700</v>
+      </c>
+      <c r="Y48" s="3">
         <v>235000</v>
       </c>
-      <c r="H48" s="3">
-        <v>247300</v>
-      </c>
-      <c r="I48" s="3">
-        <v>262000</v>
-      </c>
-      <c r="J48" s="3">
-        <v>292000</v>
-      </c>
-      <c r="K48" s="3">
-        <v>302900</v>
-      </c>
-      <c r="L48" s="3">
-        <v>311000</v>
-      </c>
-      <c r="M48" s="3">
-        <v>320700</v>
-      </c>
-      <c r="N48" s="3">
-        <v>345200</v>
-      </c>
-      <c r="O48" s="3">
-        <v>323500</v>
-      </c>
-      <c r="P48" s="3">
-        <v>333400</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>360000</v>
-      </c>
-      <c r="R48" s="3">
-        <v>408400</v>
-      </c>
-      <c r="S48" s="3">
-        <v>402000</v>
-      </c>
-      <c r="T48" s="3">
-        <v>381400</v>
-      </c>
-      <c r="U48" s="3">
-        <v>369600</v>
-      </c>
-      <c r="V48" s="3">
-        <v>358100</v>
-      </c>
-      <c r="W48" s="3">
-        <v>265700</v>
-      </c>
-      <c r="X48" s="3">
-        <v>235000</v>
-      </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>206500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>196600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>189200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>179200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>179600</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE48" s="3" t="s">
         <v>16</v>
       </c>
@@ -4198,92 +4306,95 @@
       <c r="AG48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>3402400</v>
+        <v>3410900</v>
       </c>
       <c r="E49" s="3">
-        <v>3312600</v>
+        <v>3381300</v>
       </c>
       <c r="F49" s="3">
-        <v>3252800</v>
+        <v>3292100</v>
       </c>
       <c r="G49" s="3">
-        <v>3273200</v>
+        <v>3232600</v>
       </c>
       <c r="H49" s="3">
-        <v>3351100</v>
+        <v>3253000</v>
       </c>
       <c r="I49" s="3">
-        <v>3365100</v>
+        <v>3330400</v>
       </c>
       <c r="J49" s="3">
+        <v>3344300</v>
+      </c>
+      <c r="K49" s="3">
         <v>3291500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3244400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3126500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3033800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2854200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2546200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2436900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2355300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2174600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2369400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2362800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2601800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2423100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2432100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2315500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>2285000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1858100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1623800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1409900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1221500</v>
       </c>
-      <c r="AD49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE49" s="3" t="s">
         <v>16</v>
       </c>
@@ -4293,8 +4404,11 @@
       <c r="AG49" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,92 +4600,95 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>489100</v>
+        <v>531300</v>
       </c>
       <c r="E52" s="3">
-        <v>643900</v>
+        <v>486100</v>
       </c>
       <c r="F52" s="3">
-        <v>640200</v>
+        <v>639900</v>
       </c>
       <c r="G52" s="3">
-        <v>586300</v>
+        <v>636200</v>
       </c>
       <c r="H52" s="3">
-        <v>537300</v>
+        <v>582600</v>
       </c>
       <c r="I52" s="3">
-        <v>422200</v>
+        <v>534000</v>
       </c>
       <c r="J52" s="3">
+        <v>419600</v>
+      </c>
+      <c r="K52" s="3">
         <v>441300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>420100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>405500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>449900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>373200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>380400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>382900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>405700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>460100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>431800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>545600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>562800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>686200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>787200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>685500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>570200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>530500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>439700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>409900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>378500</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE52" s="3" t="s">
         <v>16</v>
       </c>
@@ -4578,8 +4698,11 @@
       <c r="AG52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,92 +4796,95 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>6199500</v>
+        <v>6396800</v>
       </c>
       <c r="E54" s="3">
-        <v>6131600</v>
+        <v>6161200</v>
       </c>
       <c r="F54" s="3">
-        <v>5990200</v>
+        <v>6093600</v>
       </c>
       <c r="G54" s="3">
-        <v>7233600</v>
+        <v>5953200</v>
       </c>
       <c r="H54" s="3">
-        <v>6401600</v>
+        <v>7188800</v>
       </c>
       <c r="I54" s="3">
-        <v>5962900</v>
+        <v>6362000</v>
       </c>
       <c r="J54" s="3">
+        <v>5926000</v>
+      </c>
+      <c r="K54" s="3">
         <v>5920800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6018500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5864600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7007500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7025300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6819100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6707400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5970900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6230000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6816800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6897200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>7536800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7676300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>7782700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6500500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>5768700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>5474100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>3289900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2898400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>3453700</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE54" s="3" t="s">
         <v>16</v>
       </c>
@@ -4768,8 +4894,11 @@
       <c r="AG54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,92 +4968,93 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>788400</v>
+        <v>814800</v>
       </c>
       <c r="E57" s="3">
-        <v>825200</v>
+        <v>783500</v>
       </c>
       <c r="F57" s="3">
-        <v>798000</v>
+        <v>820100</v>
       </c>
       <c r="G57" s="3">
-        <v>795400</v>
+        <v>793000</v>
       </c>
       <c r="H57" s="3">
-        <v>833200</v>
+        <v>790500</v>
       </c>
       <c r="I57" s="3">
-        <v>956800</v>
+        <v>828100</v>
       </c>
       <c r="J57" s="3">
+        <v>950800</v>
+      </c>
+      <c r="K57" s="3">
         <v>877400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>969600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1228400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1297500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1181700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1045200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1052600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1088800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1133500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1304000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1264600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1574100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1464200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1574600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1475900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1458800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1269100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1252000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1010300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1035600</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE57" s="3" t="s">
         <v>16</v>
       </c>
@@ -4933,92 +5064,95 @@
       <c r="AG57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>886100</v>
+        <v>883900</v>
       </c>
       <c r="E58" s="3">
-        <v>900200</v>
+        <v>880600</v>
       </c>
       <c r="F58" s="3">
-        <v>419200</v>
+        <v>894600</v>
       </c>
       <c r="G58" s="3">
-        <v>1602500</v>
+        <v>416600</v>
       </c>
       <c r="H58" s="3">
-        <v>1620000</v>
+        <v>1592600</v>
       </c>
       <c r="I58" s="3">
-        <v>1732100</v>
+        <v>1610000</v>
       </c>
       <c r="J58" s="3">
+        <v>1721400</v>
+      </c>
+      <c r="K58" s="3">
         <v>1678900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>606400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>568600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1344000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1249600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1102100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1200900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>662600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>601300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>519500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>516600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>604300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>667800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>557600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>454600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>165500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>89900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>58400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>44400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1232000</v>
       </c>
-      <c r="AD58" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE58" s="3" t="s">
         <v>16</v>
       </c>
@@ -5028,92 +5162,95 @@
       <c r="AG58" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1431400</v>
+        <v>1478200</v>
       </c>
       <c r="E59" s="3">
-        <v>1415900</v>
+        <v>1422500</v>
       </c>
       <c r="F59" s="3">
-        <v>1387800</v>
+        <v>1407200</v>
       </c>
       <c r="G59" s="3">
-        <v>1449700</v>
+        <v>1379200</v>
       </c>
       <c r="H59" s="3">
-        <v>1457400</v>
+        <v>1440700</v>
       </c>
       <c r="I59" s="3">
-        <v>1363500</v>
+        <v>1448400</v>
       </c>
       <c r="J59" s="3">
+        <v>1355000</v>
+      </c>
+      <c r="K59" s="3">
         <v>1358100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1389900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1306500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1331100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1335500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1355800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1206300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1242700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1281200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1445100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1325100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1178200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1144200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1013800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>946900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>887200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>710200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>619500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>613400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1325600</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE59" s="3" t="s">
         <v>16</v>
       </c>
@@ -5123,92 +5260,95 @@
       <c r="AG59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>3105900</v>
+        <v>3176900</v>
       </c>
       <c r="E60" s="3">
-        <v>3141300</v>
+        <v>3086700</v>
       </c>
       <c r="F60" s="3">
-        <v>2604900</v>
+        <v>3121900</v>
       </c>
       <c r="G60" s="3">
-        <v>3847600</v>
+        <v>2588800</v>
       </c>
       <c r="H60" s="3">
-        <v>3910600</v>
+        <v>3823800</v>
       </c>
       <c r="I60" s="3">
-        <v>4052400</v>
+        <v>3886400</v>
       </c>
       <c r="J60" s="3">
+        <v>4027300</v>
+      </c>
+      <c r="K60" s="3">
         <v>3914400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2965900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3103600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3972600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3766800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3503200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3459800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2994100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3016000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3268600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3106300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3356700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3276200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3146000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2877300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2511500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2069200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1929900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1668000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3593200</v>
       </c>
-      <c r="AD60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE60" s="3" t="s">
         <v>16</v>
       </c>
@@ -5218,92 +5358,95 @@
       <c r="AG60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1145800</v>
+        <v>1199800</v>
       </c>
       <c r="E61" s="3">
-        <v>1160700</v>
+        <v>1138700</v>
       </c>
       <c r="F61" s="3">
-        <v>1591300</v>
+        <v>1153500</v>
       </c>
       <c r="G61" s="3">
-        <v>1622100</v>
+        <v>1581500</v>
       </c>
       <c r="H61" s="3">
-        <v>1330200</v>
+        <v>1612100</v>
       </c>
       <c r="I61" s="3">
-        <v>885600</v>
+        <v>1322000</v>
       </c>
       <c r="J61" s="3">
+        <v>880100</v>
+      </c>
+      <c r="K61" s="3">
         <v>832800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1828100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1747000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1801200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1808500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1763700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1660200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1889000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2001200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2112200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2029000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2057800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1879700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1856600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>777900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>38300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>39000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>40000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>40700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>42100</v>
       </c>
-      <c r="AD61" s="3">
-        <v>0</v>
-      </c>
       <c r="AE61" s="3">
         <v>0</v>
       </c>
@@ -5313,92 +5456,95 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>253800</v>
+        <v>255800</v>
       </c>
       <c r="E62" s="3">
-        <v>252200</v>
+        <v>252300</v>
       </c>
       <c r="F62" s="3">
-        <v>300700</v>
+        <v>250600</v>
       </c>
       <c r="G62" s="3">
-        <v>283100</v>
+        <v>298800</v>
       </c>
       <c r="H62" s="3">
-        <v>279000</v>
+        <v>281300</v>
       </c>
       <c r="I62" s="3">
-        <v>267200</v>
+        <v>277200</v>
       </c>
       <c r="J62" s="3">
+        <v>265600</v>
+      </c>
+      <c r="K62" s="3">
         <v>288800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>271600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>230700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>232500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>253100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>258600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>272800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>288000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>290300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>281500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>266000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>220700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>225900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>248700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>208500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>210000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>97000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>96100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1100</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE62" s="3" t="s">
         <v>16</v>
       </c>
@@ -5408,8 +5554,11 @@
       <c r="AG62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,92 +5848,95 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>4519200</v>
+        <v>4640300</v>
       </c>
       <c r="E66" s="3">
-        <v>4566700</v>
+        <v>4491300</v>
       </c>
       <c r="F66" s="3">
-        <v>4508400</v>
+        <v>4538500</v>
       </c>
       <c r="G66" s="3">
-        <v>5764300</v>
+        <v>4480500</v>
       </c>
       <c r="H66" s="3">
-        <v>5532700</v>
+        <v>5728600</v>
       </c>
       <c r="I66" s="3">
-        <v>5218300</v>
+        <v>5498500</v>
       </c>
       <c r="J66" s="3">
+        <v>5186000</v>
+      </c>
+      <c r="K66" s="3">
         <v>5048800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5075000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5148300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6071100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5873200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5566700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5418900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5194800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5329500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5684500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5423400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5659900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5402400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5268100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3880900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2771200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2205600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2066400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1710600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3636400</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE66" s="3" t="s">
         <v>16</v>
       </c>
@@ -5788,8 +5946,11 @@
       <c r="AG66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6088,17 +6256,17 @@
         <v>0</v>
       </c>
       <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="3">
         <v>3284400</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AC70" s="3">
         <v>3242900</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AD70" s="3">
         <v>4323600</v>
       </c>
-      <c r="AD70" s="3">
-        <v>0</v>
-      </c>
       <c r="AE70" s="3">
         <v>0</v>
       </c>
@@ -6108,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,92 +6374,95 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-6196600</v>
+        <v>-6067700</v>
       </c>
       <c r="E72" s="3">
-        <v>-6261400</v>
+        <v>-6158300</v>
       </c>
       <c r="F72" s="3">
-        <v>-6327600</v>
+        <v>-6222700</v>
       </c>
       <c r="G72" s="3">
-        <v>-6378300</v>
+        <v>-6288400</v>
       </c>
       <c r="H72" s="3">
-        <v>-6464300</v>
+        <v>-6338900</v>
       </c>
       <c r="I72" s="3">
-        <v>-6506600</v>
+        <v>-6424300</v>
       </c>
       <c r="J72" s="3">
+        <v>-6466300</v>
+      </c>
+      <c r="K72" s="3">
         <v>-6451600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-6378400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-6512400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-6450800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-6268400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-5880400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-5703600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-5757100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-5636300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-5750400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-5209800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-4889200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-4224500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-3852200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-3414300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-2796700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-2357100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-2130900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-2154600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-4631600</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE72" s="3" t="s">
         <v>16</v>
       </c>
@@ -6298,8 +6472,11 @@
       <c r="AG72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,92 +6766,95 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1680300</v>
+        <v>1756500</v>
       </c>
       <c r="E76" s="3">
-        <v>1564800</v>
+        <v>1669900</v>
       </c>
       <c r="F76" s="3">
-        <v>1481800</v>
+        <v>1555100</v>
       </c>
       <c r="G76" s="3">
-        <v>1469300</v>
+        <v>1472700</v>
       </c>
       <c r="H76" s="3">
-        <v>869000</v>
+        <v>1460200</v>
       </c>
       <c r="I76" s="3">
-        <v>744600</v>
+        <v>863600</v>
       </c>
       <c r="J76" s="3">
+        <v>740000</v>
+      </c>
+      <c r="K76" s="3">
         <v>872000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>943500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>716300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>936400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1152200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1252400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1288500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>776100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>900500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1132300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1473700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1876900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2273900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2514600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2619500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2997500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3268500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-2060900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-2055000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-4506300</v>
       </c>
-      <c r="AD76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE76" s="3" t="s">
         <v>16</v>
       </c>
@@ -6678,8 +6864,11 @@
       <c r="AG76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>64800</v>
+        <v>90500</v>
       </c>
       <c r="E81" s="3">
-        <v>66200</v>
+        <v>64400</v>
       </c>
       <c r="F81" s="3">
-        <v>50800</v>
+        <v>65800</v>
       </c>
       <c r="G81" s="3">
-        <v>85900</v>
+        <v>50500</v>
       </c>
       <c r="H81" s="3">
-        <v>42300</v>
+        <v>85400</v>
       </c>
       <c r="I81" s="3">
-        <v>-55000</v>
+        <v>42000</v>
       </c>
       <c r="J81" s="3">
+        <v>-54700</v>
+      </c>
+      <c r="K81" s="3">
         <v>-29700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>23300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-246300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-246500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-201300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-176800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-215700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-171700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-212700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-450300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-384200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-575400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-355600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-275900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-504900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-439500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-294800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-98300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2198300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1737000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-248500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-267600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-410200</v>
       </c>
-      <c r="AG81" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH81" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,8 +7201,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7089,8 +7288,8 @@
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>16</v>
+      <c r="AE83" s="3">
+        <v>0</v>
       </c>
       <c r="AF83" s="3" t="s">
         <v>16</v>
@@ -7098,8 +7297,11 @@
       <c r="AG83" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,62 +7787,65 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>88100</v>
+        <v>129600</v>
       </c>
       <c r="E89" s="3">
-        <v>115500</v>
+        <v>87500</v>
       </c>
       <c r="F89" s="3">
-        <v>123100</v>
+        <v>114800</v>
       </c>
       <c r="G89" s="3">
-        <v>139300</v>
+        <v>122300</v>
       </c>
       <c r="H89" s="3">
-        <v>118600</v>
+        <v>138400</v>
       </c>
       <c r="I89" s="3">
-        <v>27200</v>
+        <v>117900</v>
       </c>
       <c r="J89" s="3">
+        <v>27000</v>
+      </c>
+      <c r="K89" s="3">
         <v>6600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-161100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-151200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-295700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-204800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-187900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-211500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-281700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-200200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-94600</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>16</v>
       </c>
@@ -7641,8 +7858,8 @@
       <c r="X89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y89" s="3">
-        <v>0</v>
+      <c r="Y89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z89" s="3">
         <v>0</v>
@@ -7659,8 +7876,8 @@
       <c r="AD89" s="3">
         <v>0</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>16</v>
+      <c r="AE89" s="3">
+        <v>0</v>
       </c>
       <c r="AF89" s="3" t="s">
         <v>16</v>
@@ -7668,8 +7885,11 @@
       <c r="AG89" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,32 +7923,33 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-13300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-8800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-48100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-66000</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
         <v>0</v>
       </c>
@@ -7738,8 +7959,8 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>16</v>
+      <c r="N91" s="3">
+        <v>0</v>
       </c>
       <c r="O91" s="3" t="s">
         <v>16</v>
@@ -7750,8 +7971,8 @@
       <c r="Q91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
+      <c r="R91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="S91" s="3">
         <v>0</v>
@@ -7789,8 +8010,8 @@
       <c r="AD91" s="3">
         <v>0</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>16</v>
+      <c r="AE91" s="3">
+        <v>0</v>
       </c>
       <c r="AF91" s="3" t="s">
         <v>16</v>
@@ -7798,8 +8019,11 @@
       <c r="AG91" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,62 +8215,65 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-198900</v>
+        <v>-30800</v>
       </c>
       <c r="E94" s="3">
-        <v>-7700</v>
+        <v>-197700</v>
       </c>
       <c r="F94" s="3">
-        <v>-58500</v>
+        <v>-7600</v>
       </c>
       <c r="G94" s="3">
-        <v>23200</v>
+        <v>-58100</v>
       </c>
       <c r="H94" s="3">
-        <v>80500</v>
+        <v>23100</v>
       </c>
       <c r="I94" s="3">
-        <v>56600</v>
+        <v>80000</v>
       </c>
       <c r="J94" s="3">
+        <v>56200</v>
+      </c>
+      <c r="K94" s="3">
         <v>-90700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-9300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>289600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>268000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>8400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-386700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>39200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>50100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>168600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-252000</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>16</v>
       </c>
@@ -8056,8 +8286,8 @@
       <c r="X94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
+      <c r="Y94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z94" s="3">
         <v>0</v>
@@ -8074,8 +8304,8 @@
       <c r="AD94" s="3">
         <v>0</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>16</v>
+      <c r="AE94" s="3">
+        <v>0</v>
       </c>
       <c r="AF94" s="3" t="s">
         <v>16</v>
@@ -8083,8 +8313,11 @@
       <c r="AG94" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,8 +8351,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8213,8 +8447,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,62 +8741,65 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>36100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3100</v>
       </c>
-      <c r="E100" s="3">
-        <v>37400</v>
-      </c>
       <c r="F100" s="3">
-        <v>-163400</v>
+        <v>37200</v>
       </c>
       <c r="G100" s="3">
-        <v>-466600</v>
+        <v>-162400</v>
       </c>
       <c r="H100" s="3">
-        <v>397800</v>
+        <v>-463800</v>
       </c>
       <c r="I100" s="3">
-        <v>-14700</v>
+        <v>395400</v>
       </c>
       <c r="J100" s="3">
+        <v>-14600</v>
+      </c>
+      <c r="K100" s="3">
         <v>-46300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>282600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-723400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>123300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>115100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>85000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1168200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>34800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>121200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-12400</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>16</v>
       </c>
@@ -8566,8 +8812,8 @@
       <c r="X100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
+      <c r="Y100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z100" s="3">
         <v>0</v>
@@ -8584,8 +8830,8 @@
       <c r="AD100" s="3">
         <v>0</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>16</v>
+      <c r="AE100" s="3">
+        <v>0</v>
       </c>
       <c r="AF100" s="3" t="s">
         <v>16</v>
@@ -8593,62 +8839,65 @@
       <c r="AG100" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-4400</v>
+        <v>2000</v>
       </c>
       <c r="E101" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="F101" s="3">
         <v>600</v>
       </c>
-      <c r="F101" s="3">
-        <v>17800</v>
-      </c>
       <c r="G101" s="3">
-        <v>-1200</v>
+        <v>17700</v>
       </c>
       <c r="H101" s="3">
         <v>-1200</v>
       </c>
       <c r="I101" s="3">
-        <v>8400</v>
+        <v>-1200</v>
       </c>
       <c r="J101" s="3">
+        <v>8300</v>
+      </c>
+      <c r="K101" s="3">
         <v>10400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-10200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-3200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-13300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-3900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-16500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>10100</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U101" s="3" t="s">
         <v>16</v>
       </c>
@@ -8661,8 +8910,8 @@
       <c r="X101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
+      <c r="Y101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z101" s="3">
         <v>0</v>
@@ -8679,8 +8928,8 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-      <c r="AE101" s="3" t="s">
-        <v>16</v>
+      <c r="AE101" s="3">
+        <v>0</v>
       </c>
       <c r="AF101" s="3" t="s">
         <v>16</v>
@@ -8688,62 +8937,65 @@
       <c r="AG101" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-118300</v>
+        <v>136900</v>
       </c>
       <c r="E102" s="3">
-        <v>145900</v>
+        <v>-117600</v>
       </c>
       <c r="F102" s="3">
-        <v>-81000</v>
+        <v>145000</v>
       </c>
       <c r="G102" s="3">
-        <v>-305400</v>
+        <v>-80500</v>
       </c>
       <c r="H102" s="3">
-        <v>595700</v>
+        <v>-303500</v>
       </c>
       <c r="I102" s="3">
-        <v>77400</v>
+        <v>592100</v>
       </c>
       <c r="J102" s="3">
+        <v>76900</v>
+      </c>
+      <c r="K102" s="3">
         <v>-120000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>111600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-595300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>92400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-94700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-493500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>991300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-213400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>88300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-348900</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>16</v>
       </c>
@@ -8756,8 +9008,8 @@
       <c r="X102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y102" s="3">
-        <v>0</v>
+      <c r="Y102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z102" s="3">
         <v>0</v>
@@ -8774,13 +9026,16 @@
       <c r="AD102" s="3">
         <v>0</v>
       </c>
-      <c r="AE102" s="3" t="s">
-        <v>16</v>
+      <c r="AE102" s="3">
+        <v>0</v>
       </c>
       <c r="AF102" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AG102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH102" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IQ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IQ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="92">
   <si>
     <t>IQ</t>
   </si>
@@ -656,441 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1095200</v>
+        <v>1048700</v>
       </c>
       <c r="E8" s="3">
-        <v>1064700</v>
+        <v>1117600</v>
       </c>
       <c r="F8" s="3">
-        <v>1107400</v>
+        <v>1086500</v>
       </c>
       <c r="G8" s="3">
-        <v>1078000</v>
+        <v>1130000</v>
       </c>
       <c r="H8" s="3">
-        <v>1153500</v>
+        <v>1100000</v>
       </c>
       <c r="I8" s="3">
-        <v>1049000</v>
+        <v>1177000</v>
       </c>
       <c r="J8" s="3">
+        <v>1070400</v>
+      </c>
+      <c r="K8" s="3">
         <v>1032200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>925400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1004800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1020200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1078800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1092700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1109200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1038200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1049600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1092200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1197700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1154300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1154000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1086300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1063300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1020600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>967700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>863600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>699800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>691200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>734700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>642100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>477600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>458800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>473800</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>778000</v>
+        <v>800500</v>
       </c>
       <c r="E9" s="3">
-        <v>764500</v>
+        <v>793900</v>
       </c>
       <c r="F9" s="3">
-        <v>806800</v>
+        <v>780100</v>
       </c>
       <c r="G9" s="3">
-        <v>797700</v>
+        <v>823300</v>
       </c>
       <c r="H9" s="3">
-        <v>822900</v>
+        <v>814000</v>
       </c>
       <c r="I9" s="3">
-        <v>746400</v>
+        <v>839700</v>
       </c>
       <c r="J9" s="3">
+        <v>761600</v>
+      </c>
+      <c r="K9" s="3">
         <v>788200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>729600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>823500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>898600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>999000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>986500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>989600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>944400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>929300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1007000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1237300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1218700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1275500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1066600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1107000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1237800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1071400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>854700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>695600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>650700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>726900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1304500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1035100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>453900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>456800</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>317200</v>
+        <v>248200</v>
       </c>
       <c r="E10" s="3">
-        <v>300300</v>
+        <v>323700</v>
       </c>
       <c r="F10" s="3">
-        <v>300600</v>
+        <v>306400</v>
       </c>
       <c r="G10" s="3">
-        <v>280200</v>
+        <v>306700</v>
       </c>
       <c r="H10" s="3">
-        <v>330600</v>
+        <v>286000</v>
       </c>
       <c r="I10" s="3">
-        <v>302700</v>
+        <v>337300</v>
       </c>
       <c r="J10" s="3">
+        <v>308800</v>
+      </c>
+      <c r="K10" s="3">
         <v>244000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>195800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>181300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>121700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>79800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>106200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>119600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>93800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>120400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>85200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-39600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>-64300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>-121500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>19700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>-43700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>-217200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>-103700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>8900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>4200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>40500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>7800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>-662500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>-557500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>4900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,106 +1138,110 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>59300</v>
+        <v>63300</v>
       </c>
       <c r="E12" s="3">
-        <v>62400</v>
+        <v>60500</v>
       </c>
       <c r="F12" s="3">
-        <v>61800</v>
+        <v>63700</v>
       </c>
       <c r="G12" s="3">
-        <v>60700</v>
+        <v>63100</v>
       </c>
       <c r="H12" s="3">
-        <v>59200</v>
+        <v>61900</v>
       </c>
       <c r="I12" s="3">
-        <v>64400</v>
+        <v>60400</v>
       </c>
       <c r="J12" s="3">
         <v>65700</v>
       </c>
       <c r="K12" s="3">
+        <v>65700</v>
+      </c>
+      <c r="L12" s="3">
         <v>67000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>65600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>105400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>97100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>97200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>93600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>92300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>97800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>97900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>106200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>109500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>109700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>100000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>91000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>88200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>78100</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>61800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>55600</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>52300</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>50800</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>87400</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>78200</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>35500</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>33400</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1321,8 +1338,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1419,8 +1439,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>964700</v>
+        <v>1000500</v>
       </c>
       <c r="E17" s="3">
-        <v>957800</v>
+        <v>984400</v>
       </c>
       <c r="F17" s="3">
-        <v>1004200</v>
+        <v>977400</v>
       </c>
       <c r="G17" s="3">
-        <v>993600</v>
+        <v>1024700</v>
       </c>
       <c r="H17" s="3">
-        <v>1034800</v>
+        <v>1013900</v>
       </c>
       <c r="I17" s="3">
-        <v>940800</v>
+        <v>1056000</v>
       </c>
       <c r="J17" s="3">
+        <v>960000</v>
+      </c>
+      <c r="K17" s="3">
         <v>989400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>907900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>991900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1154900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1273200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1253800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1250400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1220200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1226300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1281000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1548600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1543700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1595700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1372300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1371500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1503400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1330400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1049400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>852200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>814000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>893000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>789100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>628800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>569700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>557900</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>130500</v>
+        <v>48200</v>
       </c>
       <c r="E18" s="3">
-        <v>106900</v>
+        <v>133200</v>
       </c>
       <c r="F18" s="3">
-        <v>103200</v>
+        <v>109100</v>
       </c>
       <c r="G18" s="3">
-        <v>84300</v>
+        <v>105300</v>
       </c>
       <c r="H18" s="3">
-        <v>118600</v>
+        <v>86100</v>
       </c>
       <c r="I18" s="3">
-        <v>108300</v>
+        <v>121000</v>
       </c>
       <c r="J18" s="3">
+        <v>110500</v>
+      </c>
+      <c r="K18" s="3">
         <v>42800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>17500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>12900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-134700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-194500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-161100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-141200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-182000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-176600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-188900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-351000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-389400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-441800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-286000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-308200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-482800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-362700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-185900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-152400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-122800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-158300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-147000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-151200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-110900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-84100</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1782,106 +1815,110 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E20" s="3">
         <v>2900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3800</v>
       </c>
-      <c r="G20" s="3">
-        <v>6100</v>
-      </c>
       <c r="H20" s="3">
-        <v>10700</v>
+        <v>6200</v>
       </c>
       <c r="I20" s="3">
-        <v>-43500</v>
+        <v>11000</v>
       </c>
       <c r="J20" s="3">
+        <v>-44300</v>
+      </c>
+      <c r="K20" s="3">
         <v>-66400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-15200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>37700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-59200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>3000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>16800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>15100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>3900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>49100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>18400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-57400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>54200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-89300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-27300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>52700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>3800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-73300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-106200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>96800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>39800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>2300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>17900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-20200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
@@ -1960,305 +1997,314 @@
       <c r="AB21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD21" s="3">
         <v>1174600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>835600</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH21" s="3">
         <v>598900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>443800</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>39000</v>
+        <v>40600</v>
       </c>
       <c r="E22" s="3">
+        <v>39800</v>
+      </c>
+      <c r="F22" s="3">
+        <v>40100</v>
+      </c>
+      <c r="G22" s="3">
+        <v>39700</v>
+      </c>
+      <c r="H22" s="3">
         <v>39300</v>
       </c>
-      <c r="F22" s="3">
-        <v>38900</v>
-      </c>
-      <c r="G22" s="3">
-        <v>38500</v>
-      </c>
-      <c r="H22" s="3">
-        <v>39500</v>
-      </c>
       <c r="I22" s="3">
-        <v>24300</v>
+        <v>40300</v>
       </c>
       <c r="J22" s="3">
+        <v>24800</v>
+      </c>
+      <c r="K22" s="3">
         <v>25100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>25300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>24200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>44800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>49900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>49300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>46000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>37500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>39300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>39100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>41000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>42600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>39700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>37900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>20600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>8900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>2200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>1300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>1200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>6300</v>
       </c>
-      <c r="AD22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE22" s="3">
+      <c r="AE22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF22" s="3">
         <v>12200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>9900</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>6100</v>
       </c>
-      <c r="AH22" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>94400</v>
+        <v>14300</v>
       </c>
       <c r="E23" s="3">
-        <v>71000</v>
+        <v>96400</v>
       </c>
       <c r="F23" s="3">
-        <v>68000</v>
+        <v>72500</v>
       </c>
       <c r="G23" s="3">
-        <v>51900</v>
+        <v>69400</v>
       </c>
       <c r="H23" s="3">
-        <v>89900</v>
+        <v>53000</v>
       </c>
       <c r="I23" s="3">
-        <v>40500</v>
+        <v>91700</v>
       </c>
       <c r="J23" s="3">
+        <v>41300</v>
+      </c>
+      <c r="K23" s="3">
         <v>-48700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-23000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>26300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-238700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-241400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-193600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-172100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-215500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-166900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-209600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-449400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-377800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-570700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-351100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-276100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-487900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-438200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-293400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-56900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-89300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-156000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-141400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-162700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-137200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-91300</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>2400</v>
+        <v>3600</v>
       </c>
       <c r="E24" s="3">
-        <v>5300</v>
+        <v>2500</v>
       </c>
       <c r="F24" s="3">
-        <v>1200</v>
+        <v>5400</v>
       </c>
       <c r="G24" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H24" s="3">
         <v>1100</v>
       </c>
-      <c r="H24" s="3">
-        <v>3400</v>
-      </c>
       <c r="I24" s="3">
+        <v>3500</v>
+      </c>
+      <c r="J24" s="3">
         <v>-1600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>4400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-2300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>3500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>11500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-1400</v>
-      </c>
-      <c r="AD24" s="3">
-        <v>100</v>
       </c>
       <c r="AE24" s="3">
         <v>100</v>
@@ -2267,13 +2313,16 @@
         <v>100</v>
       </c>
       <c r="AG24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH24" s="3">
         <v>600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>92000</v>
+        <v>10700</v>
       </c>
       <c r="E26" s="3">
-        <v>65700</v>
+        <v>93900</v>
       </c>
       <c r="F26" s="3">
-        <v>66800</v>
+        <v>67000</v>
       </c>
       <c r="G26" s="3">
-        <v>50800</v>
+        <v>68200</v>
       </c>
       <c r="H26" s="3">
-        <v>86500</v>
+        <v>51900</v>
       </c>
       <c r="I26" s="3">
-        <v>42100</v>
+        <v>88200</v>
       </c>
       <c r="J26" s="3">
+        <v>42900</v>
+      </c>
+      <c r="K26" s="3">
         <v>-54600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-28000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>24000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-243700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-242700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-198000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-175000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-213300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-169600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-212000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-450100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-381200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-573200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-352000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-277200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-499400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-437300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-294100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-56900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-87900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-156100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-141500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-162800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-137800</v>
       </c>
-      <c r="AH26" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI26" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>90500</v>
+        <v>9700</v>
       </c>
       <c r="E27" s="3">
-        <v>64400</v>
+        <v>92400</v>
       </c>
       <c r="F27" s="3">
-        <v>65800</v>
+        <v>65700</v>
       </c>
       <c r="G27" s="3">
-        <v>50500</v>
+        <v>67100</v>
       </c>
       <c r="H27" s="3">
-        <v>85400</v>
+        <v>51500</v>
       </c>
       <c r="I27" s="3">
-        <v>42000</v>
+        <v>87100</v>
       </c>
       <c r="J27" s="3">
+        <v>42900</v>
+      </c>
+      <c r="K27" s="3">
         <v>-54700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-29700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>23300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-246300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-246500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-201300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-176800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-215700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-171700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-212700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-450300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-384200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-575400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-355600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-275900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-504900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-439500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-294800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-98300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>2198300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-1737000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-248500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-267600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-410200</v>
       </c>
-      <c r="AH27" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI27" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,204 +3025,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3800</v>
       </c>
-      <c r="G32" s="3">
-        <v>-6100</v>
-      </c>
       <c r="H32" s="3">
-        <v>-10700</v>
+        <v>-6200</v>
       </c>
       <c r="I32" s="3">
-        <v>43500</v>
+        <v>-11000</v>
       </c>
       <c r="J32" s="3">
+        <v>44300</v>
+      </c>
+      <c r="K32" s="3">
         <v>66400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>15200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-37700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>59200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-3000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-16800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-15100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-3900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-49100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-18400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>57400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-54200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>89300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>27300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-52700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-3800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>73300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>106200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-96800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-39800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-17900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>1600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>20200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>90500</v>
+        <v>9700</v>
       </c>
       <c r="E33" s="3">
-        <v>64400</v>
+        <v>92400</v>
       </c>
       <c r="F33" s="3">
-        <v>65800</v>
+        <v>65700</v>
       </c>
       <c r="G33" s="3">
-        <v>50500</v>
+        <v>67100</v>
       </c>
       <c r="H33" s="3">
-        <v>85400</v>
+        <v>51500</v>
       </c>
       <c r="I33" s="3">
-        <v>42000</v>
+        <v>87100</v>
       </c>
       <c r="J33" s="3">
+        <v>42900</v>
+      </c>
+      <c r="K33" s="3">
         <v>-54700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-29700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>23300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-246300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-246500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-201300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-176800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-215700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-171700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-212700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-450300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-384200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-575400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-355600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-275900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-504900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-439500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-294800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-98300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>2198300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-1737000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-248500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-267600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-410200</v>
       </c>
-      <c r="AH33" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI33" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>90500</v>
+        <v>9700</v>
       </c>
       <c r="E35" s="3">
-        <v>64400</v>
+        <v>92400</v>
       </c>
       <c r="F35" s="3">
-        <v>65800</v>
+        <v>65700</v>
       </c>
       <c r="G35" s="3">
-        <v>50500</v>
+        <v>67100</v>
       </c>
       <c r="H35" s="3">
-        <v>85400</v>
+        <v>51500</v>
       </c>
       <c r="I35" s="3">
-        <v>42000</v>
+        <v>87100</v>
       </c>
       <c r="J35" s="3">
+        <v>42900</v>
+      </c>
+      <c r="K35" s="3">
         <v>-54700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-29700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>23300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-246300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-246500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-201300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-176800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-215700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-171700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-212700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-450300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-384200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-575400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-355600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-275900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-504900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-439500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-294800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-98300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>2198300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-1737000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-248500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-267600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-410200</v>
       </c>
-      <c r="AH35" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI35" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,95 +3611,96 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>697100</v>
+        <v>888400</v>
       </c>
       <c r="E41" s="3">
-        <v>612700</v>
+        <v>711300</v>
       </c>
       <c r="F41" s="3">
-        <v>584500</v>
+        <v>625200</v>
       </c>
       <c r="G41" s="3">
-        <v>492600</v>
+        <v>596400</v>
       </c>
       <c r="H41" s="3">
-        <v>625800</v>
+        <v>502600</v>
       </c>
       <c r="I41" s="3">
-        <v>980700</v>
+        <v>638500</v>
       </c>
       <c r="J41" s="3">
+        <v>1000700</v>
+      </c>
+      <c r="K41" s="3">
         <v>491800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>406400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>526300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>413900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1037100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>960100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1023500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1519400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>461900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>630800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>578200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>913800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>702900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>829200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1806300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>666100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>816200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1159100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>57900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>105200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>176500</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF41" s="3" t="s">
         <v>16</v>
       </c>
@@ -3623,95 +3710,98 @@
       <c r="AH41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>136200</v>
+        <v>103700</v>
       </c>
       <c r="E42" s="3">
-        <v>130100</v>
+        <v>139000</v>
       </c>
       <c r="F42" s="3">
-        <v>141600</v>
+        <v>132800</v>
       </c>
       <c r="G42" s="3">
-        <v>140200</v>
+        <v>144500</v>
       </c>
       <c r="H42" s="3">
-        <v>92400</v>
+        <v>143100</v>
       </c>
       <c r="I42" s="3">
-        <v>113100</v>
+        <v>94300</v>
       </c>
       <c r="J42" s="3">
+        <v>115400</v>
+      </c>
+      <c r="K42" s="3">
         <v>203200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>262800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>177100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>186200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>520500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>793700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>823300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>467500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>526300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>618400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>823300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>705100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1067400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1347200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>591100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>880400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>538000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>665100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>70700</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>111900</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>497500</v>
       </c>
-      <c r="AE42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF42" s="3" t="s">
         <v>16</v>
       </c>
@@ -3721,95 +3811,98 @@
       <c r="AH42" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>614000</v>
+        <v>374900</v>
       </c>
       <c r="E43" s="3">
-        <v>535500</v>
+        <v>626500</v>
       </c>
       <c r="F43" s="3">
-        <v>369700</v>
+        <v>546400</v>
       </c>
       <c r="G43" s="3">
-        <v>394000</v>
+        <v>377300</v>
       </c>
       <c r="H43" s="3">
-        <v>399900</v>
+        <v>402100</v>
       </c>
       <c r="I43" s="3">
-        <v>346300</v>
+        <v>408000</v>
       </c>
       <c r="J43" s="3">
+        <v>353400</v>
+      </c>
+      <c r="K43" s="3">
         <v>380500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>359000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>388200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>400900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>448800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>478900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>494800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>478900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>500900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>503700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>717100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>591200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>514100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>513100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>535000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>460500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>452200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>350200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>420800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>322200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>693700</v>
       </c>
-      <c r="AE43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF43" s="3" t="s">
         <v>16</v>
       </c>
@@ -3819,95 +3912,98 @@
       <c r="AH43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>100100</v>
+        <v>90400</v>
       </c>
       <c r="E44" s="3">
-        <v>80500</v>
+        <v>102200</v>
       </c>
       <c r="F44" s="3">
-        <v>96300</v>
+        <v>82100</v>
       </c>
       <c r="G44" s="3">
-        <v>115000</v>
+        <v>98300</v>
       </c>
       <c r="H44" s="3">
-        <v>129900</v>
+        <v>117300</v>
       </c>
       <c r="I44" s="3">
-        <v>103100</v>
+        <v>132600</v>
       </c>
       <c r="J44" s="3">
+        <v>105200</v>
+      </c>
+      <c r="K44" s="3">
         <v>113000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>110700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>125700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>128600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>155900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>127900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>143600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>144100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>182200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>174500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>224300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>188600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>206500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>179700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>191900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>169000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>147200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>162900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>172400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>117500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>110300</v>
       </c>
-      <c r="AE44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF44" s="3" t="s">
         <v>16</v>
       </c>
@@ -3917,95 +4013,98 @@
       <c r="AH44" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>359500</v>
+        <v>340500</v>
       </c>
       <c r="E45" s="3">
-        <v>386900</v>
+        <v>366900</v>
       </c>
       <c r="F45" s="3">
-        <v>408900</v>
+        <v>394800</v>
       </c>
       <c r="G45" s="3">
-        <v>369000</v>
+        <v>417200</v>
       </c>
       <c r="H45" s="3">
-        <v>1551100</v>
+        <v>376500</v>
       </c>
       <c r="I45" s="3">
-        <v>361500</v>
+        <v>1582800</v>
       </c>
       <c r="J45" s="3">
+        <v>368900</v>
+      </c>
+      <c r="K45" s="3">
         <v>310100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>308700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>381200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>461800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>540900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>588900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>597800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>492900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>601500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>679700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>690600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>722800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1031300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>926000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>772700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>707300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>430500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>377800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>145500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>161200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>137200</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF45" s="3" t="s">
         <v>16</v>
       </c>
@@ -4015,95 +4114,98 @@
       <c r="AH45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1906900</v>
+        <v>1798000</v>
       </c>
       <c r="E46" s="3">
-        <v>1745700</v>
+        <v>1945900</v>
       </c>
       <c r="F46" s="3">
-        <v>1601000</v>
+        <v>1781300</v>
       </c>
       <c r="G46" s="3">
-        <v>1510800</v>
+        <v>1633700</v>
       </c>
       <c r="H46" s="3">
-        <v>2799100</v>
+        <v>1541600</v>
       </c>
       <c r="I46" s="3">
-        <v>1904600</v>
+        <v>2856300</v>
       </c>
       <c r="J46" s="3">
+        <v>1943500</v>
+      </c>
+      <c r="K46" s="3">
         <v>1498600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1447600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1598500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1591300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2703300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2949500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3083100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3102800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2272700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2607100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3033400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3121600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3522200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3795200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3897100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2883300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2384200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2715100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>867300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>817900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1615200</v>
       </c>
-      <c r="AE46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF46" s="3" t="s">
         <v>16</v>
       </c>
@@ -4113,95 +4215,98 @@
       <c r="AH46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>339500</v>
+        <v>532100</v>
       </c>
       <c r="E47" s="3">
-        <v>334300</v>
+        <v>346400</v>
       </c>
       <c r="F47" s="3">
-        <v>347200</v>
+        <v>341100</v>
       </c>
       <c r="G47" s="3">
-        <v>350200</v>
+        <v>354300</v>
       </c>
       <c r="H47" s="3">
-        <v>320600</v>
+        <v>357400</v>
       </c>
       <c r="I47" s="3">
-        <v>347300</v>
+        <v>327100</v>
       </c>
       <c r="J47" s="3">
+        <v>354400</v>
+      </c>
+      <c r="K47" s="3">
         <v>403100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>448400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>452500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>430300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>499900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>503200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>485900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>451300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>577200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>579900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>580200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>485700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>480400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>413700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>400600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>381200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>322800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>173900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>170000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>81500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>59000</v>
       </c>
-      <c r="AE47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF47" s="3" t="s">
         <v>16</v>
       </c>
@@ -4211,95 +4316,98 @@
       <c r="AH47" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>208100</v>
+        <v>210300</v>
       </c>
       <c r="E48" s="3">
-        <v>213800</v>
+        <v>212400</v>
       </c>
       <c r="F48" s="3">
-        <v>213400</v>
+        <v>218200</v>
       </c>
       <c r="G48" s="3">
-        <v>223300</v>
+        <v>217700</v>
       </c>
       <c r="H48" s="3">
-        <v>233500</v>
+        <v>227900</v>
       </c>
       <c r="I48" s="3">
-        <v>245700</v>
+        <v>238300</v>
       </c>
       <c r="J48" s="3">
+        <v>250800</v>
+      </c>
+      <c r="K48" s="3">
         <v>260400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>292000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>302900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>311000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>320700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>345200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>323500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>333400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>360000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>408400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>402000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>381400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>369600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>358100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>265700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>235000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>206500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>196600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>189200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>179200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>179600</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF48" s="3" t="s">
         <v>16</v>
       </c>
@@ -4309,95 +4417,98 @@
       <c r="AH48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>3410900</v>
+        <v>3578700</v>
       </c>
       <c r="E49" s="3">
-        <v>3381300</v>
+        <v>3480500</v>
       </c>
       <c r="F49" s="3">
-        <v>3292100</v>
+        <v>3450300</v>
       </c>
       <c r="G49" s="3">
-        <v>3232600</v>
+        <v>3359300</v>
       </c>
       <c r="H49" s="3">
-        <v>3253000</v>
+        <v>3298600</v>
       </c>
       <c r="I49" s="3">
-        <v>3330400</v>
+        <v>3319400</v>
       </c>
       <c r="J49" s="3">
+        <v>3398400</v>
+      </c>
+      <c r="K49" s="3">
         <v>3344300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3291500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3244400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3126500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3033800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2854200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2546200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2436900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2355300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2174600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2369400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2362800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2601800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2423100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2432100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>2315500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2285000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1858100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1623800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1409900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1221500</v>
       </c>
-      <c r="AE49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF49" s="3" t="s">
         <v>16</v>
       </c>
@@ -4407,8 +4518,11 @@
       <c r="AH49" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,95 +4720,98 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>531300</v>
+        <v>598300</v>
       </c>
       <c r="E52" s="3">
-        <v>486100</v>
+        <v>542100</v>
       </c>
       <c r="F52" s="3">
-        <v>639900</v>
+        <v>496000</v>
       </c>
       <c r="G52" s="3">
-        <v>636200</v>
+        <v>653000</v>
       </c>
       <c r="H52" s="3">
-        <v>582600</v>
+        <v>649200</v>
       </c>
       <c r="I52" s="3">
-        <v>534000</v>
+        <v>594500</v>
       </c>
       <c r="J52" s="3">
+        <v>544900</v>
+      </c>
+      <c r="K52" s="3">
         <v>419600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>441300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>420100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>405500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>449900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>373200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>380400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>382900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>405700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>460100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>431800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>545600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>562800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>686200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>787200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>685500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>570200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>530500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>439700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>409900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>378500</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF52" s="3" t="s">
         <v>16</v>
       </c>
@@ -4701,8 +4821,11 @@
       <c r="AH52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,95 +4922,98 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>6396800</v>
+        <v>6717500</v>
       </c>
       <c r="E54" s="3">
-        <v>6161200</v>
+        <v>6527300</v>
       </c>
       <c r="F54" s="3">
-        <v>6093600</v>
+        <v>6286900</v>
       </c>
       <c r="G54" s="3">
-        <v>5953200</v>
+        <v>6218000</v>
       </c>
       <c r="H54" s="3">
-        <v>7188800</v>
+        <v>6074700</v>
       </c>
       <c r="I54" s="3">
-        <v>6362000</v>
+        <v>7335600</v>
       </c>
       <c r="J54" s="3">
+        <v>6491900</v>
+      </c>
+      <c r="K54" s="3">
         <v>5926000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5920800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6018500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5864600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7007500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7025300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6819100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6707400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5970900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6230000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6816800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6897200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7536800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>7676300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>7782700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6500500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>5768700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>5474100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>3289900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2898400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>3453700</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF54" s="3" t="s">
         <v>16</v>
       </c>
@@ -4897,8 +5023,11 @@
       <c r="AH54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,95 +5099,96 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>814800</v>
+        <v>841600</v>
       </c>
       <c r="E57" s="3">
-        <v>783500</v>
+        <v>831400</v>
       </c>
       <c r="F57" s="3">
-        <v>820100</v>
+        <v>799500</v>
       </c>
       <c r="G57" s="3">
-        <v>793000</v>
+        <v>836900</v>
       </c>
       <c r="H57" s="3">
-        <v>790500</v>
+        <v>809200</v>
       </c>
       <c r="I57" s="3">
-        <v>828100</v>
+        <v>806600</v>
       </c>
       <c r="J57" s="3">
+        <v>845000</v>
+      </c>
+      <c r="K57" s="3">
         <v>950800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>877400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>969600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1228400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1297500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1181700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1045200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1052600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1088800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1133500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1304000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1264600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1574100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1464200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1574600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1475900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1458800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1269100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1252000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1010300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1035600</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF57" s="3" t="s">
         <v>16</v>
       </c>
@@ -5067,95 +5198,98 @@
       <c r="AH57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>883900</v>
+        <v>1012800</v>
       </c>
       <c r="E58" s="3">
-        <v>880600</v>
+        <v>902000</v>
       </c>
       <c r="F58" s="3">
-        <v>894600</v>
+        <v>898600</v>
       </c>
       <c r="G58" s="3">
-        <v>416600</v>
+        <v>912900</v>
       </c>
       <c r="H58" s="3">
-        <v>1592600</v>
+        <v>425100</v>
       </c>
       <c r="I58" s="3">
-        <v>1610000</v>
+        <v>1625100</v>
       </c>
       <c r="J58" s="3">
+        <v>1642900</v>
+      </c>
+      <c r="K58" s="3">
         <v>1721400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1678900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>606400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>568600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1344000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1249600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1102100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1200900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>662600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>601300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>519500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>516600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>604300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>667800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>557600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>454600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>165500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>89900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>58400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>44400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1232000</v>
       </c>
-      <c r="AE58" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF58" s="3" t="s">
         <v>16</v>
       </c>
@@ -5165,95 +5299,98 @@
       <c r="AH58" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1478200</v>
+        <v>1531600</v>
       </c>
       <c r="E59" s="3">
-        <v>1422500</v>
+        <v>1508400</v>
       </c>
       <c r="F59" s="3">
-        <v>1407200</v>
+        <v>1451600</v>
       </c>
       <c r="G59" s="3">
-        <v>1379200</v>
+        <v>1435900</v>
       </c>
       <c r="H59" s="3">
-        <v>1440700</v>
+        <v>1407300</v>
       </c>
       <c r="I59" s="3">
-        <v>1448400</v>
+        <v>1470100</v>
       </c>
       <c r="J59" s="3">
+        <v>1478000</v>
+      </c>
+      <c r="K59" s="3">
         <v>1355000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1358100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1389900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1306500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1331100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1335500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1355800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1206300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1242700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1281200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1445100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1325100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1178200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1144200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1013800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>946900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>887200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>710200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>619500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>613400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1325600</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF59" s="3" t="s">
         <v>16</v>
       </c>
@@ -5263,95 +5400,98 @@
       <c r="AH59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>3176900</v>
+        <v>3386000</v>
       </c>
       <c r="E60" s="3">
-        <v>3086700</v>
+        <v>3241700</v>
       </c>
       <c r="F60" s="3">
-        <v>3121900</v>
+        <v>3149700</v>
       </c>
       <c r="G60" s="3">
-        <v>2588800</v>
+        <v>3185600</v>
       </c>
       <c r="H60" s="3">
-        <v>3823800</v>
+        <v>2641700</v>
       </c>
       <c r="I60" s="3">
-        <v>3886400</v>
+        <v>3901800</v>
       </c>
       <c r="J60" s="3">
+        <v>3965800</v>
+      </c>
+      <c r="K60" s="3">
         <v>4027300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3914400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2965900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3103600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3972600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3766800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3503200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3459800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2994100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3016000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3268600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3106300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3356700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3276200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3146000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2877300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2511500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2069200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1929900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1668000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3593200</v>
       </c>
-      <c r="AE60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF60" s="3" t="s">
         <v>16</v>
       </c>
@@ -5361,95 +5501,98 @@
       <c r="AH60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1199800</v>
+        <v>1238800</v>
       </c>
       <c r="E61" s="3">
-        <v>1138700</v>
+        <v>1224300</v>
       </c>
       <c r="F61" s="3">
-        <v>1153500</v>
+        <v>1162000</v>
       </c>
       <c r="G61" s="3">
-        <v>1581500</v>
+        <v>1177100</v>
       </c>
       <c r="H61" s="3">
-        <v>1612100</v>
+        <v>1613800</v>
       </c>
       <c r="I61" s="3">
-        <v>1322000</v>
+        <v>1645000</v>
       </c>
       <c r="J61" s="3">
+        <v>1348900</v>
+      </c>
+      <c r="K61" s="3">
         <v>880100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>832800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1828100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1747000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1801200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1808500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1763700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1660200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1889000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2001200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2112200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2029000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2057800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1879700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1856600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>777900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>38300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>39000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>40000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>40700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>42100</v>
       </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
       <c r="AF61" s="3">
         <v>0</v>
       </c>
@@ -5459,95 +5602,98 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>256100</v>
+      </c>
+      <c r="E62" s="3">
+        <v>261100</v>
+      </c>
+      <c r="F62" s="3">
+        <v>257400</v>
+      </c>
+      <c r="G62" s="3">
         <v>255800</v>
       </c>
-      <c r="E62" s="3">
-        <v>252300</v>
-      </c>
-      <c r="F62" s="3">
-        <v>250600</v>
-      </c>
-      <c r="G62" s="3">
-        <v>298800</v>
-      </c>
       <c r="H62" s="3">
-        <v>281300</v>
+        <v>304900</v>
       </c>
       <c r="I62" s="3">
-        <v>277200</v>
+        <v>287100</v>
       </c>
       <c r="J62" s="3">
+        <v>282900</v>
+      </c>
+      <c r="K62" s="3">
         <v>265600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>288800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>271600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>230700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>232500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>253100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>258600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>272800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>288000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>290300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>281500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>266000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>220700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>225900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>248700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>208500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>210000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>97000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>96100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1100</v>
       </c>
-      <c r="AE62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF62" s="3" t="s">
         <v>16</v>
       </c>
@@ -5557,8 +5703,11 @@
       <c r="AH62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,95 +6006,98 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>4640300</v>
+        <v>4889900</v>
       </c>
       <c r="E66" s="3">
-        <v>4491300</v>
+        <v>4735000</v>
       </c>
       <c r="F66" s="3">
-        <v>4538500</v>
+        <v>4583000</v>
       </c>
       <c r="G66" s="3">
-        <v>4480500</v>
+        <v>4631100</v>
       </c>
       <c r="H66" s="3">
-        <v>5728600</v>
+        <v>4572000</v>
       </c>
       <c r="I66" s="3">
-        <v>5498500</v>
+        <v>5845500</v>
       </c>
       <c r="J66" s="3">
+        <v>5610700</v>
+      </c>
+      <c r="K66" s="3">
         <v>5186000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5048800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5075000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5148300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6071100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5873200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5566700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5418900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5194800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5329500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5684500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5423400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5659900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5402400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5268100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3880900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2771200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2205600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2066400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1710600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3636400</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF66" s="3" t="s">
         <v>16</v>
       </c>
@@ -5949,8 +6107,11 @@
       <c r="AH66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6259,17 +6427,17 @@
         <v>0</v>
       </c>
       <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="3">
         <v>3284400</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AD70" s="3">
         <v>3242900</v>
       </c>
-      <c r="AD70" s="3">
+      <c r="AE70" s="3">
         <v>4323600</v>
       </c>
-      <c r="AE70" s="3">
-        <v>0</v>
-      </c>
       <c r="AF70" s="3">
         <v>0</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,95 +6548,98 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-6067700</v>
+        <v>-6181900</v>
       </c>
       <c r="E72" s="3">
-        <v>-6158300</v>
+        <v>-6191600</v>
       </c>
       <c r="F72" s="3">
-        <v>-6222700</v>
+        <v>-6284000</v>
       </c>
       <c r="G72" s="3">
-        <v>-6288400</v>
+        <v>-6349700</v>
       </c>
       <c r="H72" s="3">
-        <v>-6338900</v>
+        <v>-6416800</v>
       </c>
       <c r="I72" s="3">
-        <v>-6424300</v>
+        <v>-6468300</v>
       </c>
       <c r="J72" s="3">
+        <v>-6555400</v>
+      </c>
+      <c r="K72" s="3">
         <v>-6466300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-6451600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-6378400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-6512400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-6450800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-6268400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-5880400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-5703600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-5757100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-5636300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-5750400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-5209800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-4889200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-4224500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-3852200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-3414300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-2796700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-2357100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-2130900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-2154600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-4631600</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF72" s="3" t="s">
         <v>16</v>
       </c>
@@ -6475,8 +6649,11 @@
       <c r="AH72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,95 +6952,98 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1756500</v>
+        <v>1827500</v>
       </c>
       <c r="E76" s="3">
-        <v>1669900</v>
+        <v>1792400</v>
       </c>
       <c r="F76" s="3">
-        <v>1555100</v>
+        <v>1704000</v>
       </c>
       <c r="G76" s="3">
-        <v>1472700</v>
+        <v>1586900</v>
       </c>
       <c r="H76" s="3">
-        <v>1460200</v>
+        <v>1502700</v>
       </c>
       <c r="I76" s="3">
-        <v>863600</v>
+        <v>1490000</v>
       </c>
       <c r="J76" s="3">
+        <v>881200</v>
+      </c>
+      <c r="K76" s="3">
         <v>740000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>872000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>943500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>716300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>936400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1152200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1252400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1288500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>776100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>900500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1132300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1473700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1876900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2273900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2514600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2619500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2997500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>3268500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-2060900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-2055000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-4506300</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF76" s="3" t="s">
         <v>16</v>
       </c>
@@ -6867,8 +7053,11 @@
       <c r="AH76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>90500</v>
+        <v>9700</v>
       </c>
       <c r="E81" s="3">
-        <v>64400</v>
+        <v>92400</v>
       </c>
       <c r="F81" s="3">
-        <v>65800</v>
+        <v>65700</v>
       </c>
       <c r="G81" s="3">
-        <v>50500</v>
+        <v>67100</v>
       </c>
       <c r="H81" s="3">
-        <v>85400</v>
+        <v>51500</v>
       </c>
       <c r="I81" s="3">
-        <v>42000</v>
+        <v>87100</v>
       </c>
       <c r="J81" s="3">
+        <v>42900</v>
+      </c>
+      <c r="K81" s="3">
         <v>-54700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-29700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>23300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-246300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-246500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-201300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-176800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-215700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-171700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-212700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-450300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-384200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-575400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-355600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-275900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-504900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-439500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-294800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-98300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>2198300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-1737000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-248500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-267600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-410200</v>
       </c>
-      <c r="AH81" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI81" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,8 +7400,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7291,8 +7490,8 @@
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>16</v>
+      <c r="AF83" s="3">
+        <v>0</v>
       </c>
       <c r="AG83" s="3" t="s">
         <v>16</v>
@@ -7300,8 +7499,11 @@
       <c r="AH83" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,65 +8004,68 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>129600</v>
+        <v>57900</v>
       </c>
       <c r="E89" s="3">
-        <v>87500</v>
+        <v>132200</v>
       </c>
       <c r="F89" s="3">
-        <v>114800</v>
+        <v>89300</v>
       </c>
       <c r="G89" s="3">
-        <v>122300</v>
+        <v>117100</v>
       </c>
       <c r="H89" s="3">
-        <v>138400</v>
+        <v>124800</v>
       </c>
       <c r="I89" s="3">
-        <v>117900</v>
+        <v>141200</v>
       </c>
       <c r="J89" s="3">
+        <v>120300</v>
+      </c>
+      <c r="K89" s="3">
         <v>27000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>6600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-161100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-151200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-295700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-204800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-187900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-211500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-281700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-200200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-94600</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>16</v>
       </c>
@@ -7861,8 +8078,8 @@
       <c r="Y89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Z89" s="3">
-        <v>0</v>
+      <c r="Z89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AA89" s="3">
         <v>0</v>
@@ -7879,8 +8096,8 @@
       <c r="AE89" s="3">
         <v>0</v>
       </c>
-      <c r="AF89" s="3" t="s">
-        <v>16</v>
+      <c r="AF89" s="3">
+        <v>0</v>
       </c>
       <c r="AG89" s="3" t="s">
         <v>16</v>
@@ -7888,8 +8105,11 @@
       <c r="AH89" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI89" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,35 +8144,36 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-28300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-13300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-8800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-48100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-66000</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
@@ -7962,8 +8183,8 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>16</v>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>16</v>
@@ -7974,8 +8195,8 @@
       <c r="R91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
+      <c r="S91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="T91" s="3">
         <v>0</v>
@@ -8013,8 +8234,8 @@
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>16</v>
+      <c r="AF91" s="3">
+        <v>0</v>
       </c>
       <c r="AG91" s="3" t="s">
         <v>16</v>
@@ -8022,8 +8243,11 @@
       <c r="AH91" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,65 +8445,68 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-30800</v>
+        <v>47400</v>
       </c>
       <c r="E94" s="3">
-        <v>-197700</v>
+        <v>-31400</v>
       </c>
       <c r="F94" s="3">
-        <v>-7600</v>
+        <v>-201700</v>
       </c>
       <c r="G94" s="3">
-        <v>-58100</v>
+        <v>-7800</v>
       </c>
       <c r="H94" s="3">
-        <v>23100</v>
+        <v>-59300</v>
       </c>
       <c r="I94" s="3">
-        <v>80000</v>
+        <v>23500</v>
       </c>
       <c r="J94" s="3">
+        <v>81600</v>
+      </c>
+      <c r="K94" s="3">
         <v>56200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-90700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-9300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>289600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>268000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>8400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-386700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>39200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>50100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>168600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-252000</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>16</v>
       </c>
@@ -8289,8 +8519,8 @@
       <c r="Y94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
+      <c r="Z94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AA94" s="3">
         <v>0</v>
@@ -8307,8 +8537,8 @@
       <c r="AE94" s="3">
         <v>0</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>16</v>
+      <c r="AF94" s="3">
+        <v>0</v>
       </c>
       <c r="AG94" s="3" t="s">
         <v>16</v>
@@ -8316,8 +8546,11 @@
       <c r="AH94" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,65 +8987,68 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>36100</v>
+        <v>122100</v>
       </c>
       <c r="E100" s="3">
-        <v>-3100</v>
+        <v>36800</v>
       </c>
       <c r="F100" s="3">
-        <v>37200</v>
+        <v>-3200</v>
       </c>
       <c r="G100" s="3">
-        <v>-162400</v>
+        <v>38000</v>
       </c>
       <c r="H100" s="3">
-        <v>-463800</v>
+        <v>-165700</v>
       </c>
       <c r="I100" s="3">
-        <v>395400</v>
+        <v>-473200</v>
       </c>
       <c r="J100" s="3">
+        <v>403400</v>
+      </c>
+      <c r="K100" s="3">
         <v>-14600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-46300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>282600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-723400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>123300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>115100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>85000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1168200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>34800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>121200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-12400</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>16</v>
       </c>
@@ -8815,8 +9061,8 @@
       <c r="Y100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
+      <c r="Z100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AA100" s="3">
         <v>0</v>
@@ -8833,8 +9079,8 @@
       <c r="AE100" s="3">
         <v>0</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>16</v>
+      <c r="AF100" s="3">
+        <v>0</v>
       </c>
       <c r="AG100" s="3" t="s">
         <v>16</v>
@@ -8842,65 +9088,68 @@
       <c r="AH100" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>2000</v>
+        <v>3300</v>
       </c>
       <c r="E101" s="3">
-        <v>-4300</v>
+        <v>2100</v>
       </c>
       <c r="F101" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="G101" s="3">
         <v>600</v>
       </c>
-      <c r="G101" s="3">
-        <v>17700</v>
-      </c>
       <c r="H101" s="3">
-        <v>-1200</v>
+        <v>18000</v>
       </c>
       <c r="I101" s="3">
         <v>-1200</v>
       </c>
       <c r="J101" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="K101" s="3">
         <v>8300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>10400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-10200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-3200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-13300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-4600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-16500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-1500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>10100</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V101" s="3" t="s">
         <v>16</v>
       </c>
@@ -8913,8 +9162,8 @@
       <c r="Y101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
+      <c r="Z101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AA101" s="3">
         <v>0</v>
@@ -8931,8 +9180,8 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-      <c r="AF101" s="3" t="s">
-        <v>16</v>
+      <c r="AF101" s="3">
+        <v>0</v>
       </c>
       <c r="AG101" s="3" t="s">
         <v>16</v>
@@ -8940,65 +9189,68 @@
       <c r="AH101" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>136900</v>
+        <v>230600</v>
       </c>
       <c r="E102" s="3">
-        <v>-117600</v>
+        <v>139700</v>
       </c>
       <c r="F102" s="3">
-        <v>145000</v>
+        <v>-120000</v>
       </c>
       <c r="G102" s="3">
-        <v>-80500</v>
+        <v>147900</v>
       </c>
       <c r="H102" s="3">
-        <v>-303500</v>
+        <v>-82100</v>
       </c>
       <c r="I102" s="3">
-        <v>592100</v>
+        <v>-309700</v>
       </c>
       <c r="J102" s="3">
+        <v>604100</v>
+      </c>
+      <c r="K102" s="3">
         <v>76900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-120000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>111600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-595300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>92400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-94700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-493500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>991300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-213400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>88300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-348900</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>16</v>
       </c>
@@ -9011,8 +9263,8 @@
       <c r="Y102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Z102" s="3">
-        <v>0</v>
+      <c r="Z102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AA102" s="3">
         <v>0</v>
@@ -9029,13 +9281,16 @@
       <c r="AE102" s="3">
         <v>0</v>
       </c>
-      <c r="AF102" s="3" t="s">
-        <v>16</v>
+      <c r="AF102" s="3">
+        <v>0</v>
       </c>
       <c r="AG102" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AH102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI102" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IQ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IQ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="92">
   <si>
     <t>IQ</t>
   </si>
@@ -656,454 +656,467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1048700</v>
+        <v>1033000</v>
       </c>
       <c r="E8" s="3">
-        <v>1117600</v>
+        <v>1023700</v>
       </c>
       <c r="F8" s="3">
-        <v>1086500</v>
+        <v>1097900</v>
       </c>
       <c r="G8" s="3">
-        <v>1130000</v>
+        <v>1086800</v>
       </c>
       <c r="H8" s="3">
-        <v>1100000</v>
+        <v>1098500</v>
       </c>
       <c r="I8" s="3">
-        <v>1177000</v>
+        <v>1075800</v>
       </c>
       <c r="J8" s="3">
+        <v>1215400</v>
+      </c>
+      <c r="K8" s="3">
         <v>1070400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1032200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>925400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1004800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1020200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1078800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1092700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1109200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1038200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1049600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1092200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1197700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1154300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1154000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1086300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1063300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1020600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>967700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>863600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>699800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>691200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>734700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>642100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>477600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>458800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>473800</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>800500</v>
+        <v>805500</v>
       </c>
       <c r="E9" s="3">
-        <v>793900</v>
+        <v>781400</v>
       </c>
       <c r="F9" s="3">
-        <v>780100</v>
+        <v>779900</v>
       </c>
       <c r="G9" s="3">
-        <v>823300</v>
+        <v>744600</v>
       </c>
       <c r="H9" s="3">
-        <v>814000</v>
+        <v>800300</v>
       </c>
       <c r="I9" s="3">
-        <v>839700</v>
+        <v>796100</v>
       </c>
       <c r="J9" s="3">
+        <v>867100</v>
+      </c>
+      <c r="K9" s="3">
         <v>761600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>788200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>729600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>823500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>898600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>999000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>986500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>989600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>944400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>929300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1007000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1237300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1218700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1275500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1066600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1107000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1237800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1071400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>854700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>695600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>650700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>726900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1304500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1035100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>453900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>456800</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>248200</v>
+        <v>227500</v>
       </c>
       <c r="E10" s="3">
-        <v>323700</v>
+        <v>242300</v>
       </c>
       <c r="F10" s="3">
-        <v>306400</v>
+        <v>318000</v>
       </c>
       <c r="G10" s="3">
-        <v>306700</v>
+        <v>342200</v>
       </c>
       <c r="H10" s="3">
-        <v>286000</v>
+        <v>298200</v>
       </c>
       <c r="I10" s="3">
-        <v>337300</v>
+        <v>279700</v>
       </c>
       <c r="J10" s="3">
+        <v>348300</v>
+      </c>
+      <c r="K10" s="3">
         <v>308800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>244000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>195800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>181300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>121700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>79800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>106200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>119600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>93800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>120400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>85200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>-39600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>-64300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>-121500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>19700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>-43700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>-217200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>-103700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>8900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>4200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>40500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>7800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>-662500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>-557500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>4900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,109 +1152,113 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>63300</v>
+        <v>64000</v>
       </c>
       <c r="E12" s="3">
+        <v>61700</v>
+      </c>
+      <c r="F12" s="3">
+        <v>59500</v>
+      </c>
+      <c r="G12" s="3">
+        <v>63700</v>
+      </c>
+      <c r="H12" s="3">
+        <v>61300</v>
+      </c>
+      <c r="I12" s="3">
         <v>60500</v>
       </c>
-      <c r="F12" s="3">
-        <v>63700</v>
-      </c>
-      <c r="G12" s="3">
-        <v>63100</v>
-      </c>
-      <c r="H12" s="3">
-        <v>61900</v>
-      </c>
-      <c r="I12" s="3">
-        <v>60400</v>
-      </c>
       <c r="J12" s="3">
-        <v>65700</v>
+        <v>62400</v>
       </c>
       <c r="K12" s="3">
         <v>65700</v>
       </c>
       <c r="L12" s="3">
+        <v>65700</v>
+      </c>
+      <c r="M12" s="3">
         <v>67000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>65600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>105400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>97100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>97200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>93600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>92300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>97800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>97900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>106200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>109500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>109700</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>100000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>91000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>88200</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>78100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>61800</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>55600</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>52300</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>50800</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>87400</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>78200</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>35500</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>33400</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1341,31 +1358,34 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>36300</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1442,31 +1462,34 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>268800</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>259500</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>261100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>265900</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>284200</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>286000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>301900</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1543,8 +1566,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>1000500</v>
+        <v>998900</v>
       </c>
       <c r="E17" s="3">
-        <v>984400</v>
+        <v>976600</v>
       </c>
       <c r="F17" s="3">
-        <v>977400</v>
+        <v>967100</v>
       </c>
       <c r="G17" s="3">
-        <v>1024700</v>
+        <v>942000</v>
       </c>
       <c r="H17" s="3">
-        <v>1013900</v>
+        <v>996100</v>
       </c>
       <c r="I17" s="3">
-        <v>1056000</v>
+        <v>991700</v>
       </c>
       <c r="J17" s="3">
+        <v>1090400</v>
+      </c>
+      <c r="K17" s="3">
         <v>960000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>989400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>907900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>991900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1154900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1273200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1253800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1250400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1220200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1226300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1281000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1548600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1543700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1595700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1372300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1371500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1503400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1330400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1049400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>852200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>814000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>893000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>789100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>628800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>569700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>557900</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>48200</v>
+        <v>34100</v>
       </c>
       <c r="E18" s="3">
-        <v>133200</v>
+        <v>47100</v>
       </c>
       <c r="F18" s="3">
-        <v>109100</v>
+        <v>130800</v>
       </c>
       <c r="G18" s="3">
-        <v>105300</v>
+        <v>144800</v>
       </c>
       <c r="H18" s="3">
-        <v>86100</v>
+        <v>102300</v>
       </c>
       <c r="I18" s="3">
-        <v>121000</v>
+        <v>84200</v>
       </c>
       <c r="J18" s="3">
+        <v>125000</v>
+      </c>
+      <c r="K18" s="3">
         <v>110500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>42800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>17500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>12900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-134700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-194500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-161100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-141200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-182000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-176600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-188900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-351000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-389400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-441800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-286000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-308200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-482800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-362700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-185900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-152400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-122800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-158300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-147000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-151200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-110900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-84100</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1816,132 +1849,136 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>6700</v>
+        <v>-27900</v>
       </c>
       <c r="E20" s="3">
         <v>2900</v>
       </c>
       <c r="F20" s="3">
-        <v>3400</v>
+        <v>5200</v>
       </c>
       <c r="G20" s="3">
+        <v>3700</v>
+      </c>
+      <c r="H20" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I20" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J20" s="3">
+        <v>4000</v>
+      </c>
+      <c r="K20" s="3">
+        <v>-44300</v>
+      </c>
+      <c r="L20" s="3">
+        <v>-66400</v>
+      </c>
+      <c r="M20" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="N20" s="3">
+        <v>37700</v>
+      </c>
+      <c r="O20" s="3">
+        <v>-59200</v>
+      </c>
+      <c r="P20" s="3">
+        <v>3000</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>16800</v>
+      </c>
+      <c r="R20" s="3">
+        <v>15100</v>
+      </c>
+      <c r="S20" s="3">
+        <v>3900</v>
+      </c>
+      <c r="T20" s="3">
+        <v>49100</v>
+      </c>
+      <c r="U20" s="3">
+        <v>18400</v>
+      </c>
+      <c r="V20" s="3">
+        <v>-57400</v>
+      </c>
+      <c r="W20" s="3">
+        <v>54200</v>
+      </c>
+      <c r="X20" s="3">
+        <v>-89300</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>-27300</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>52700</v>
+      </c>
+      <c r="AA20" s="3">
         <v>3800</v>
       </c>
-      <c r="H20" s="3">
-        <v>6200</v>
-      </c>
-      <c r="I20" s="3">
-        <v>11000</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-44300</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-66400</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-15200</v>
-      </c>
-      <c r="M20" s="3">
-        <v>37700</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-59200</v>
-      </c>
-      <c r="O20" s="3">
-        <v>3000</v>
-      </c>
-      <c r="P20" s="3">
-        <v>16800</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>15100</v>
-      </c>
-      <c r="R20" s="3">
-        <v>3900</v>
-      </c>
-      <c r="S20" s="3">
-        <v>49100</v>
-      </c>
-      <c r="T20" s="3">
-        <v>18400</v>
-      </c>
-      <c r="U20" s="3">
-        <v>-57400</v>
-      </c>
-      <c r="V20" s="3">
-        <v>54200</v>
-      </c>
-      <c r="W20" s="3">
-        <v>-89300</v>
-      </c>
-      <c r="X20" s="3">
-        <v>-27300</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>52700</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>3800</v>
-      </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-73300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-106200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>96800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>39800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>2300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>17900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-20200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>16</v>
+      <c r="D21" s="3">
+        <v>330800</v>
+      </c>
+      <c r="E21" s="3">
+        <v>303700</v>
+      </c>
+      <c r="F21" s="3">
+        <v>386700</v>
+      </c>
+      <c r="G21" s="3">
+        <v>407000</v>
+      </c>
+      <c r="H21" s="3">
+        <v>384100</v>
+      </c>
+      <c r="I21" s="3">
+        <v>369000</v>
+      </c>
+      <c r="J21" s="3">
+        <v>422900</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>16</v>
@@ -2000,314 +2037,323 @@
       <c r="AC21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AD21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AE21" s="3">
         <v>1174600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>835600</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AG21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AH21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI21" s="3">
         <v>598900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>443800</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>40600</v>
+        <v>36600</v>
       </c>
       <c r="E22" s="3">
-        <v>39800</v>
+        <v>39700</v>
       </c>
       <c r="F22" s="3">
+        <v>39100</v>
+      </c>
+      <c r="G22" s="3">
         <v>40100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
+        <v>38600</v>
+      </c>
+      <c r="I22" s="3">
+        <v>38400</v>
+      </c>
+      <c r="J22" s="3">
+        <v>41600</v>
+      </c>
+      <c r="K22" s="3">
+        <v>24800</v>
+      </c>
+      <c r="L22" s="3">
+        <v>25100</v>
+      </c>
+      <c r="M22" s="3">
+        <v>25300</v>
+      </c>
+      <c r="N22" s="3">
+        <v>24200</v>
+      </c>
+      <c r="O22" s="3">
+        <v>44800</v>
+      </c>
+      <c r="P22" s="3">
+        <v>49900</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>49300</v>
+      </c>
+      <c r="R22" s="3">
+        <v>46000</v>
+      </c>
+      <c r="S22" s="3">
+        <v>37500</v>
+      </c>
+      <c r="T22" s="3">
+        <v>39300</v>
+      </c>
+      <c r="U22" s="3">
+        <v>39100</v>
+      </c>
+      <c r="V22" s="3">
+        <v>41000</v>
+      </c>
+      <c r="W22" s="3">
+        <v>42600</v>
+      </c>
+      <c r="X22" s="3">
         <v>39700</v>
       </c>
-      <c r="H22" s="3">
-        <v>39300</v>
-      </c>
-      <c r="I22" s="3">
-        <v>40300</v>
-      </c>
-      <c r="J22" s="3">
-        <v>24800</v>
-      </c>
-      <c r="K22" s="3">
-        <v>25100</v>
-      </c>
-      <c r="L22" s="3">
-        <v>25300</v>
-      </c>
-      <c r="M22" s="3">
-        <v>24200</v>
-      </c>
-      <c r="N22" s="3">
-        <v>44800</v>
-      </c>
-      <c r="O22" s="3">
-        <v>49900</v>
-      </c>
-      <c r="P22" s="3">
-        <v>49300</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>46000</v>
-      </c>
-      <c r="R22" s="3">
-        <v>37500</v>
-      </c>
-      <c r="S22" s="3">
-        <v>39300</v>
-      </c>
-      <c r="T22" s="3">
-        <v>39100</v>
-      </c>
-      <c r="U22" s="3">
-        <v>41000</v>
-      </c>
-      <c r="V22" s="3">
-        <v>42600</v>
-      </c>
-      <c r="W22" s="3">
-        <v>39700</v>
-      </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>37900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>20600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>8900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>2200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>1300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>1200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>6300</v>
       </c>
-      <c r="AE22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AF22" s="3">
+      <c r="AF22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG22" s="3">
         <v>12200</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>9900</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>6100</v>
       </c>
-      <c r="AI22" s="3" t="s">
+      <c r="AJ22" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>14300</v>
+        <v>35300</v>
       </c>
       <c r="E23" s="3">
-        <v>96400</v>
+        <v>14000</v>
       </c>
       <c r="F23" s="3">
+        <v>94700</v>
+      </c>
+      <c r="G23" s="3">
         <v>72500</v>
       </c>
-      <c r="G23" s="3">
-        <v>69400</v>
-      </c>
       <c r="H23" s="3">
-        <v>53000</v>
+        <v>67500</v>
       </c>
       <c r="I23" s="3">
-        <v>91700</v>
+        <v>51800</v>
       </c>
       <c r="J23" s="3">
+        <v>94700</v>
+      </c>
+      <c r="K23" s="3">
         <v>41300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-48700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-23000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>26300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-238700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-241400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-193600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-172100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-215500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-166900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-209600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-449400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-377800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-570700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-351100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-276100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-487900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-438200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-293400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-56900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-89300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-156000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-141400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-162700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-137200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-91300</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E24" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F24" s="3">
+        <v>2400</v>
+      </c>
+      <c r="G24" s="3">
+        <v>5400</v>
+      </c>
+      <c r="H24" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I24" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J24" s="3">
         <v>3600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="K24" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="L24" s="3">
+        <v>5900</v>
+      </c>
+      <c r="M24" s="3">
+        <v>5000</v>
+      </c>
+      <c r="N24" s="3">
+        <v>2300</v>
+      </c>
+      <c r="O24" s="3">
+        <v>5000</v>
+      </c>
+      <c r="P24" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>4400</v>
+      </c>
+      <c r="R24" s="3">
+        <v>2900</v>
+      </c>
+      <c r="S24" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="T24" s="3">
+        <v>2800</v>
+      </c>
+      <c r="U24" s="3">
+        <v>2300</v>
+      </c>
+      <c r="V24" s="3">
+        <v>800</v>
+      </c>
+      <c r="W24" s="3">
+        <v>3500</v>
+      </c>
+      <c r="X24" s="3">
         <v>2500</v>
       </c>
-      <c r="F24" s="3">
-        <v>5400</v>
-      </c>
-      <c r="G24" s="3">
-        <v>1300</v>
-      </c>
-      <c r="H24" s="3">
+      <c r="Y24" s="3">
+        <v>900</v>
+      </c>
+      <c r="Z24" s="3">
         <v>1100</v>
       </c>
-      <c r="I24" s="3">
-        <v>3500</v>
-      </c>
-      <c r="J24" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="K24" s="3">
-        <v>5900</v>
-      </c>
-      <c r="L24" s="3">
-        <v>5000</v>
-      </c>
-      <c r="M24" s="3">
-        <v>2300</v>
-      </c>
-      <c r="N24" s="3">
-        <v>5000</v>
-      </c>
-      <c r="O24" s="3">
-        <v>1300</v>
-      </c>
-      <c r="P24" s="3">
-        <v>4400</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>2900</v>
-      </c>
-      <c r="R24" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="S24" s="3">
-        <v>2800</v>
-      </c>
-      <c r="T24" s="3">
-        <v>2300</v>
-      </c>
-      <c r="U24" s="3">
-        <v>800</v>
-      </c>
-      <c r="V24" s="3">
-        <v>3500</v>
-      </c>
-      <c r="W24" s="3">
-        <v>2500</v>
-      </c>
-      <c r="X24" s="3">
-        <v>900</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>1100</v>
-      </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>11500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-1400</v>
-      </c>
-      <c r="AE24" s="3">
-        <v>100</v>
       </c>
       <c r="AF24" s="3">
         <v>100</v>
@@ -2316,13 +2362,16 @@
         <v>100</v>
       </c>
       <c r="AH24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI24" s="3">
         <v>600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>10700</v>
+        <v>33600</v>
       </c>
       <c r="E26" s="3">
-        <v>93900</v>
+        <v>10400</v>
       </c>
       <c r="F26" s="3">
+        <v>92200</v>
+      </c>
+      <c r="G26" s="3">
         <v>67000</v>
       </c>
-      <c r="G26" s="3">
-        <v>68200</v>
-      </c>
       <c r="H26" s="3">
-        <v>51900</v>
+        <v>66300</v>
       </c>
       <c r="I26" s="3">
-        <v>88200</v>
+        <v>50700</v>
       </c>
       <c r="J26" s="3">
+        <v>91100</v>
+      </c>
+      <c r="K26" s="3">
         <v>42900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-54600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-28000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>24000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-243700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-242700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-198000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-175000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-213300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-169600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-212000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-450100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-381200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-573200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-352000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-277200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-499400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-437300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-294100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-56900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-87900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-156100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-141500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-162800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-137800</v>
       </c>
-      <c r="AI26" s="3" t="s">
+      <c r="AJ26" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>9700</v>
+        <v>32700</v>
       </c>
       <c r="E27" s="3">
-        <v>92400</v>
+        <v>9500</v>
       </c>
       <c r="F27" s="3">
-        <v>65700</v>
+        <v>90800</v>
       </c>
       <c r="G27" s="3">
-        <v>67100</v>
+        <v>65800</v>
       </c>
       <c r="H27" s="3">
-        <v>51500</v>
+        <v>65200</v>
       </c>
       <c r="I27" s="3">
-        <v>87100</v>
+        <v>50400</v>
       </c>
       <c r="J27" s="3">
+        <v>90000</v>
+      </c>
+      <c r="K27" s="3">
         <v>42900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-54700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-29700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>23300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-246300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-246500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-201300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-176800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-215700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-171700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-212700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-450300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-384200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-575400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-355600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-275900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-504900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-439500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-294800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-98300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>2198300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-1737000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-248500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-267600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-410200</v>
       </c>
-      <c r="AI27" s="3" t="s">
+      <c r="AJ27" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,210 +3095,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-6700</v>
+        <v>27900</v>
       </c>
       <c r="E32" s="3">
         <v>-2900</v>
       </c>
       <c r="F32" s="3">
-        <v>-3400</v>
+        <v>-5200</v>
       </c>
       <c r="G32" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="K32" s="3">
+        <v>44300</v>
+      </c>
+      <c r="L32" s="3">
+        <v>66400</v>
+      </c>
+      <c r="M32" s="3">
+        <v>15200</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-37700</v>
+      </c>
+      <c r="O32" s="3">
+        <v>59200</v>
+      </c>
+      <c r="P32" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>-16800</v>
+      </c>
+      <c r="R32" s="3">
+        <v>-15100</v>
+      </c>
+      <c r="S32" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="T32" s="3">
+        <v>-49100</v>
+      </c>
+      <c r="U32" s="3">
+        <v>-18400</v>
+      </c>
+      <c r="V32" s="3">
+        <v>57400</v>
+      </c>
+      <c r="W32" s="3">
+        <v>-54200</v>
+      </c>
+      <c r="X32" s="3">
+        <v>89300</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>27300</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>-52700</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-3800</v>
       </c>
-      <c r="H32" s="3">
-        <v>-6200</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-11000</v>
-      </c>
-      <c r="J32" s="3">
-        <v>44300</v>
-      </c>
-      <c r="K32" s="3">
-        <v>66400</v>
-      </c>
-      <c r="L32" s="3">
-        <v>15200</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-37700</v>
-      </c>
-      <c r="N32" s="3">
-        <v>59200</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-16800</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-15100</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-3900</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-49100</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-18400</v>
-      </c>
-      <c r="U32" s="3">
-        <v>57400</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-54200</v>
-      </c>
-      <c r="W32" s="3">
-        <v>89300</v>
-      </c>
-      <c r="X32" s="3">
-        <v>27300</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>-52700</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>73300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>106200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-96800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-39800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-2300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-17900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>1600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>20200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>9700</v>
+        <v>32700</v>
       </c>
       <c r="E33" s="3">
-        <v>92400</v>
+        <v>9500</v>
       </c>
       <c r="F33" s="3">
-        <v>65700</v>
+        <v>90800</v>
       </c>
       <c r="G33" s="3">
-        <v>67100</v>
+        <v>65800</v>
       </c>
       <c r="H33" s="3">
-        <v>51500</v>
+        <v>65200</v>
       </c>
       <c r="I33" s="3">
-        <v>87100</v>
+        <v>50400</v>
       </c>
       <c r="J33" s="3">
+        <v>90000</v>
+      </c>
+      <c r="K33" s="3">
         <v>42900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-54700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-29700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>23300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-246300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-246500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-201300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-176800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-215700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-171700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-212700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-450300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-384200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-575400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-355600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-275900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-504900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-439500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-294800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-98300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>2198300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-1737000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-248500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-267600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-410200</v>
       </c>
-      <c r="AI33" s="3" t="s">
+      <c r="AJ33" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>9700</v>
+        <v>32700</v>
       </c>
       <c r="E35" s="3">
-        <v>92400</v>
+        <v>9500</v>
       </c>
       <c r="F35" s="3">
-        <v>65700</v>
+        <v>90800</v>
       </c>
       <c r="G35" s="3">
-        <v>67100</v>
+        <v>65800</v>
       </c>
       <c r="H35" s="3">
-        <v>51500</v>
+        <v>65200</v>
       </c>
       <c r="I35" s="3">
-        <v>87100</v>
+        <v>50400</v>
       </c>
       <c r="J35" s="3">
+        <v>90000</v>
+      </c>
+      <c r="K35" s="3">
         <v>42900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-54700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-29700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>23300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-246300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-246500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-201300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-176800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-215700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-171700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-212700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-450300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-384200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-575400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-355600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-275900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-504900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-439500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-294800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-98300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>2198300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-1737000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-248500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-267600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-410200</v>
       </c>
-      <c r="AI35" s="3" t="s">
+      <c r="AJ35" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,98 +3698,99 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>888400</v>
+        <v>462100</v>
       </c>
       <c r="E41" s="3">
-        <v>711300</v>
+        <v>867200</v>
       </c>
       <c r="F41" s="3">
-        <v>625200</v>
+        <v>698700</v>
       </c>
       <c r="G41" s="3">
-        <v>596400</v>
+        <v>625400</v>
       </c>
       <c r="H41" s="3">
-        <v>502600</v>
+        <v>579800</v>
       </c>
       <c r="I41" s="3">
-        <v>638500</v>
+        <v>491600</v>
       </c>
       <c r="J41" s="3">
+        <v>659400</v>
+      </c>
+      <c r="K41" s="3">
         <v>1000700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>491800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>406400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>526300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>413900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1037100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>960100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1023500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1519400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>461900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>630800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>578200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>913800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>702900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>829200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1806300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>666100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>816200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1159100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>57900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>105200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>176500</v>
       </c>
-      <c r="AF41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AG41" s="3" t="s">
         <v>16</v>
       </c>
@@ -3713,98 +3800,101 @@
       <c r="AI41" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ41" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>103700</v>
+        <v>133500</v>
       </c>
       <c r="E42" s="3">
-        <v>139000</v>
+        <v>101300</v>
       </c>
       <c r="F42" s="3">
+        <v>136600</v>
+      </c>
+      <c r="G42" s="3">
         <v>132800</v>
       </c>
-      <c r="G42" s="3">
-        <v>144500</v>
-      </c>
       <c r="H42" s="3">
-        <v>143100</v>
+        <v>140500</v>
       </c>
       <c r="I42" s="3">
-        <v>94300</v>
+        <v>139900</v>
       </c>
       <c r="J42" s="3">
+        <v>97400</v>
+      </c>
+      <c r="K42" s="3">
         <v>115400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>203200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>262800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>177100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>186200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>520500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>793700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>823300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>467500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>526300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>618400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>823300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>705100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1067400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1347200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>591100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>880400</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>538000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>665100</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>70700</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>111900</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>497500</v>
       </c>
-      <c r="AF42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AG42" s="3" t="s">
         <v>16</v>
       </c>
@@ -3814,98 +3904,101 @@
       <c r="AI42" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ42" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>374900</v>
+        <v>365100</v>
       </c>
       <c r="E43" s="3">
-        <v>626500</v>
+        <v>366000</v>
       </c>
       <c r="F43" s="3">
-        <v>546400</v>
+        <v>615500</v>
       </c>
       <c r="G43" s="3">
-        <v>377300</v>
+        <v>847400</v>
       </c>
       <c r="H43" s="3">
-        <v>402100</v>
+        <v>366700</v>
       </c>
       <c r="I43" s="3">
-        <v>408000</v>
+        <v>393300</v>
       </c>
       <c r="J43" s="3">
+        <v>421300</v>
+      </c>
+      <c r="K43" s="3">
         <v>353400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>380500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>359000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>388200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>400900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>448800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>478900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>494800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>478900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>500900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>503700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>717100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>591200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>514100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>513100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>535000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>460500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>452200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>350200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>420800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>322200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>693700</v>
       </c>
-      <c r="AF43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AG43" s="3" t="s">
         <v>16</v>
       </c>
@@ -3915,98 +4008,101 @@
       <c r="AI43" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ43" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>90400</v>
-      </c>
-      <c r="E44" s="3">
-        <v>102200</v>
-      </c>
-      <c r="F44" s="3">
-        <v>82100</v>
-      </c>
-      <c r="G44" s="3">
-        <v>98300</v>
-      </c>
-      <c r="H44" s="3">
-        <v>117300</v>
-      </c>
-      <c r="I44" s="3">
-        <v>132600</v>
-      </c>
-      <c r="J44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K44" s="3">
         <v>105200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>113000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>110700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>125700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>128600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>155900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>127900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>143600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>144100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>182200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>174500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>224300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>188600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>206500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>179700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>191900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>169000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>147200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>162900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>172400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>117500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>110300</v>
       </c>
-      <c r="AF44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AG44" s="3" t="s">
         <v>16</v>
       </c>
@@ -4016,98 +4112,101 @@
       <c r="AI44" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ44" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>340500</v>
+        <v>402800</v>
       </c>
       <c r="E45" s="3">
-        <v>366900</v>
+        <v>420600</v>
       </c>
       <c r="F45" s="3">
-        <v>394800</v>
+        <v>460800</v>
       </c>
       <c r="G45" s="3">
-        <v>417200</v>
+        <v>175400</v>
       </c>
       <c r="H45" s="3">
-        <v>376500</v>
+        <v>500300</v>
       </c>
       <c r="I45" s="3">
-        <v>1582800</v>
+        <v>482100</v>
       </c>
       <c r="J45" s="3">
+        <v>1770400</v>
+      </c>
+      <c r="K45" s="3">
         <v>368900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>310100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>308700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>381200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>461800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>540900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>588900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>597800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>492900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>601500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>679700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>690600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>722800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1031300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>926000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>772700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>707300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>430500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>377800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>145500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>161200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>137200</v>
       </c>
-      <c r="AF45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AG45" s="3" t="s">
         <v>16</v>
       </c>
@@ -4117,98 +4216,101 @@
       <c r="AI45" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ45" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1798000</v>
+        <v>1363500</v>
       </c>
       <c r="E46" s="3">
-        <v>1945900</v>
+        <v>1755100</v>
       </c>
       <c r="F46" s="3">
-        <v>1781300</v>
+        <v>1911600</v>
       </c>
       <c r="G46" s="3">
-        <v>1633700</v>
+        <v>1781900</v>
       </c>
       <c r="H46" s="3">
-        <v>1541600</v>
+        <v>1588200</v>
       </c>
       <c r="I46" s="3">
-        <v>2856300</v>
+        <v>1507800</v>
       </c>
       <c r="J46" s="3">
+        <v>2949400</v>
+      </c>
+      <c r="K46" s="3">
         <v>1943500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1498600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1447600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1598500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1591300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2703300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2949500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3083100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3102800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2272700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2607100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3033400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3121600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3522200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3795200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3897100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2883300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2384200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2715100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>867300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>817900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1615200</v>
       </c>
-      <c r="AF46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AG46" s="3" t="s">
         <v>16</v>
       </c>
@@ -4218,98 +4320,101 @@
       <c r="AI46" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ46" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>532100</v>
+        <v>292900</v>
       </c>
       <c r="E47" s="3">
-        <v>346400</v>
+        <v>298900</v>
       </c>
       <c r="F47" s="3">
-        <v>341100</v>
+        <v>307200</v>
       </c>
       <c r="G47" s="3">
-        <v>354300</v>
+        <v>318800</v>
       </c>
       <c r="H47" s="3">
-        <v>357400</v>
+        <v>324100</v>
       </c>
       <c r="I47" s="3">
-        <v>327100</v>
+        <v>325400</v>
       </c>
       <c r="J47" s="3">
+        <v>323800</v>
+      </c>
+      <c r="K47" s="3">
         <v>354400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>403100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>448400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>452500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>430300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>499900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>503200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>485900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>451300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>577200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>579900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>580200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>485700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>480400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>413700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>400600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>381200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>322800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>173900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>170000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>81500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>59000</v>
       </c>
-      <c r="AF47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AG47" s="3" t="s">
         <v>16</v>
       </c>
@@ -4319,98 +4424,101 @@
       <c r="AI47" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ47" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>210300</v>
+        <v>208300</v>
       </c>
       <c r="E48" s="3">
-        <v>212400</v>
+        <v>205300</v>
       </c>
       <c r="F48" s="3">
-        <v>218200</v>
+        <v>208600</v>
       </c>
       <c r="G48" s="3">
-        <v>217700</v>
+        <v>218300</v>
       </c>
       <c r="H48" s="3">
-        <v>227900</v>
+        <v>211600</v>
       </c>
       <c r="I48" s="3">
-        <v>238300</v>
+        <v>222900</v>
       </c>
       <c r="J48" s="3">
+        <v>246100</v>
+      </c>
+      <c r="K48" s="3">
         <v>250800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>260400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>292000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>302900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>311000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>320700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>345200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>323500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>333400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>360000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>408400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>402000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>381400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>369600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>358100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>265700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>235000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>206500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>196600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>189200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>179200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>179600</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AG48" s="3" t="s">
         <v>16</v>
       </c>
@@ -4420,98 +4528,101 @@
       <c r="AI48" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ48" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>3578700</v>
+        <v>1567200</v>
       </c>
       <c r="E49" s="3">
-        <v>3480500</v>
+        <v>1521400</v>
       </c>
       <c r="F49" s="3">
-        <v>3450300</v>
+        <v>1533800</v>
       </c>
       <c r="G49" s="3">
-        <v>3359300</v>
+        <v>1564900</v>
       </c>
       <c r="H49" s="3">
-        <v>3298600</v>
+        <v>1535300</v>
       </c>
       <c r="I49" s="3">
-        <v>3319400</v>
+        <v>1472000</v>
       </c>
       <c r="J49" s="3">
+        <v>1592700</v>
+      </c>
+      <c r="K49" s="3">
         <v>3398400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3344300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3291500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3244400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3126500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3033800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2854200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2546200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2436900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2355300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2174600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2369400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2362800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2601800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2423100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>2432100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2315500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>2285000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1858100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1623800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1409900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1221500</v>
       </c>
-      <c r="AF49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AG49" s="3" t="s">
         <v>16</v>
       </c>
@@ -4521,8 +4632,11 @@
       <c r="AI49" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ49" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,98 +4840,101 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>598300</v>
+        <v>2959200</v>
       </c>
       <c r="E52" s="3">
-        <v>542100</v>
+        <v>2776200</v>
       </c>
       <c r="F52" s="3">
-        <v>496000</v>
+        <v>2451100</v>
       </c>
       <c r="G52" s="3">
-        <v>653000</v>
+        <v>2405000</v>
       </c>
       <c r="H52" s="3">
-        <v>649200</v>
+        <v>2385400</v>
       </c>
       <c r="I52" s="3">
-        <v>594500</v>
+        <v>2413300</v>
       </c>
       <c r="J52" s="3">
+        <v>2462800</v>
+      </c>
+      <c r="K52" s="3">
         <v>544900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>419600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>441300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>420100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>405500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>449900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>373200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>380400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>382900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>405700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>460100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>431800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>545600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>562800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>686200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>787200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>685500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>570200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>530500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>439700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>409900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>378500</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AG52" s="3" t="s">
         <v>16</v>
       </c>
@@ -4824,8 +4944,11 @@
       <c r="AI52" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ52" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,98 +5048,101 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>6717500</v>
+        <v>6391100</v>
       </c>
       <c r="E54" s="3">
-        <v>6527300</v>
+        <v>6556900</v>
       </c>
       <c r="F54" s="3">
-        <v>6286900</v>
+        <v>6412300</v>
       </c>
       <c r="G54" s="3">
-        <v>6218000</v>
+        <v>6289000</v>
       </c>
       <c r="H54" s="3">
-        <v>6074700</v>
+        <v>6044700</v>
       </c>
       <c r="I54" s="3">
-        <v>7335600</v>
+        <v>5941400</v>
       </c>
       <c r="J54" s="3">
+        <v>7574800</v>
+      </c>
+      <c r="K54" s="3">
         <v>6491900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5926000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5920800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6018500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5864600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7007500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7025300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6819100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6707400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5970900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6230000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6816800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6897200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>7536800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>7676300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>7782700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6500500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>5768700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>5474100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>3289900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2898400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>3453700</v>
       </c>
-      <c r="AF54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AG54" s="3" t="s">
         <v>16</v>
       </c>
@@ -5026,8 +5152,11 @@
       <c r="AI54" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ54" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,98 +5230,99 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>841600</v>
+        <v>924700</v>
       </c>
       <c r="E57" s="3">
-        <v>831400</v>
+        <v>821500</v>
       </c>
       <c r="F57" s="3">
-        <v>799500</v>
+        <v>816700</v>
       </c>
       <c r="G57" s="3">
-        <v>836900</v>
+        <v>799800</v>
       </c>
       <c r="H57" s="3">
-        <v>809200</v>
+        <v>813500</v>
       </c>
       <c r="I57" s="3">
-        <v>806600</v>
+        <v>791500</v>
       </c>
       <c r="J57" s="3">
+        <v>832900</v>
+      </c>
+      <c r="K57" s="3">
         <v>845000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>950800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>877400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>969600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1228400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1297500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1181700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1045200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1052600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1088800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1133500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1304000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1264600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1574100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1464200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1574600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1475900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1458800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1269100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1252000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1010300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1035600</v>
       </c>
-      <c r="AF57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AG57" s="3" t="s">
         <v>16</v>
       </c>
@@ -5201,98 +5332,101 @@
       <c r="AI57" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ57" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1012800</v>
+        <v>640700</v>
       </c>
       <c r="E58" s="3">
-        <v>902000</v>
+        <v>1001900</v>
       </c>
       <c r="F58" s="3">
-        <v>898600</v>
+        <v>899500</v>
       </c>
       <c r="G58" s="3">
-        <v>912900</v>
+        <v>922800</v>
       </c>
       <c r="H58" s="3">
-        <v>425100</v>
+        <v>900500</v>
       </c>
       <c r="I58" s="3">
-        <v>1625100</v>
+        <v>429600</v>
       </c>
       <c r="J58" s="3">
+        <v>1692600</v>
+      </c>
+      <c r="K58" s="3">
         <v>1642900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1721400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1678900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>606400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>568600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1344000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1249600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1102100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1200900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>662600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>601300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>519500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>516600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>604300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>667800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>557600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>454600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>165500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>89900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>58400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>44400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1232000</v>
       </c>
-      <c r="AF58" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AG58" s="3" t="s">
         <v>16</v>
       </c>
@@ -5302,98 +5436,101 @@
       <c r="AI58" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ58" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1531600</v>
+        <v>1081800</v>
       </c>
       <c r="E59" s="3">
-        <v>1508400</v>
+        <v>1060900</v>
       </c>
       <c r="F59" s="3">
-        <v>1451600</v>
+        <v>1037300</v>
       </c>
       <c r="G59" s="3">
-        <v>1435900</v>
+        <v>878300</v>
       </c>
       <c r="H59" s="3">
-        <v>1407300</v>
+        <v>1040600</v>
       </c>
       <c r="I59" s="3">
-        <v>1470100</v>
+        <v>1035500</v>
       </c>
       <c r="J59" s="3">
+        <v>1117700</v>
+      </c>
+      <c r="K59" s="3">
         <v>1478000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1355000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1358100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1389900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1306500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1331100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1335500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1355800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1206300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1242700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1281200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1445100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1325100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1178200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1144200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1013800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>946900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>887200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>710200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>619500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>613400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1325600</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AG59" s="3" t="s">
         <v>16</v>
       </c>
@@ -5403,98 +5540,101 @@
       <c r="AI59" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ59" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>3386000</v>
+        <v>3058200</v>
       </c>
       <c r="E60" s="3">
-        <v>3241700</v>
+        <v>3305000</v>
       </c>
       <c r="F60" s="3">
-        <v>3149700</v>
+        <v>3184600</v>
       </c>
       <c r="G60" s="3">
-        <v>3185600</v>
+        <v>3150700</v>
       </c>
       <c r="H60" s="3">
-        <v>2641700</v>
+        <v>3096800</v>
       </c>
       <c r="I60" s="3">
-        <v>3901800</v>
+        <v>2583700</v>
       </c>
       <c r="J60" s="3">
+        <v>4029100</v>
+      </c>
+      <c r="K60" s="3">
         <v>3965800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4027300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3914400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2965900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3103600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3972600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3766800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3503200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3459800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2994100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3016000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3268600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3106300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3356700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3276200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3146000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2877300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2511500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2069200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1929900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1668000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>3593200</v>
       </c>
-      <c r="AF60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AG60" s="3" t="s">
         <v>16</v>
       </c>
@@ -5504,98 +5644,101 @@
       <c r="AI60" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ60" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1238800</v>
+        <v>1304300</v>
       </c>
       <c r="E61" s="3">
-        <v>1224300</v>
+        <v>1276600</v>
       </c>
       <c r="F61" s="3">
-        <v>1162000</v>
+        <v>1271900</v>
       </c>
       <c r="G61" s="3">
-        <v>1177100</v>
+        <v>1236200</v>
       </c>
       <c r="H61" s="3">
-        <v>1613800</v>
+        <v>1209300</v>
       </c>
       <c r="I61" s="3">
-        <v>1645000</v>
+        <v>1645900</v>
       </c>
       <c r="J61" s="3">
+        <v>1769800</v>
+      </c>
+      <c r="K61" s="3">
         <v>1348900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>880100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>832800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1828100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1747000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1801200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1808500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1763700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1660200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1889000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2001200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2112200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2029000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2057800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1879700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1856600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>777900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>38300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>39000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>40000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>40700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>42100</v>
       </c>
-      <c r="AF61" s="3">
-        <v>0</v>
-      </c>
       <c r="AG61" s="3">
         <v>0</v>
       </c>
@@ -5605,98 +5748,101 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>256100</v>
+        <v>135500</v>
       </c>
       <c r="E62" s="3">
-        <v>261100</v>
+        <v>182700</v>
       </c>
       <c r="F62" s="3">
-        <v>257400</v>
+        <v>187200</v>
       </c>
       <c r="G62" s="3">
-        <v>255800</v>
+        <v>172700</v>
       </c>
       <c r="H62" s="3">
-        <v>304900</v>
+        <v>183400</v>
       </c>
       <c r="I62" s="3">
-        <v>287100</v>
+        <v>230500</v>
       </c>
       <c r="J62" s="3">
+        <v>225200</v>
+      </c>
+      <c r="K62" s="3">
         <v>282900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>265600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>288800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>271600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>230700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>232500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>253100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>258600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>272800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>288000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>290300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>281500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>266000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>220700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>225900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>248700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>208500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>210000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>97000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>96100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1100</v>
       </c>
-      <c r="AF62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AG62" s="3" t="s">
         <v>16</v>
       </c>
@@ -5706,8 +5852,11 @@
       <c r="AI62" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ62" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,98 +6164,101 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>4889900</v>
+        <v>4498000</v>
       </c>
       <c r="E66" s="3">
-        <v>4735000</v>
+        <v>4764300</v>
       </c>
       <c r="F66" s="3">
-        <v>4583000</v>
+        <v>4643700</v>
       </c>
       <c r="G66" s="3">
-        <v>4631100</v>
+        <v>4570600</v>
       </c>
       <c r="H66" s="3">
-        <v>4572000</v>
+        <v>4489700</v>
       </c>
       <c r="I66" s="3">
-        <v>5845500</v>
+        <v>4460300</v>
       </c>
       <c r="J66" s="3">
+        <v>6024200</v>
+      </c>
+      <c r="K66" s="3">
         <v>5610700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5186000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5048800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5075000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5148300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6071100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5873200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5566700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5418900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5194800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5329500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5684500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5423400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5659900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5402400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5268100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3880900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2771200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2205600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2066400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1710600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3636400</v>
       </c>
-      <c r="AF66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AG66" s="3" t="s">
         <v>16</v>
       </c>
@@ -6110,8 +6268,11 @@
       <c r="AI66" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ66" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6430,17 +6598,17 @@
         <v>0</v>
       </c>
       <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD70" s="3">
         <v>3284400</v>
       </c>
-      <c r="AD70" s="3">
+      <c r="AE70" s="3">
         <v>3242900</v>
       </c>
-      <c r="AE70" s="3">
+      <c r="AF70" s="3">
         <v>4323600</v>
       </c>
-      <c r="AF70" s="3">
-        <v>0</v>
-      </c>
       <c r="AG70" s="3">
         <v>0</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,98 +6722,101 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-6181900</v>
+        <v>-6218500</v>
       </c>
       <c r="E72" s="3">
-        <v>-6191600</v>
+        <v>-6034100</v>
       </c>
       <c r="F72" s="3">
-        <v>-6284000</v>
+        <v>-6082400</v>
       </c>
       <c r="G72" s="3">
-        <v>-6349700</v>
+        <v>-6286000</v>
       </c>
       <c r="H72" s="3">
-        <v>-6416800</v>
+        <v>-6172700</v>
       </c>
       <c r="I72" s="3">
-        <v>-6468300</v>
+        <v>-6276000</v>
       </c>
       <c r="J72" s="3">
+        <v>-6679200</v>
+      </c>
+      <c r="K72" s="3">
         <v>-6555400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-6466300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-6451600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-6378400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-6512400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-6450800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-6268400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-5880400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-5703600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-5757100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-5636300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-5750400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-5209800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-4889200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-4224500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-3852200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-3414300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-2796700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-2357100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-2130900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-2154600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-4631600</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AG72" s="3" t="s">
         <v>16</v>
       </c>
@@ -6652,8 +6826,11 @@
       <c r="AI72" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ72" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,98 +7138,101 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1827500</v>
+        <v>1883100</v>
       </c>
       <c r="E76" s="3">
-        <v>1792400</v>
+        <v>1783900</v>
       </c>
       <c r="F76" s="3">
-        <v>1704000</v>
+        <v>1760800</v>
       </c>
       <c r="G76" s="3">
-        <v>1586900</v>
+        <v>1704500</v>
       </c>
       <c r="H76" s="3">
-        <v>1502700</v>
+        <v>1542600</v>
       </c>
       <c r="I76" s="3">
-        <v>1490000</v>
+        <v>1469800</v>
       </c>
       <c r="J76" s="3">
+        <v>1538600</v>
+      </c>
+      <c r="K76" s="3">
         <v>881200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>740000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>872000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>943500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>716300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>936400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1152200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1252400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1288500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>776100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>900500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1132300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1473700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1876900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2273900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2514600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2619500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2997500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>3268500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-2060900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-2055000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-4506300</v>
       </c>
-      <c r="AF76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AG76" s="3" t="s">
         <v>16</v>
       </c>
@@ -7056,8 +7242,11 @@
       <c r="AI76" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ76" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>9700</v>
+        <v>32700</v>
       </c>
       <c r="E81" s="3">
-        <v>92400</v>
+        <v>9500</v>
       </c>
       <c r="F81" s="3">
-        <v>65700</v>
+        <v>90800</v>
       </c>
       <c r="G81" s="3">
-        <v>67100</v>
+        <v>65800</v>
       </c>
       <c r="H81" s="3">
-        <v>51500</v>
+        <v>65200</v>
       </c>
       <c r="I81" s="3">
-        <v>87100</v>
+        <v>50400</v>
       </c>
       <c r="J81" s="3">
+        <v>90000</v>
+      </c>
+      <c r="K81" s="3">
         <v>42900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-54700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-29700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>23300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-246300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-246500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-201300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-176800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-215700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-171700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-212700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-450300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-384200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-575400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-355600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-275900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-504900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-439500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-294800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-98300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>2198300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-1737000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-248500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-267600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-410200</v>
       </c>
-      <c r="AI81" s="3" t="s">
+      <c r="AJ81" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,31 +7599,32 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+        <v>48900</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -7493,8 +7692,8 @@
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>16</v>
+      <c r="AG83" s="3">
+        <v>0</v>
       </c>
       <c r="AH83" s="3" t="s">
         <v>16</v>
@@ -7502,8 +7701,11 @@
       <c r="AI83" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ83" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,68 +8221,71 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>57900</v>
+        <v>34600</v>
       </c>
       <c r="E89" s="3">
-        <v>132200</v>
+        <v>56500</v>
       </c>
       <c r="F89" s="3">
-        <v>89300</v>
+        <v>129900</v>
       </c>
       <c r="G89" s="3">
-        <v>117100</v>
+        <v>89400</v>
       </c>
       <c r="H89" s="3">
-        <v>124800</v>
+        <v>113800</v>
       </c>
       <c r="I89" s="3">
-        <v>141200</v>
+        <v>122100</v>
       </c>
       <c r="J89" s="3">
+        <v>145800</v>
+      </c>
+      <c r="K89" s="3">
         <v>120300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>27000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>6600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-161100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-151200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-295700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-204800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-187900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-211500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-281700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-200200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-94600</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>16</v>
       </c>
@@ -8081,8 +8298,8 @@
       <c r="Z89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA89" s="3">
-        <v>0</v>
+      <c r="AA89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AB89" s="3">
         <v>0</v>
@@ -8099,8 +8316,8 @@
       <c r="AF89" s="3">
         <v>0</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>16</v>
+      <c r="AG89" s="3">
+        <v>0</v>
       </c>
       <c r="AH89" s="3" t="s">
         <v>16</v>
@@ -8108,8 +8325,11 @@
       <c r="AI89" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ89" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,38 +8365,39 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-28300</v>
+        <v>-1100</v>
       </c>
       <c r="E91" s="3">
-        <v>-4700</v>
+        <v>-3900</v>
       </c>
       <c r="F91" s="3">
-        <v>-4200</v>
+        <v>-3100</v>
       </c>
       <c r="G91" s="3">
-        <v>-13300</v>
+        <v>-2700</v>
       </c>
       <c r="H91" s="3">
-        <v>-200</v>
+        <v>-600</v>
       </c>
       <c r="I91" s="3">
-        <v>-8800</v>
+        <v>-1800</v>
       </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-48100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-66000</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
@@ -8186,8 +8407,8 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>16</v>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>16</v>
@@ -8198,8 +8419,8 @@
       <c r="S91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
+      <c r="T91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
@@ -8237,8 +8458,8 @@
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-      <c r="AG91" s="3" t="s">
-        <v>16</v>
+      <c r="AG91" s="3">
+        <v>0</v>
       </c>
       <c r="AH91" s="3" t="s">
         <v>16</v>
@@ -8246,8 +8467,11 @@
       <c r="AI91" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ91" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,68 +8675,71 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>47400</v>
+        <v>-237000</v>
       </c>
       <c r="E94" s="3">
-        <v>-31400</v>
+        <v>46300</v>
       </c>
       <c r="F94" s="3">
-        <v>-201700</v>
+        <v>-30900</v>
       </c>
       <c r="G94" s="3">
-        <v>-7800</v>
+        <v>-201800</v>
       </c>
       <c r="H94" s="3">
-        <v>-59300</v>
+        <v>-7600</v>
       </c>
       <c r="I94" s="3">
-        <v>23500</v>
+        <v>-58000</v>
       </c>
       <c r="J94" s="3">
+        <v>24300</v>
+      </c>
+      <c r="K94" s="3">
         <v>81600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>56200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-90700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-9300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>289600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>268000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>8400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-386700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>39200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>50100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>168600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-252000</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>16</v>
       </c>
@@ -8522,8 +8752,8 @@
       <c r="Z94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA94" s="3">
-        <v>0</v>
+      <c r="AA94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AB94" s="3">
         <v>0</v>
@@ -8540,8 +8770,8 @@
       <c r="AF94" s="3">
         <v>0</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>16</v>
+      <c r="AG94" s="3">
+        <v>0</v>
       </c>
       <c r="AH94" s="3" t="s">
         <v>16</v>
@@ -8549,8 +8779,11 @@
       <c r="AI94" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ94" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,31 +8819,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8687,8 +8921,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,68 +9233,71 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>122100</v>
+        <v>-372300</v>
       </c>
       <c r="E100" s="3">
-        <v>36800</v>
+        <v>119200</v>
       </c>
       <c r="F100" s="3">
+        <v>36200</v>
+      </c>
+      <c r="G100" s="3">
         <v>-3200</v>
       </c>
-      <c r="G100" s="3">
-        <v>38000</v>
-      </c>
       <c r="H100" s="3">
-        <v>-165700</v>
+        <v>36900</v>
       </c>
       <c r="I100" s="3">
-        <v>-473200</v>
+        <v>-162000</v>
       </c>
       <c r="J100" s="3">
+        <v>-488600</v>
+      </c>
+      <c r="K100" s="3">
         <v>403400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-14600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-46300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>282600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-723400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>123300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>115100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>85000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1168200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>34800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>121200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-12400</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>16</v>
       </c>
@@ -9064,8 +9310,8 @@
       <c r="Z100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
+      <c r="AA100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AB100" s="3">
         <v>0</v>
@@ -9082,8 +9328,8 @@
       <c r="AF100" s="3">
         <v>0</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>16</v>
+      <c r="AG100" s="3">
+        <v>0</v>
       </c>
       <c r="AH100" s="3" t="s">
         <v>16</v>
@@ -9091,68 +9337,71 @@
       <c r="AI100" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ100" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>3300</v>
+        <v>600</v>
       </c>
       <c r="E101" s="3">
-        <v>2100</v>
+        <v>17600</v>
       </c>
       <c r="F101" s="3">
-        <v>-4400</v>
+        <v>-1300</v>
       </c>
       <c r="G101" s="3">
-        <v>600</v>
+        <v>-1200</v>
       </c>
       <c r="H101" s="3">
-        <v>18000</v>
+        <v>8500</v>
       </c>
       <c r="I101" s="3">
+        <v>11200</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-700</v>
+      </c>
+      <c r="K101" s="3">
         <v>-1200</v>
       </c>
-      <c r="J101" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>8300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>10400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-10200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-3200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-13300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-3900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-4600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-16500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>10100</v>
       </c>
-      <c r="V101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W101" s="3" t="s">
         <v>16</v>
       </c>
@@ -9165,8 +9414,8 @@
       <c r="Z101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
+      <c r="AA101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AB101" s="3">
         <v>0</v>
@@ -9183,8 +9432,8 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-      <c r="AG101" s="3" t="s">
-        <v>16</v>
+      <c r="AG101" s="3">
+        <v>0</v>
       </c>
       <c r="AH101" s="3" t="s">
         <v>16</v>
@@ -9192,68 +9441,71 @@
       <c r="AI101" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ101" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>230600</v>
+        <v>-586700</v>
       </c>
       <c r="E102" s="3">
-        <v>139700</v>
+        <v>225100</v>
       </c>
       <c r="F102" s="3">
+        <v>137200</v>
+      </c>
+      <c r="G102" s="3">
         <v>-120000</v>
       </c>
-      <c r="G102" s="3">
-        <v>147900</v>
-      </c>
       <c r="H102" s="3">
-        <v>-82100</v>
+        <v>143800</v>
       </c>
       <c r="I102" s="3">
-        <v>-309700</v>
+        <v>-80300</v>
       </c>
       <c r="J102" s="3">
+        <v>-319800</v>
+      </c>
+      <c r="K102" s="3">
         <v>604100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>76900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-120000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>111600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-595300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>92400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-94700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-493500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>991300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-213400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>88300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-348900</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>16</v>
       </c>
@@ -9266,8 +9518,8 @@
       <c r="Z102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA102" s="3">
-        <v>0</v>
+      <c r="AA102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AB102" s="3">
         <v>0</v>
@@ -9284,13 +9536,16 @@
       <c r="AF102" s="3">
         <v>0</v>
       </c>
-      <c r="AG102" s="3" t="s">
-        <v>16</v>
+      <c r="AG102" s="3">
+        <v>0</v>
       </c>
       <c r="AH102" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AI102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ102" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IQ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IQ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="92">
   <si>
     <t>IQ</t>
   </si>
@@ -656,467 +656,479 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>906100</v>
+      </c>
+      <c r="E8" s="3">
         <v>1033000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1023700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1097900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1086800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1098500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1075800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1215400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1070400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1032200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>925400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1004800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1020200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1078800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1092700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1109200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1038200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1049600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1092200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1197700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1154300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1154000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1086300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1063300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1020600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>967700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>863600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>699800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>691200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>734700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>642100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>477600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>458800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>473800</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>684200</v>
+      </c>
+      <c r="E9" s="3">
         <v>805500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>781400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>779900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>744600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>800300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>796100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>867100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>761600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>788200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>729600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>823500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>898600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>999000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>986500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>989600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>944400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>929300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1007000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1237300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1218700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1275500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1066600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1107000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1237800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1071400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>854700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>695600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>650700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>726900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1304500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1035100</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>453900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>456800</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>221800</v>
+      </c>
+      <c r="E10" s="3">
         <v>227500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>242300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>318000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>342200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>298200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>279700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>348300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>308800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>244000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>195800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>181300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>121700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>79800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>106200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>119600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>93800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>120400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>85200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>-39600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>-64300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>-121500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>19700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>-43700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>-217200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>-103700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>8900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>4200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>40500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>7800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>-662500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>-557500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>4900</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1153,112 +1165,116 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>61800</v>
+      </c>
+      <c r="E12" s="3">
         <v>64000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>61700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>59500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>63700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>61300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>60500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>62400</v>
-      </c>
-      <c r="K12" s="3">
-        <v>65700</v>
       </c>
       <c r="L12" s="3">
         <v>65700</v>
       </c>
       <c r="M12" s="3">
+        <v>65700</v>
+      </c>
+      <c r="N12" s="3">
         <v>67000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>65600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>105400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>97100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>97200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>93600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>92300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>97800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>97900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>106200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>109500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>109700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>100000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>91000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>88200</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>78100</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>61800</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>55600</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>52300</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>50800</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>87400</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>78200</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>35500</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>33400</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1361,8 +1377,11 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1375,20 +1394,20 @@
       <c r="F14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="3">
         <v>36300</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>16</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1465,35 +1484,38 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>200</v>
+      </c>
+      <c r="E15" s="3">
         <v>268800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>259500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>261100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>265900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>284200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>286000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>301900</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1569,8 +1591,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1629,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>867000</v>
+      </c>
+      <c r="E17" s="3">
         <v>998900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>976600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>967100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>942000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>996100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>991700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1090400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>960000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>989400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>907900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>991900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1154900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1273200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1253800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1250400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1220200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1226300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1281000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1548600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1543700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1595700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1372300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1371500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1503400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1330400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1049400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>852200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>814000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>893000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>789100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>628800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>569700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>557900</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>39100</v>
+      </c>
+      <c r="E18" s="3">
         <v>34100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>47100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>130800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>144800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>102300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>84200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>125000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>110500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>42800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>17500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>12900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-134700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-194500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-161100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-141200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-182000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-176600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-188900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-351000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-389400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-441800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-286000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-308200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-482800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-362700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-185900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-152400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-122800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-158300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-147000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-151200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-110900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-84100</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1850,139 +1882,143 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>42000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-27900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>5200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>3700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>4000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-44300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-66400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-15200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>37700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-59200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>3000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>16800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>15100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>3900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>49100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>18400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-57400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>54200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-89300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-27300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>52700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>3800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-73300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-106200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>96800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>39800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>2300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>17900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-20200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E21" s="3">
         <v>330800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>303700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>386700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>407000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>384100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>369000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>422900</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>16</v>
       </c>
@@ -2040,323 +2076,332 @@
       <c r="AD21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF21" s="3">
         <v>1174600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>835600</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AI21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ21" s="3">
         <v>598900</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>443800</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>32200</v>
+      </c>
+      <c r="E22" s="3">
         <v>36600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>39700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>39100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>40100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>38600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>38400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>41600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>24800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>25100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>25300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>24200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>44800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>49900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>49300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>46000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>37500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>39300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>39100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>41000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>42600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>39700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>37900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>20600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>8900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>2200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>1300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>1200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>6300</v>
       </c>
-      <c r="AF22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG22" s="3">
+      <c r="AG22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH22" s="3">
         <v>12200</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>9900</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>6100</v>
       </c>
-      <c r="AJ22" s="3" t="s">
+      <c r="AK22" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-24800</v>
+      </c>
+      <c r="E23" s="3">
         <v>35300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>14000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>94700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>72500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>67500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>51800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>94700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>41300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-48700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-23000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>26300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-238700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-241400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-193600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-172100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-215500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-166900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-209600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-449400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-377800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-570700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-351100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-276100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-487900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-438200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-293400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-56900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-89300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-156000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-141400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-162700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-137200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-91300</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>900</v>
+      </c>
+      <c r="E24" s="3">
         <v>1600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-1600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>4400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-2300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>3500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>11500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-1400</v>
-      </c>
-      <c r="AF24" s="3">
-        <v>100</v>
       </c>
       <c r="AG24" s="3">
         <v>100</v>
@@ -2365,13 +2410,16 @@
         <v>100</v>
       </c>
       <c r="AI24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ24" s="3">
         <v>600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2522,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-25600</v>
+      </c>
+      <c r="E26" s="3">
         <v>33600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>10400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>92200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>67000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>66300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>50700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>91100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>42900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-54600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-28000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>24000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-243700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-242700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-198000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-175000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-213300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-169600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-212000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-450100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-381200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-573200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-352000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-277200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-499400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-437300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-294100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-56900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-87900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-156100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-141500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-162800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-137800</v>
       </c>
-      <c r="AJ26" s="3" t="s">
+      <c r="AK26" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-25900</v>
+      </c>
+      <c r="E27" s="3">
         <v>32700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>9500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>90800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>65800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>65200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>50400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>90000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>42900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-54700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-29700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>23300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-246300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-246500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-201300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-176800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-215700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-171700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-212700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-450300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-384200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-575400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-355600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-275900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-504900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-439500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-294800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-98300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>2198300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-1737000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-248500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-267600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-410200</v>
       </c>
-      <c r="AJ27" s="3" t="s">
+      <c r="AK27" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2843,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2890,8 +2950,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3057,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,216 +3164,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-42000</v>
+      </c>
+      <c r="E32" s="3">
         <v>27900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-5200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-3700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-4000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>44300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>66400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>15200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-37700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>59200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-16800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-15100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-3900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-49100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-18400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>57400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-54200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>89300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>27300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-52700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>73300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>106200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-96800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-39800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-2300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-17900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>1600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>20200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-25900</v>
+      </c>
+      <c r="E33" s="3">
         <v>32700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>9500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>90800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>65800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>65200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>50400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>90000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>42900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-54700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-29700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>23300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-246300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-246500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-201300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-176800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-215700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-171700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-212700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-450300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-384200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-575400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-355600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-275900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-504900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-439500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-294800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-98300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2198300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-1737000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-248500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-267600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-410200</v>
       </c>
-      <c r="AJ33" s="3" t="s">
+      <c r="AK33" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3485,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-25900</v>
+      </c>
+      <c r="E35" s="3">
         <v>32700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>9500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>90800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>65800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>65200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>50400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>90000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>42900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-54700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-29700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>23300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-246300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-246500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-201300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-176800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-215700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-171700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-212700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-450300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-384200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-575400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-355600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-275900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-504900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-439500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-294800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-98300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2198300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-1737000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-248500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-267600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-410200</v>
       </c>
-      <c r="AJ35" s="3" t="s">
+      <c r="AK35" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3745,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,101 +3784,102 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>483600</v>
+      </c>
+      <c r="E41" s="3">
         <v>462100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>867200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>698700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>625400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>579800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>491600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>659400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1000700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>491800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>406400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>526300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>413900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1037100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>960100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1023500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1519400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>461900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>630800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>578200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>913800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>702900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>829200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1806300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>666100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>816200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1159100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>57900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>105200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>176500</v>
       </c>
-      <c r="AG41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH41" s="3" t="s">
         <v>16</v>
       </c>
@@ -3803,101 +3889,104 @@
       <c r="AJ41" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK41" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>129000</v>
+      </c>
+      <c r="E42" s="3">
         <v>133500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>101300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>136600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>132800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>140500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>139900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>97400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>115400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>203200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>262800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>177100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>186200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>520500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>793700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>823300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>467500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>526300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>618400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>823300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>705100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1067400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1347200</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>591100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>880400</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>538000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>665100</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>70700</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>111900</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>497500</v>
       </c>
-      <c r="AG42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH42" s="3" t="s">
         <v>16</v>
       </c>
@@ -3907,101 +3996,104 @@
       <c r="AJ42" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK42" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>339000</v>
+      </c>
+      <c r="E43" s="3">
         <v>365100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>366000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>615500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>847400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>366700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>393300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>421300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>353400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>380500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>359000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>388200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>400900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>448800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>478900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>494800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>478900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>500900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>503700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>717100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>591200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>514100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>513100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>535000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>460500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>452200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>350200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>420800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>322200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>693700</v>
       </c>
-      <c r="AG43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH43" s="3" t="s">
         <v>16</v>
       </c>
@@ -4011,8 +4103,11 @@
       <c r="AJ43" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK43" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4037,75 +4132,75 @@
       <c r="J44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L44" s="3">
         <v>105200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>113000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>110700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>125700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>128600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>155900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>127900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>143600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>144100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>182200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>174500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>224300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>188600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>206500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>179700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>191900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>169000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>147200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>162900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>172400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>117500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>110300</v>
       </c>
-      <c r="AG44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH44" s="3" t="s">
         <v>16</v>
       </c>
@@ -4115,101 +4210,104 @@
       <c r="AJ44" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK44" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>353700</v>
+      </c>
+      <c r="E45" s="3">
         <v>402800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>420600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>460800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>175400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>500300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>482100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1770400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>368900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>310100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>308700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>381200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>461800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>540900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>588900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>597800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>492900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>601500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>679700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>690600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>722800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1031300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>926000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>772700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>707300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>430500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>377800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>145500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>161200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>137200</v>
       </c>
-      <c r="AG45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH45" s="3" t="s">
         <v>16</v>
       </c>
@@ -4219,101 +4317,104 @@
       <c r="AJ45" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK45" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1305300</v>
+      </c>
+      <c r="E46" s="3">
         <v>1363500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1755100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1911600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1781900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1588200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1507800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2949400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1943500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1498600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1447600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1598500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1591300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2703300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2949500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3083100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3102800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2272700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2607100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3033400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3121600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3522200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3795200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3897100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2883300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2384200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2715100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>867300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>817900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1615200</v>
       </c>
-      <c r="AG46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH46" s="3" t="s">
         <v>16</v>
       </c>
@@ -4323,101 +4424,104 @@
       <c r="AJ46" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK46" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>288900</v>
+      </c>
+      <c r="E47" s="3">
         <v>292900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>298900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>307200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>318800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>324100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>325400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>323800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>354400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>403100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>448400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>452500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>430300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>499900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>503200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>485900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>451300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>577200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>579900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>580200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>485700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>480400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>413700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>400600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>381200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>322800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>173900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>170000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>81500</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>59000</v>
       </c>
-      <c r="AG47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH47" s="3" t="s">
         <v>16</v>
       </c>
@@ -4427,101 +4531,104 @@
       <c r="AJ47" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK47" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>203800</v>
+      </c>
+      <c r="E48" s="3">
         <v>208300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>205300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>208600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>218300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>211600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>222900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>246100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>250800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>260400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>292000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>302900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>311000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>320700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>345200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>323500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>333400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>360000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>408400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>402000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>381400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>369600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>358100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>265700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>235000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>206500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>196600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>189200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>179200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>179600</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH48" s="3" t="s">
         <v>16</v>
       </c>
@@ -4531,101 +4638,104 @@
       <c r="AJ48" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK48" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1512600</v>
+      </c>
+      <c r="E49" s="3">
         <v>1567200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1521400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1533800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1564900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1535300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1472000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1592700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3398400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3344300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3291500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3244400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3126500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3033800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2854200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2546200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2436900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2355300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2174600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2369400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2362800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2601800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>2423100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2432100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>2315500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>2285000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1858100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1623800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1409900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1221500</v>
       </c>
-      <c r="AG49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH49" s="3" t="s">
         <v>16</v>
       </c>
@@ -4635,8 +4745,11 @@
       <c r="AJ49" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK49" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4852,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,101 +4959,104 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2955500</v>
+      </c>
+      <c r="E52" s="3">
         <v>2959200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2776200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2451100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2405000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2385400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2413300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2462800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>544900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>419600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>441300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>420100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>405500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>449900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>373200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>380400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>382900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>405700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>460100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>431800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>545600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>562800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>686200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>787200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>685500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>570200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>530500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>439700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>409900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>378500</v>
       </c>
-      <c r="AG52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH52" s="3" t="s">
         <v>16</v>
       </c>
@@ -4947,8 +5066,11 @@
       <c r="AJ52" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK52" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,101 +5173,104 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6269300</v>
+      </c>
+      <c r="E54" s="3">
         <v>6391100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6556900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6412300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6289000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6044700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5941400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7574800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6491900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5926000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5920800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6018500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5864600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7007500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7025300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6819100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6707400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5970900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6230000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6816800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6897200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>7536800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>7676300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>7782700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>6500500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>5768700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>5474100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>3289900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2898400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>3453700</v>
       </c>
-      <c r="AG54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH54" s="3" t="s">
         <v>16</v>
       </c>
@@ -5155,8 +5280,11 @@
       <c r="AJ54" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK54" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5321,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,101 +5360,102 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>888100</v>
+      </c>
+      <c r="E57" s="3">
         <v>924700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>821500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>816700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>799800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>813500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>791500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>832900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>845000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>950800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>877400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>969600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1228400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1297500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1181700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1045200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1052600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1088800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1133500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1304000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1264600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1574100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1464200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1574600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1475900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1458800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1269100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1252000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1010300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1035600</v>
       </c>
-      <c r="AG57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH57" s="3" t="s">
         <v>16</v>
       </c>
@@ -5335,101 +5465,104 @@
       <c r="AJ57" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK57" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>588300</v>
+      </c>
+      <c r="E58" s="3">
         <v>640700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1001900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>899500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>922800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>900500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>429600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1692600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1642900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1721400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1678900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>606400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>568600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1344000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1249600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1102100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1200900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>662600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>601300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>519500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>516600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>604300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>667800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>557600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>454600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>165500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>89900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>58400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>44400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1232000</v>
       </c>
-      <c r="AG58" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH58" s="3" t="s">
         <v>16</v>
       </c>
@@ -5439,101 +5572,104 @@
       <c r="AJ58" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK58" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1047100</v>
+      </c>
+      <c r="E59" s="3">
         <v>1081800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1060900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1037300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>878300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1040600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1035500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1117700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1478000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1355000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1358100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1389900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1306500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1331100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1335500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1355800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1206300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1242700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1281200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1445100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1325100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1178200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1144200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1013800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>946900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>887200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>710200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>619500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>613400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1325600</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH59" s="3" t="s">
         <v>16</v>
       </c>
@@ -5543,101 +5679,104 @@
       <c r="AJ59" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK59" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2942500</v>
+      </c>
+      <c r="E60" s="3">
         <v>3058200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3305000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3184600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3150700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3096800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2583700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4029100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3965800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4027300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3914400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2965900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3103600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3972600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3766800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3503200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3459800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2994100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3016000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3268600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3106300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3356700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3276200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3146000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2877300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2511500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2069200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1929900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1668000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>3593200</v>
       </c>
-      <c r="AG60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH60" s="3" t="s">
         <v>16</v>
       </c>
@@ -5647,101 +5786,104 @@
       <c r="AJ60" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK60" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1349400</v>
+      </c>
+      <c r="E61" s="3">
         <v>1304300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1276600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1271900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1236200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1209300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1645900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1769800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1348900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>880100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>832800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1828100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1747000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1801200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1808500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1763700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1660200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1889000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2001200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2112200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2029000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2057800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1879700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1856600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>777900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>38300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>39000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>40000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>40700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>42100</v>
       </c>
-      <c r="AG61" s="3">
-        <v>0</v>
-      </c>
       <c r="AH61" s="3">
         <v>0</v>
       </c>
@@ -5751,101 +5893,104 @@
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>145200</v>
+      </c>
+      <c r="E62" s="3">
         <v>135500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>182700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>187200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>172700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>183400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>230500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>225200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>282900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>265600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>288800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>271600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>230700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>232500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>253100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>258600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>272800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>288000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>290300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>281500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>266000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>220700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>225900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>248700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>208500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>210000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>97000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>96100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1100</v>
       </c>
-      <c r="AG62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH62" s="3" t="s">
         <v>16</v>
       </c>
@@ -5855,8 +6000,11 @@
       <c r="AJ62" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK62" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6107,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6214,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,101 +6321,104 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4437100</v>
+      </c>
+      <c r="E66" s="3">
         <v>4498000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4764300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4643700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4570600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4489700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4460300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6024200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5610700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5186000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5048800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5075000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5148300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6071100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5873200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5566700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5418900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5194800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5329500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5684500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5423400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5659900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5402400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>5268100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3880900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2771200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2205600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2066400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1710600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3636400</v>
       </c>
-      <c r="AG66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH66" s="3" t="s">
         <v>16</v>
       </c>
@@ -6271,8 +6428,11 @@
       <c r="AJ66" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK66" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6469,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6574,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6681,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6601,17 +6768,17 @@
         <v>0</v>
       </c>
       <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="3">
         <v>3284400</v>
       </c>
-      <c r="AE70" s="3">
+      <c r="AF70" s="3">
         <v>3242900</v>
       </c>
-      <c r="AF70" s="3">
+      <c r="AG70" s="3">
         <v>4323600</v>
       </c>
-      <c r="AG70" s="3">
-        <v>0</v>
-      </c>
       <c r="AH70" s="3">
         <v>0</v>
       </c>
@@ -6621,8 +6788,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,101 +6895,104 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-6002000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-6218500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-6034100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-6082400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-6286000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-6172700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-6276000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-6679200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-6555400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-6466300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-6451600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-6378400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-6512400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-6450800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-6268400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-5880400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-5703600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-5757100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-5636300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-5750400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-5209800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-4889200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-4224500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-3852200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-3414300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-2796700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-2357100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-2130900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-2154600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-4631600</v>
       </c>
-      <c r="AG72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH72" s="3" t="s">
         <v>16</v>
       </c>
@@ -6829,8 +7002,11 @@
       <c r="AJ72" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK72" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7109,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7216,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,101 +7323,104 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1831100</v>
+      </c>
+      <c r="E76" s="3">
         <v>1883100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1783900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1760800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1704500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1542600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1469800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1538600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>881200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>740000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>872000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>943500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>716300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>936400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1152200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1252400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1288500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>776100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>900500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1132300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1473700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1876900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2273900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2514600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2619500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2997500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>3268500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-2060900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-2055000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-4506300</v>
       </c>
-      <c r="AG76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH76" s="3" t="s">
         <v>16</v>
       </c>
@@ -7245,8 +7430,11 @@
       <c r="AJ76" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK76" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7537,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-25900</v>
+      </c>
+      <c r="E81" s="3">
         <v>32700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>9500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>90800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>65800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>65200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>50400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>90000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>42900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-54700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-29700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>23300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-246300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-246500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-201300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-176800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-215700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-171700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-212700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-450300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-384200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-575400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-355600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-275900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-504900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-439500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-294800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-98300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2198300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-1737000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-248500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-267600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-410200</v>
       </c>
-      <c r="AJ81" s="3" t="s">
+      <c r="AK81" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,13 +7797,14 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>16</v>
+      <c r="D83" s="3">
+        <v>38800</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>16</v>
@@ -7614,20 +7812,20 @@
       <c r="F83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G83" s="3">
+      <c r="G83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H83" s="3">
         <v>48900</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="I83" s="3" t="s">
         <v>16</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -7695,8 +7893,8 @@
       <c r="AG83" s="3">
         <v>0</v>
       </c>
-      <c r="AH83" s="3" t="s">
-        <v>16</v>
+      <c r="AH83" s="3">
+        <v>0</v>
       </c>
       <c r="AI83" s="3" t="s">
         <v>16</v>
@@ -7704,8 +7902,11 @@
       <c r="AJ83" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK83" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8009,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8116,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8223,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8330,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,71 +8437,74 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>71100</v>
+      </c>
+      <c r="E89" s="3">
         <v>34600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>56500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>129900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>89400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>113800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>122100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>145800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>120300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>27000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>6600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-161100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-151200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-295700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-204800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-187900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-211500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-281700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-200200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-94600</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>16</v>
       </c>
@@ -8301,8 +8517,8 @@
       <c r="AA89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB89" s="3">
-        <v>0</v>
+      <c r="AB89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AC89" s="3">
         <v>0</v>
@@ -8319,8 +8535,8 @@
       <c r="AG89" s="3">
         <v>0</v>
       </c>
-      <c r="AH89" s="3" t="s">
-        <v>16</v>
+      <c r="AH89" s="3">
+        <v>0</v>
       </c>
       <c r="AI89" s="3" t="s">
         <v>16</v>
@@ -8328,8 +8544,11 @@
       <c r="AJ89" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK89" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,41 +8585,42 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1800</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-48100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-66000</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
@@ -8410,8 +8630,8 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>16</v>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>16</v>
@@ -8422,8 +8642,8 @@
       <c r="T91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
+      <c r="U91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
@@ -8461,8 +8681,8 @@
       <c r="AG91" s="3">
         <v>0</v>
       </c>
-      <c r="AH91" s="3" t="s">
-        <v>16</v>
+      <c r="AH91" s="3">
+        <v>0</v>
       </c>
       <c r="AI91" s="3" t="s">
         <v>16</v>
@@ -8470,8 +8690,11 @@
       <c r="AJ91" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK91" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8797,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,71 +8904,74 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-122700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-237000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>46300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-30900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-201800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-7600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-58000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>24300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>81600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>56200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-90700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-9300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>289600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>268000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>8400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-386700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>39200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>50100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>168600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-252000</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>16</v>
       </c>
@@ -8755,8 +8984,8 @@
       <c r="AA94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB94" s="3">
-        <v>0</v>
+      <c r="AB94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AC94" s="3">
         <v>0</v>
@@ -8773,8 +9002,8 @@
       <c r="AG94" s="3">
         <v>0</v>
       </c>
-      <c r="AH94" s="3" t="s">
-        <v>16</v>
+      <c r="AH94" s="3">
+        <v>0</v>
       </c>
       <c r="AI94" s="3" t="s">
         <v>16</v>
@@ -8782,8 +9011,11 @@
       <c r="AJ94" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK94" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,8 +9052,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8846,8 +9079,8 @@
       <c r="J96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8924,8 +9157,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9264,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9371,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,71 +9478,74 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-372300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>119200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>36200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>36900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-162000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-488600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>403400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-14600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-46300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>282600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-723400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>123300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>115100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>85000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1168200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>34800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>121200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-12400</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>16</v>
       </c>
@@ -9313,8 +9558,8 @@
       <c r="AA100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
+      <c r="AB100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AC100" s="3">
         <v>0</v>
@@ -9331,8 +9576,8 @@
       <c r="AG100" s="3">
         <v>0</v>
       </c>
-      <c r="AH100" s="3" t="s">
-        <v>16</v>
+      <c r="AH100" s="3">
+        <v>0</v>
       </c>
       <c r="AI100" s="3" t="s">
         <v>16</v>
@@ -9340,71 +9585,74 @@
       <c r="AJ100" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK100" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E101" s="3">
         <v>600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>17600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>8500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>11200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>8300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>10400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-10200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-13300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-3900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-4600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-16500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>10100</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X101" s="3" t="s">
         <v>16</v>
       </c>
@@ -9417,8 +9665,8 @@
       <c r="AA101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
+      <c r="AB101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AC101" s="3">
         <v>0</v>
@@ -9435,8 +9683,8 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-      <c r="AH101" s="3" t="s">
-        <v>16</v>
+      <c r="AH101" s="3">
+        <v>0</v>
       </c>
       <c r="AI101" s="3" t="s">
         <v>16</v>
@@ -9444,71 +9692,74 @@
       <c r="AJ101" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK101" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-27600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-586700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>225100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>137200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-120000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>143800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-80300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-319800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>604100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>76900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-120000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>111600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-595300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>92400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-94700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-493500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>991300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-213400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>88300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-348900</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>16</v>
       </c>
@@ -9521,8 +9772,8 @@
       <c r="AA102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB102" s="3">
-        <v>0</v>
+      <c r="AB102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AC102" s="3">
         <v>0</v>
@@ -9539,13 +9790,16 @@
       <c r="AG102" s="3">
         <v>0</v>
       </c>
-      <c r="AH102" s="3" t="s">
-        <v>16</v>
+      <c r="AH102" s="3">
+        <v>0</v>
       </c>
       <c r="AI102" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AJ102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK102" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IQ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IQ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="92">
   <si>
     <t>IQ</t>
   </si>
@@ -919,7 +919,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>684200</v>
+        <v>671200</v>
       </c>
       <c r="E9" s="3">
         <v>805500</v>
@@ -1026,7 +1026,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>221800</v>
+        <v>234900</v>
       </c>
       <c r="E10" s="3">
         <v>227500</v>
@@ -1385,8 +1385,8 @@
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>16</v>
+      <c r="D14" s="3">
+        <v>13100</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>16</v>
@@ -1493,7 +1493,7 @@
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>200</v>
+        <v>264800</v>
       </c>
       <c r="E15" s="3">
         <v>268800</v>
@@ -1636,7 +1636,7 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>867000</v>
+        <v>853900</v>
       </c>
       <c r="E17" s="3">
         <v>998900</v>
@@ -1743,7 +1743,7 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>39100</v>
+        <v>52200</v>
       </c>
       <c r="E18" s="3">
         <v>34100</v>
@@ -1996,7 +1996,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>-2600</v>
+        <v>275000</v>
       </c>
       <c r="E21" s="3">
         <v>330800</v>
@@ -4005,7 +4005,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>339000</v>
+        <v>565700</v>
       </c>
       <c r="E43" s="3">
         <v>365100</v>
@@ -4219,7 +4219,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>353700</v>
+        <v>127000</v>
       </c>
       <c r="E45" s="3">
         <v>402800</v>
@@ -5474,7 +5474,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>588300</v>
+        <v>595100</v>
       </c>
       <c r="E58" s="3">
         <v>640700</v>
@@ -5486,7 +5486,7 @@
         <v>899500</v>
       </c>
       <c r="H58" s="3">
-        <v>922800</v>
+        <v>923100</v>
       </c>
       <c r="I58" s="3">
         <v>900500</v>
@@ -5581,7 +5581,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1047100</v>
+        <v>909000</v>
       </c>
       <c r="E59" s="3">
         <v>1081800</v>
@@ -5593,7 +5593,7 @@
         <v>1037300</v>
       </c>
       <c r="H59" s="3">
-        <v>878300</v>
+        <v>878000</v>
       </c>
       <c r="I59" s="3">
         <v>1040600</v>
@@ -5902,7 +5902,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>145200</v>
+        <v>137700</v>
       </c>
       <c r="E62" s="3">
         <v>135500</v>

--- a/AAII_Financials/Quarterly/IQ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IQ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="92">
   <si>
     <t>IQ</t>
   </si>
@@ -656,479 +656,505 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="3">
+        <v>990300</v>
+      </c>
+      <c r="F8" s="3">
         <v>906100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>1033000</v>
       </c>
-      <c r="F8" s="3">
-        <v>1023700</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="3">
         <v>1097900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>1086800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>1098500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1075800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>1215400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>1070400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>1032200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>925400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>1004800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>1020200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>1078800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>1092700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>1109200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>1038200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1049600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>1092200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>1197700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>1154300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>1154000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>1086300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>1063300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>1020600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>967700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>863600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>699800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>691200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>734700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>642100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>477600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>458800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>473800</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="3">
+        <v>745000</v>
+      </c>
+      <c r="F9" s="3">
         <v>671200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>805500</v>
       </c>
-      <c r="F9" s="3">
-        <v>781400</v>
-      </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="3">
         <v>779900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>744600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>800300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>796100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>867100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>761600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>788200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>729600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>823500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>898600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>999000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>986500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>989600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>944400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>929300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>1007000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>1237300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>1218700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>1275500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>1066600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>1107000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>1237800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>1071400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>854700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>695600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>650700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>726900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>1304500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>1035100</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>453900</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>456800</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="3">
+        <v>245300</v>
+      </c>
+      <c r="F10" s="3">
         <v>234900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>227500</v>
       </c>
-      <c r="F10" s="3">
-        <v>242300</v>
-      </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" s="3">
         <v>318000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>342200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>298200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>279700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>348300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>308800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>244000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>195800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>181300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>121700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>79800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>106200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>119600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>93800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>120400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>85200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>-39600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>-64300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>-121500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>19700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>-43700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>-217200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>-103700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>8900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>4200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>40500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>7800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>-662500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>-557500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>4900</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AM10" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1166,115 +1192,123 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="3">
+        <v>56800</v>
+      </c>
+      <c r="F12" s="3">
         <v>61800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>64000</v>
       </c>
-      <c r="F12" s="3">
-        <v>61700</v>
-      </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="3">
         <v>59500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>63700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>61300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>60500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>62400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>65700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>65700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>67000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>65600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>105400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>97100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>97200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>93600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>92300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>97800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>97900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>106200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>109500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>109700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>100000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>91000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>88200</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>78100</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>61800</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>55600</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>52300</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AI12" s="3">
         <v>50800</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AJ12" s="3">
         <v>87400</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AK12" s="3">
         <v>78200</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AL12" s="3">
         <v>35500</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AM12" s="3">
         <v>33400</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1380,40 +1414,46 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="3">
         <v>13100</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="3">
         <v>36300</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1487,41 +1527,47 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>266400</v>
+      </c>
+      <c r="F15" s="3">
         <v>264800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>268800</v>
       </c>
-      <c r="F15" s="3">
-        <v>259500</v>
-      </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
         <v>261100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>265900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>284200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>286000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>301900</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1594,8 +1640,14 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1630,222 +1682,236 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="3">
+        <v>943200</v>
+      </c>
+      <c r="F17" s="3">
         <v>853900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>998900</v>
       </c>
-      <c r="F17" s="3">
-        <v>976600</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" s="3">
         <v>967100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>942000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>996100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>991700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1090400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>960000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>989400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>907900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>991900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>1154900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>1273200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1253800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>1250400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>1220200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>1226300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>1281000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>1548600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>1543700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>1595700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>1372300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>1371500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>1503400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>1330400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>1049400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>852200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>814000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>893000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>789100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>628800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>569700</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>557900</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="3">
+        <v>47100</v>
+      </c>
+      <c r="F18" s="3">
         <v>52200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>34100</v>
       </c>
-      <c r="F18" s="3">
-        <v>47100</v>
-      </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" s="3">
         <v>130800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>144800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>102300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>84200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>125000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>110500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>42800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>17500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>12900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-134700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-194500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-161100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-141200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-182000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-176600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-188900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-351000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-389400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-441800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-286000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-308200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-482800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-362700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-185900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-152400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-122800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>-158300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>-147000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>-151200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>-110900</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>-84100</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1883,148 +1949,156 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="F20" s="3">
         <v>42000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-27900</v>
       </c>
-      <c r="F20" s="3">
-        <v>2900</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" s="3">
         <v>5200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>3700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>2500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>1100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>4000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-44300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-66400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-15200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>37700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-59200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>3000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>16800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>15100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>3900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>49100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>18400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-57400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>54200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-89300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-27300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>52700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>3800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-73300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>-106200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>96800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>39800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>2300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>17900</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>-20200</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AM20" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
+        <v>319000</v>
+      </c>
+      <c r="F21" s="3">
         <v>275000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>330800</v>
       </c>
-      <c r="F21" s="3">
-        <v>303700</v>
-      </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
         <v>386700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>407000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>384100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>369000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>422900</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>16</v>
       </c>
@@ -2079,347 +2153,371 @@
       <c r="AE21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AF21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH21" s="3">
         <v>1174600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>835600</v>
       </c>
-      <c r="AH21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AJ21" s="3">
+      <c r="AJ21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL21" s="3">
         <v>598900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>443800</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="3">
         <v>32200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
+        <v>32200</v>
+      </c>
+      <c r="G22" s="3">
         <v>36600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" s="3">
+        <v>39100</v>
+      </c>
+      <c r="J22" s="3">
+        <v>40100</v>
+      </c>
+      <c r="K22" s="3">
+        <v>38600</v>
+      </c>
+      <c r="L22" s="3">
+        <v>38400</v>
+      </c>
+      <c r="M22" s="3">
+        <v>41600</v>
+      </c>
+      <c r="N22" s="3">
+        <v>24800</v>
+      </c>
+      <c r="O22" s="3">
+        <v>25100</v>
+      </c>
+      <c r="P22" s="3">
+        <v>25300</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>24200</v>
+      </c>
+      <c r="R22" s="3">
+        <v>44800</v>
+      </c>
+      <c r="S22" s="3">
+        <v>49900</v>
+      </c>
+      <c r="T22" s="3">
+        <v>49300</v>
+      </c>
+      <c r="U22" s="3">
+        <v>46000</v>
+      </c>
+      <c r="V22" s="3">
+        <v>37500</v>
+      </c>
+      <c r="W22" s="3">
+        <v>39300</v>
+      </c>
+      <c r="X22" s="3">
+        <v>39100</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>41000</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>42600</v>
+      </c>
+      <c r="AA22" s="3">
         <v>39700</v>
       </c>
-      <c r="G22" s="3">
-        <v>39100</v>
-      </c>
-      <c r="H22" s="3">
-        <v>40100</v>
-      </c>
-      <c r="I22" s="3">
-        <v>38600</v>
-      </c>
-      <c r="J22" s="3">
-        <v>38400</v>
-      </c>
-      <c r="K22" s="3">
-        <v>41600</v>
-      </c>
-      <c r="L22" s="3">
-        <v>24800</v>
-      </c>
-      <c r="M22" s="3">
-        <v>25100</v>
-      </c>
-      <c r="N22" s="3">
-        <v>25300</v>
-      </c>
-      <c r="O22" s="3">
-        <v>24200</v>
-      </c>
-      <c r="P22" s="3">
-        <v>44800</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>49900</v>
-      </c>
-      <c r="R22" s="3">
-        <v>49300</v>
-      </c>
-      <c r="S22" s="3">
-        <v>46000</v>
-      </c>
-      <c r="T22" s="3">
-        <v>37500</v>
-      </c>
-      <c r="U22" s="3">
-        <v>39300</v>
-      </c>
-      <c r="V22" s="3">
-        <v>39100</v>
-      </c>
-      <c r="W22" s="3">
-        <v>41000</v>
-      </c>
-      <c r="X22" s="3">
-        <v>42600</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>39700</v>
-      </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>37900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>20600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>8900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>2200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>1300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>1200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>6300</v>
       </c>
-      <c r="AG22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>12200</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AK22" s="3">
         <v>9900</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AL22" s="3">
         <v>6100</v>
       </c>
-      <c r="AK22" s="3" t="s">
+      <c r="AM22" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" s="3">
+        <v>31300</v>
+      </c>
+      <c r="F23" s="3">
         <v>-24800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>35300</v>
       </c>
-      <c r="F23" s="3">
-        <v>14000</v>
-      </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I23" s="3">
         <v>94700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>72500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>67500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>51800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>94700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>41300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-48700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-23000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>26300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-238700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-241400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-193600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-172100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-215500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-166900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-209600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-449400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-377800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-570700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-351100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-276100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-487900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-438200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-293400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-56900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-89300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>-156000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>-141400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>-162700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>-137200</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>-91300</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="3">
+        <v>5700</v>
+      </c>
+      <c r="F24" s="3">
         <v>900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>1600</v>
       </c>
-      <c r="F24" s="3">
-        <v>3500</v>
-      </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" s="3">
         <v>2400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>5400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>1200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>1100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>3600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-1600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>5900</v>
-      </c>
-      <c r="N24" s="3">
-        <v>5000</v>
-      </c>
-      <c r="O24" s="3">
-        <v>2300</v>
       </c>
       <c r="P24" s="3">
         <v>5000</v>
       </c>
       <c r="Q24" s="3">
+        <v>2300</v>
+      </c>
+      <c r="R24" s="3">
+        <v>5000</v>
+      </c>
+      <c r="S24" s="3">
         <v>1300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>4400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>2900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>-2300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>2800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>2300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>3500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>2500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>1100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>11500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>-800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>700</v>
-      </c>
-      <c r="AE24" s="3">
-        <v>100</v>
-      </c>
-      <c r="AF24" s="3">
-        <v>-1400</v>
       </c>
       <c r="AG24" s="3">
         <v>100</v>
       </c>
       <c r="AH24" s="3">
-        <v>100</v>
+        <v>-1400</v>
       </c>
       <c r="AI24" s="3">
         <v>100</v>
       </c>
       <c r="AJ24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AK24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AL24" s="3">
         <v>600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2525,222 +2623,240 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" s="3">
+        <v>25600</v>
+      </c>
+      <c r="F26" s="3">
         <v>-25600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>33600</v>
       </c>
-      <c r="F26" s="3">
-        <v>10400</v>
-      </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I26" s="3">
         <v>92200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>67000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>66300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>50700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>91100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>42900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-54600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-28000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>24000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-243700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-242700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-198000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-175000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-213300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-169600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-212000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-450100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-381200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-573200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-352000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-277200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-499400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-437300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-294100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-56900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-87900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>-156100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>-141500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>-162800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>-137800</v>
       </c>
-      <c r="AK26" s="3" t="s">
+      <c r="AM26" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="3">
+        <v>25100</v>
+      </c>
+      <c r="F27" s="3">
         <v>-25900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>32700</v>
       </c>
-      <c r="F27" s="3">
-        <v>9500</v>
-      </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I27" s="3">
         <v>90800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>65800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>65200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>50400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>90000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>42900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-54700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-29700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>23300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-246300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-246500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-201300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-176800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-215700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-171700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-212700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-450300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-384200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-575400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-355600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-275900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-504900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-439500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-294800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-98300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>2198300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>-1737000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>-248500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>-267600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>-410200</v>
       </c>
-      <c r="AK27" s="3" t="s">
+      <c r="AM27" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2846,8 +2962,14 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2953,8 +3075,14 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3060,8 +3188,14 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3167,222 +3301,240 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" s="3">
+        <v>5500</v>
+      </c>
+      <c r="F32" s="3">
         <v>-42000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>27900</v>
       </c>
-      <c r="F32" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I32" s="3">
         <v>-5200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-3700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-2500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-1100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-4000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>44300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>66400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>15200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-37700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>59200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-3000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-16800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-15100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-3900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-49100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-18400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>57400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-54200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>89300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>27300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-52700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-3800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>73300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>106200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-96800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-39800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>-2300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>-17900</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>1600</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>20200</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AM32" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" s="3">
+        <v>25100</v>
+      </c>
+      <c r="F33" s="3">
         <v>-25900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>32700</v>
       </c>
-      <c r="F33" s="3">
-        <v>9500</v>
-      </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I33" s="3">
         <v>90800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>65800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>65200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>50400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>90000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>42900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-54700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-29700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>23300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-246300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-246500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-201300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-176800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-215700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-171700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-212700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-450300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-384200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-575400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-355600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-275900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-504900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-439500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-294800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-98300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>2198300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>-1737000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>-248500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>-267600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>-410200</v>
       </c>
-      <c r="AK33" s="3" t="s">
+      <c r="AM33" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3488,227 +3640,245 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35" s="3">
+        <v>25100</v>
+      </c>
+      <c r="F35" s="3">
         <v>-25900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>32700</v>
       </c>
-      <c r="F35" s="3">
-        <v>9500</v>
-      </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I35" s="3">
         <v>90800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>65800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>65200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>50400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>90000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>42900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-54700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-29700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>23300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-246300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-246500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-201300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-176800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-215700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-171700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-212700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-450300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-384200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-575400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-355600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-275900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-504900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-439500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-294800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-98300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>2198300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>-1737000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>-248500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>-267600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>-410200</v>
       </c>
-      <c r="AK35" s="3" t="s">
+      <c r="AM35" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3746,8 +3916,10 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3785,329 +3957,349 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E41" s="3">
+        <v>595300</v>
+      </c>
+      <c r="F41" s="3">
         <v>483600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>462100</v>
       </c>
-      <c r="F41" s="3">
-        <v>867200</v>
-      </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I41" s="3">
         <v>698700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>625400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>579800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>491600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>659400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1000700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>491800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>406400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>526300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>413900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>1037100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>960100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>1023500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>1519400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>461900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>630800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>578200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>913800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>702900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>829200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>1806300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>666100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>816200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>1159100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>57900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>105200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>176500</v>
       </c>
-      <c r="AH41" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ41" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AK41" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM41" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>130400</v>
+      </c>
+      <c r="F42" s="3">
         <v>129000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>133500</v>
       </c>
-      <c r="F42" s="3">
-        <v>101300</v>
-      </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>136600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>132800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>140500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>139900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>97400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>115400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>203200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>262800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>177100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>186200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>520500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>793700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>823300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>467500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>526300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>618400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>823300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>705100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>1067400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>1347200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>591100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>880400</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>538000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AF42" s="3">
         <v>665100</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AG42" s="3">
         <v>70700</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AH42" s="3">
         <v>111900</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AI42" s="3">
         <v>497500</v>
       </c>
-      <c r="AH42" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ42" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AK42" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM42" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E43" s="3">
+        <v>365300</v>
+      </c>
+      <c r="F43" s="3">
         <v>565700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>365100</v>
       </c>
-      <c r="F43" s="3">
-        <v>366000</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I43" s="3">
         <v>615500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>847400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>366700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>393300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>421300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>353400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>380500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>359000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>388200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>400900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>448800</v>
-      </c>
-      <c r="R43" s="3">
-        <v>478900</v>
-      </c>
-      <c r="S43" s="3">
-        <v>494800</v>
       </c>
       <c r="T43" s="3">
         <v>478900</v>
       </c>
       <c r="U43" s="3">
+        <v>494800</v>
+      </c>
+      <c r="V43" s="3">
+        <v>478900</v>
+      </c>
+      <c r="W43" s="3">
         <v>500900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>503700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>717100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>591200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>514100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>513100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>535000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>460500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>452200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>350200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>420800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>322200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>693700</v>
       </c>
-      <c r="AH43" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ43" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AK43" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM43" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4135,621 +4327,657 @@
       <c r="K44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L44" s="3">
+      <c r="L44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N44" s="3">
         <v>105200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>113000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>110700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>125700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>128600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>155900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>127900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>143600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>144100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>182200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>174500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>224300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>188600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>206500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>179700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>191900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>169000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>147200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>162900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>172400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>117500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>110300</v>
       </c>
-      <c r="AH44" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ44" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AK44" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM44" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E45" s="3">
+        <v>398700</v>
+      </c>
+      <c r="F45" s="3">
         <v>127000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>402800</v>
       </c>
-      <c r="F45" s="3">
-        <v>420600</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I45" s="3">
         <v>460800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>175400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>500300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>482100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>1770400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>368900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>310100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>308700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>381200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>461800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>540900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>588900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>597800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>492900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>601500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>679700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>690600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>722800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>1031300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>926000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>772700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>707300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>430500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>377800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>145500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>161200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>137200</v>
       </c>
-      <c r="AH45" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ45" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AK45" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM45" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1490000</v>
+      </c>
+      <c r="F46" s="3">
         <v>1305300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1363500</v>
       </c>
-      <c r="F46" s="3">
-        <v>1755100</v>
-      </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I46" s="3">
         <v>1911600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1781900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1588200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1507800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>2949400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1943500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1498600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1447600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1598500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>1591300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>2703300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>2949500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>3083100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>3102800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>2272700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>2607100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>3033400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>3121600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>3522200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>3795200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>3897100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>2883300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>2384200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>2715100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>867300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>817900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>1615200</v>
       </c>
-      <c r="AH46" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ46" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AK46" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM46" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E47" s="3">
+        <v>289200</v>
+      </c>
+      <c r="F47" s="3">
         <v>288900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>292900</v>
       </c>
-      <c r="F47" s="3">
-        <v>298900</v>
-      </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I47" s="3">
         <v>307200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>318800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>324100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>325400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>323800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>354400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>403100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>448400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>452500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>430300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>499900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>503200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>485900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>451300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>577200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>579900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>580200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>485700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>480400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>413700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>400600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>381200</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>322800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>173900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>170000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>81500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AI47" s="3">
         <v>59000</v>
       </c>
-      <c r="AH47" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ47" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AK47" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM47" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E48" s="3">
+        <v>199000</v>
+      </c>
+      <c r="F48" s="3">
         <v>203800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>208300</v>
       </c>
-      <c r="F48" s="3">
-        <v>205300</v>
-      </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I48" s="3">
         <v>208600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>218300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>211600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>222900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>246100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>250800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>260400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>292000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>302900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>311000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>320700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>345200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>323500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>333400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>360000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>408400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>402000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>381400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>369600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>358100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>265700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>235000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>206500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>196600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>189200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>179200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>179600</v>
       </c>
-      <c r="AH48" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ48" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AK48" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM48" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1457800</v>
+      </c>
+      <c r="F49" s="3">
         <v>1512600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>1567200</v>
       </c>
-      <c r="F49" s="3">
-        <v>1521400</v>
-      </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I49" s="3">
         <v>1533800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>1564900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>1535300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>1472000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>1592700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>3398400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>3344300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>3291500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>3244400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>3126500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>3033800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>2854200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>2546200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>2436900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>2355300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>2174600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>2369400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>2362800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>2601800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>2423100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>2432100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>2315500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>2285000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>1858100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>1623800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>1409900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>1221500</v>
       </c>
-      <c r="AH49" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ49" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AK49" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM49" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4855,8 +5083,14 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4962,115 +5196,127 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E52" s="3">
+        <v>3054300</v>
+      </c>
+      <c r="F52" s="3">
         <v>2955500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>2959200</v>
       </c>
-      <c r="F52" s="3">
-        <v>2776200</v>
-      </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I52" s="3">
         <v>2451100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>2405000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>2385400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>2413300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>2462800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>544900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>419600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>441300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>420100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>405500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>449900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>373200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>380400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>382900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>405700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>460100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>431800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>545600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>562800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>686200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>787200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>685500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>570200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>530500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>439700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>409900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>378500</v>
       </c>
-      <c r="AH52" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ52" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AK52" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM52" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5176,115 +5422,127 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E54" s="3">
+        <v>6493400</v>
+      </c>
+      <c r="F54" s="3">
         <v>6269300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>6391100</v>
       </c>
-      <c r="F54" s="3">
-        <v>6556900</v>
-      </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I54" s="3">
         <v>6412300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>6289000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>6044700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>5941400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>7574800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>6491900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>5926000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>5920800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>6018500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>5864600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>7007500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>7025300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>6819100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>6707400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>5970900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>6230000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>6816800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>6897200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>7536800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>7676300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>7782700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>6500500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>5768700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>5474100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>3289900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>2898400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>3453700</v>
       </c>
-      <c r="AH54" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ54" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AK54" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM54" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5322,8 +5580,10 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5361,650 +5621,688 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E57" s="3">
+        <v>893000</v>
+      </c>
+      <c r="F57" s="3">
         <v>888100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>924700</v>
       </c>
-      <c r="F57" s="3">
-        <v>821500</v>
-      </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I57" s="3">
         <v>816700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>799800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>813500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>791500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>832900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>845000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>950800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>877400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>969600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>1228400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>1297500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>1181700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>1045200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>1052600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>1088800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>1133500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>1304000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>1264600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>1574100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>1464200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>1574600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>1475900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>1458800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>1269100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>1252000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>1010300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>1035600</v>
       </c>
-      <c r="AH57" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ57" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AK57" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM57" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E58" s="3">
+        <v>858500</v>
+      </c>
+      <c r="F58" s="3">
         <v>595100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>640700</v>
       </c>
-      <c r="F58" s="3">
-        <v>1001900</v>
-      </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I58" s="3">
         <v>899500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>923100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>900500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>429600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1692600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1642900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1721400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>1678900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>606400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>568600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>1344000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>1249600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>1102100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>1200900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>662600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>601300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>519500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>516600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>604300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>667800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>557600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>454600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>165500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>89900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>58400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>44400</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>1232000</v>
       </c>
-      <c r="AH58" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI58" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ58" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AK58" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM58" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1087900</v>
+      </c>
+      <c r="F59" s="3">
         <v>909000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1081800</v>
       </c>
-      <c r="F59" s="3">
-        <v>1060900</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I59" s="3">
         <v>1037300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>878000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1040600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1035500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1117700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1478000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1355000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1358100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>1389900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1306500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1331100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>1335500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>1355800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>1206300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>1242700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>1281200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>1445100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>1325100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>1178200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>1144200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>1013800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>946900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>887200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>710200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>619500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>613400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>1325600</v>
       </c>
-      <c r="AH59" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ59" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AK59" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM59" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E60" s="3">
+        <v>3258600</v>
+      </c>
+      <c r="F60" s="3">
         <v>2942500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>3058200</v>
       </c>
-      <c r="F60" s="3">
-        <v>3305000</v>
-      </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I60" s="3">
         <v>3184600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>3150700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>3096800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>2583700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>4029100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>3965800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>4027300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>3914400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>2965900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>3103600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>3972600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>3766800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>3503200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>3459800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>2994100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>3016000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>3268600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>3106300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>3356700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>3276200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>3146000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>2877300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>2511500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>2069200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>1929900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>1668000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>3593200</v>
       </c>
-      <c r="AH60" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ60" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AK60" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM60" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1212200</v>
+      </c>
+      <c r="F61" s="3">
         <v>1349400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1304300</v>
       </c>
-      <c r="F61" s="3">
-        <v>1276600</v>
-      </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>1271900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>1236200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>1209300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>1645900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>1769800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>1348900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>880100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>832800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>1828100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>1747000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>1801200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>1808500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>1763700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>1660200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>1889000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>2001200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>2112200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>2029000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>2057800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>1879700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>1856600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>777900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>38300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>39000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>40000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>40700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>42100</v>
       </c>
-      <c r="AH61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI61" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
       <c r="AK61" s="3">
         <v>0</v>
       </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E62" s="3">
+        <v>143100</v>
+      </c>
+      <c r="F62" s="3">
         <v>137700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>135500</v>
       </c>
-      <c r="F62" s="3">
-        <v>182700</v>
-      </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I62" s="3">
         <v>187200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>172700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>183400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>230500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>225200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>282900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>265600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>288800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>271600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>230700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>232500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>253100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>258600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>272800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>288000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>290300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>281500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>266000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>220700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>225900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>248700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>208500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>210000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>97000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>96100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>1200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>1100</v>
       </c>
-      <c r="AH62" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ62" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AK62" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM62" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6110,8 +6408,14 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6217,8 +6521,14 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6324,115 +6634,127 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E66" s="3">
+        <v>4614000</v>
+      </c>
+      <c r="F66" s="3">
         <v>4437100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>4498000</v>
       </c>
-      <c r="F66" s="3">
-        <v>4764300</v>
-      </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I66" s="3">
         <v>4643700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>4570600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>4489700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>4460300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>6024200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>5610700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>5186000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>5048800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>5075000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>5148300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>6071100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>5873200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>5566700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>5418900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>5194800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>5329500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>5684500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>5423400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>5659900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>5402400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>5268100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>3880900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>2771200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>2205600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>2066400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>1710600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>3636400</v>
       </c>
-      <c r="AH66" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ66" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AK66" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM66" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6470,8 +6792,10 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6577,8 +6901,14 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6684,8 +7014,14 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6771,28 +7107,34 @@
         <v>0</v>
       </c>
       <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
         <v>3284400</v>
       </c>
-      <c r="AF70" s="3">
+      <c r="AH70" s="3">
         <v>3242900</v>
       </c>
-      <c r="AG70" s="3">
+      <c r="AI70" s="3">
         <v>4323600</v>
       </c>
-      <c r="AH70" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI70" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6898,115 +7240,127 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-6012200</v>
+      </c>
+      <c r="F72" s="3">
         <v>-6002000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-6218500</v>
       </c>
-      <c r="F72" s="3">
-        <v>-6034100</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I72" s="3">
         <v>-6082400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-6286000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-6172700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-6276000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-6679200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-6555400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-6466300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-6451600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-6378400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-6512400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-6450800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-6268400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-5880400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-5703600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-5757100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-5636300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-5750400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-5209800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-4889200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-4224500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-3852200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-3414300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-2796700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-2357100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-2130900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>-2154600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>-4631600</v>
       </c>
-      <c r="AH72" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ72" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AK72" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM72" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7112,8 +7466,14 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7219,8 +7579,14 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7326,115 +7692,127 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1880400</v>
+      </c>
+      <c r="F76" s="3">
         <v>1831100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1883100</v>
       </c>
-      <c r="F76" s="3">
-        <v>1783900</v>
-      </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I76" s="3">
         <v>1760800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>1704500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>1542600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>1469800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1538600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>881200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>740000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>872000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>943500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>716300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>936400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>1152200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>1252400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>1288500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>776100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>900500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>1132300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>1473700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>1876900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>2273900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>2514600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>2619500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>2997500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>3268500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>-2060900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>-2055000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>-4506300</v>
       </c>
-      <c r="AH76" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ76" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AK76" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM76" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7540,227 +7918,245 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E81" s="3">
+        <v>25100</v>
+      </c>
+      <c r="F81" s="3">
         <v>-25900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>32700</v>
       </c>
-      <c r="F81" s="3">
-        <v>9500</v>
-      </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I81" s="3">
         <v>90800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>65800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>65200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>50400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>90000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>42900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-54700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-29700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>23300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-246300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-246500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-201300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-176800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-215700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-171700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-212700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-450300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-384200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-575400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-355600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-275900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-504900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-439500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-294800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-98300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>2198300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>-1737000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>-248500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>-267600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>-410200</v>
       </c>
-      <c r="AK81" s="3" t="s">
+      <c r="AM81" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7798,40 +8194,42 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F83" s="3">
         <v>38800</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="G83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H83" s="3">
+      <c r="H83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J83" s="3">
         <v>48900</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -7896,17 +8294,23 @@
       <c r="AH83" s="3">
         <v>0</v>
       </c>
-      <c r="AI83" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AJ83" s="3" t="s">
-        <v>16</v>
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ83" s="3">
+        <v>0</v>
       </c>
       <c r="AK83" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM83" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8012,8 +8416,14 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8119,8 +8529,14 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8226,8 +8642,14 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8333,8 +8755,14 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8440,77 +8868,83 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E89" s="3">
+        <v>46700</v>
+      </c>
+      <c r="F89" s="3">
         <v>71100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>34600</v>
       </c>
-      <c r="F89" s="3">
-        <v>56500</v>
-      </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I89" s="3">
         <v>129900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>89400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>113800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>122100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>145800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>120300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>27000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>6600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-161100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-151200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-295700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-204800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-187900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-211500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-281700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-200200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-94600</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>16</v>
       </c>
@@ -8520,11 +8954,11 @@
       <c r="AB89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AC89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD89" s="3">
-        <v>0</v>
+      <c r="AC89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AE89" s="3">
         <v>0</v>
@@ -8538,17 +8972,23 @@
       <c r="AH89" s="3">
         <v>0</v>
       </c>
-      <c r="AI89" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AJ89" s="3" t="s">
-        <v>16</v>
+      <c r="AI89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ89" s="3">
+        <v>0</v>
       </c>
       <c r="AK89" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM89" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8586,58 +9026,60 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-2900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-1100</v>
       </c>
-      <c r="F91" s="3">
-        <v>-3900</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-3100</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="H91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="J91" s="3">
         <v>-2700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-1800</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-48100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-66000</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="S91" s="3" t="s">
-        <v>16</v>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>16</v>
@@ -8645,11 +9087,11 @@
       <c r="U91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
-      <c r="W91" s="3">
-        <v>0</v>
+      <c r="V91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="W91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X91" s="3">
         <v>0</v>
@@ -8684,17 +9126,23 @@
       <c r="AH91" s="3">
         <v>0</v>
       </c>
-      <c r="AI91" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AJ91" s="3" t="s">
-        <v>16</v>
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ91" s="3">
+        <v>0</v>
       </c>
       <c r="AK91" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM91" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8800,8 +9248,14 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8907,77 +9361,83 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="F94" s="3">
         <v>-122700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-237000</v>
       </c>
-      <c r="F94" s="3">
-        <v>46300</v>
-      </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I94" s="3">
         <v>-30900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-201800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-7600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-58000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>24300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>81600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>56200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-90700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-9300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>289600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>268000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>8400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-386700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>39200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>50100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>168600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-252000</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>16</v>
       </c>
@@ -8987,11 +9447,11 @@
       <c r="AB94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AC94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD94" s="3">
-        <v>0</v>
+      <c r="AC94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AE94" s="3">
         <v>0</v>
@@ -9005,17 +9465,23 @@
       <c r="AH94" s="3">
         <v>0</v>
       </c>
-      <c r="AI94" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AJ94" s="3" t="s">
-        <v>16</v>
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ94" s="3">
+        <v>0</v>
       </c>
       <c r="AK94" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM94" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9053,8 +9519,10 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9082,11 +9550,11 @@
       <c r="K96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9160,8 +9628,14 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9267,8 +9741,14 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9374,8 +9854,14 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9481,77 +9967,83 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E100" s="3">
+        <v>118600</v>
+      </c>
+      <c r="F100" s="3">
         <v>15700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-372300</v>
       </c>
-      <c r="F100" s="3">
-        <v>119200</v>
-      </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I100" s="3">
         <v>36200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-3200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>36900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-162000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-488600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>403400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-14600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-46300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>282600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-723400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>123300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>115100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>85000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>1168200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>34800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>121200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-12400</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>16</v>
       </c>
@@ -9561,11 +10053,11 @@
       <c r="AB100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD100" s="3">
-        <v>0</v>
+      <c r="AC100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AE100" s="3">
         <v>0</v>
@@ -9579,86 +10071,92 @@
       <c r="AH100" s="3">
         <v>0</v>
       </c>
-      <c r="AI100" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AJ100" s="3" t="s">
-        <v>16</v>
+      <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ100" s="3">
+        <v>0</v>
       </c>
       <c r="AK100" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM100" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F101" s="3">
         <v>-4400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>600</v>
       </c>
-      <c r="F101" s="3">
-        <v>17600</v>
-      </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I101" s="3">
         <v>-1300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-1200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>8500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>11200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-1200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>8300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>10400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-10200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-3200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-13300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-3900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-4600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-16500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-1500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>10100</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z101" s="3" t="s">
         <v>16</v>
       </c>
@@ -9668,11 +10166,11 @@
       <c r="AB101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD101" s="3">
-        <v>0</v>
+      <c r="AC101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AE101" s="3">
         <v>0</v>
@@ -9686,86 +10184,92 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-      <c r="AI101" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AJ101" s="3" t="s">
-        <v>16</v>
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
       </c>
       <c r="AK101" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM101" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>161000</v>
+      </c>
+      <c r="F102" s="3">
         <v>-27600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-586700</v>
       </c>
-      <c r="F102" s="3">
-        <v>225100</v>
-      </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>137200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-120000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>143800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-80300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-319800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>604100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>76900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-120000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>111600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-595300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>92400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-94700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-493500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>991300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-213400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>88300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-348900</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>16</v>
       </c>
@@ -9775,11 +10279,11 @@
       <c r="AB102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AC102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD102" s="3">
-        <v>0</v>
+      <c r="AC102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AE102" s="3">
         <v>0</v>
@@ -9793,13 +10297,19 @@
       <c r="AH102" s="3">
         <v>0</v>
       </c>
-      <c r="AI102" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AJ102" s="3" t="s">
-        <v>16</v>
+      <c r="AI102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ102" s="3">
+        <v>0</v>
       </c>
       <c r="AK102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM102" s="3" t="s">
         <v>16</v>
       </c>
     </row>
